--- a/data/output/Timehistory_modal/响应统计结果.xlsx
+++ b/data/output/Timehistory_modal/响应统计结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyFiles\GitHub\corner-point-response\data\output\Timehistory_modal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87589024-60C5-47E1-8892-BB5896608A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C1C5A9-5CF1-480C-94BB-3C2FF83516DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,6 @@
     <sheet name="3-1_Acceleration" sheetId="3" r:id="rId3"/>
     <sheet name="结果对比" sheetId="4" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-    <externalReference r:id="rId6"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -471,7 +467,38 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -499,27 +526,34 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" altLang="zh-CN"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
-          <a:prstDash val="solid"/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -535,48 +569,48 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Sheet1!$E$5:$E$14</c:f>
+              <c:f>结果对比!$E$5:$E$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.9769999999999999E-2</c:v>
+                  <c:v>6.473000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.9930000000000006E-2</c:v>
+                  <c:v>6.5129999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.9639999999999999E-2</c:v>
+                  <c:v>5.525E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.4280000000000004E-2</c:v>
+                  <c:v>6.012E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.4140000000000001E-2</c:v>
+                  <c:v>5.0380000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.4609999999999999E-2</c:v>
+                  <c:v>5.1290000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.33E-2</c:v>
+                  <c:v>5.0349999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.9360000000000003E-2</c:v>
+                  <c:v>5.5879999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9159999999999997E-2</c:v>
+                  <c:v>5.5229999999999987E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.6919999999999998E-2</c:v>
+                  <c:v>5.3159999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -584,7 +618,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-00FA-4377-83C4-DE3E6216A7B8}"/>
+              <c16:uniqueId val="{00000000-D1A3-4FA1-BF8C-2F7029461899}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -596,16 +630,16 @@
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Sheet1!$F$5:$F$14</c:f>
+              <c:f>结果对比!$F$5:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -645,7 +679,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-00FA-4377-83C4-DE3E6216A7B8}"/>
+              <c16:uniqueId val="{00000001-D1A3-4FA1-BF8C-2F7029461899}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -657,48 +691,48 @@
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[1]Sheet1!$G$5:$G$14</c:f>
+              <c:f>结果对比!$G$5:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.12695000000000001</c:v>
+                  <c:v>0.12665999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14552999999999999</c:v>
+                  <c:v>0.14563000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13299</c:v>
+                  <c:v>0.13300999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11885999999999999</c:v>
+                  <c:v>0.11905</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.955E-2</c:v>
+                  <c:v>9.9919999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.1939999999999999E-2</c:v>
+                  <c:v>8.2189999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2170000000000007E-2</c:v>
+                  <c:v>8.2290000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.5400000000000009E-2</c:v>
+                  <c:v>7.3810000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.0730000000000001E-2</c:v>
+                  <c:v>6.8659999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.9339999999999999E-2</c:v>
+                  <c:v>6.7409999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -706,7 +740,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-00FA-4377-83C4-DE3E6216A7B8}"/>
+              <c16:uniqueId val="{00000002-D1A3-4FA1-BF8C-2F7029461899}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -719,11 +753,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="639407936"/>
-        <c:axId val="639398936"/>
+        <c:axId val="812207544"/>
+        <c:axId val="812200704"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="639407936"/>
+        <c:axId val="812207544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -741,16 +775,16 @@
                 <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
-            <a:prstDash val="solid"/>
             <a:round/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -765,7 +799,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="639398936"/>
+        <c:crossAx val="812200704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -773,7 +807,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="639398936"/>
+        <c:axId val="812200704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -788,9 +822,9 @@
                   <a:lumOff val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
+            <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -801,15 +835,15 @@
           <a:noFill/>
           <a:ln>
             <a:noFill/>
-            <a:prstDash val="solid"/>
           </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -824,10 +858,17 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="639407936"/>
+        <c:crossAx val="812207544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -836,15 +877,15 @@
         <a:noFill/>
         <a:ln>
           <a:noFill/>
-          <a:prstDash val="solid"/>
         </a:ln>
+        <a:effectLst/>
       </c:spPr>
       <c:txPr>
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -862,6 +903,13 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -875,10 +923,20 @@
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:prstDash val="solid"/>
       <a:round/>
     </a:ln>
+    <a:effectLst/>
   </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -954,7 +1012,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[2]Sheet1!$E$4:$E$22</c:f>
+              <c:f>结果对比!$E$30:$E$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -1021,7 +1079,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8105-4593-AA56-4FD00832529F}"/>
+              <c16:uniqueId val="{00000000-64CA-4BE1-966C-A3E5D09B3B84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1042,7 +1100,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[2]Sheet1!$F$4:$F$22</c:f>
+              <c:f>结果对比!$F$30:$F$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -1109,7 +1167,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8105-4593-AA56-4FD00832529F}"/>
+              <c16:uniqueId val="{00000001-64CA-4BE1-966C-A3E5D09B3B84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1130,7 +1188,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>[2]Sheet1!$G$4:$G$22</c:f>
+              <c:f>结果对比!$G$30:$G$48</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -1197,7 +1255,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8105-4593-AA56-4FD00832529F}"/>
+              <c16:uniqueId val="{00000002-64CA-4BE1-966C-A3E5D09B3B84}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1210,11 +1268,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="678909600"/>
-        <c:axId val="678909960"/>
+        <c:axId val="812199984"/>
+        <c:axId val="812204664"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="678909600"/>
+        <c:axId val="812199984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1256,7 +1314,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678909960"/>
+        <c:crossAx val="812204664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1264,7 +1322,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="678909960"/>
+        <c:axId val="812204664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1315,7 +1373,555 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678909600"/>
+        <c:crossAx val="812199984"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>结果对比!$E$57</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>X</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>结果对比!$E$58:$E$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>6.7780000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.5129999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.470999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5409999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.0900000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.7229999999999987E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.7479999999999987E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.5269999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5770000000000012E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.042E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.4089999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.4420000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.2840000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.888E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.2690000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.9859999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.1009999999999988E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.583E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.4090000000000003E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1337-4B5F-8FC5-B201542A4096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>结果对比!$F$57</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>结果对比!$F$58:$F$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>4.2500000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.5400000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.4790000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6039999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.6710000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.0329999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.3520000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.9600000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.512E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.4170000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.213E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.0740000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.1080000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.1499999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.0570000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.1350000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2.2249999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.4410000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.4840000000000001E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1337-4B5F-8FC5-B201542A4096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>结果对比!$G$57</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>结果对比!$G$58:$G$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>6.8030000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.5519999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.4909999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6.5619999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.1400000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.9689999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4.7659999999999987E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.5439999999999987E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5840000000000013E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5.0500000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.4150000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4.4429999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.2869999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.8920000000000012E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.2749999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.9929999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.1069999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>6.5909999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.4189999999999992E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1337-4B5F-8FC5-B201542A4096}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="360567536"/>
+        <c:axId val="360562136"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="360567536"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="360562136"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="360562136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="360567536"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1403,6 +2009,86 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1958,33 +2644,1063 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>608647</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>179070</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>134302</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>158115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>303847</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>20955</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>439102</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>5715</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="6" name="图表 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39B39969-0B83-4480-A428-8A1F1190E563}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{769DE66F-4F45-0556-9BAD-6D4BE8DC69CC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2000,29 +3716,27 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>159067</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>353377</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>34290</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>463867</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>48577</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>62865</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="图表 2">
+        <xdr:cNvPr id="7" name="图表 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE0D7E65-CCE8-4BE0-923F-091B41A7A35A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0557334A-D9B9-E335-FF7B-E86BBA41E731}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2036,364 +3750,43 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>353377</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>48577</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>81915</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="图表 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6617138A-B58F-D6CE-98E9-0E3620F8918E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="1-1_Acceleration"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="E5">
-            <v>6.9769999999999999E-2</v>
-          </cell>
-          <cell r="F5">
-            <v>0.1265</v>
-          </cell>
-          <cell r="G5">
-            <v>0.12695000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="E6">
-            <v>6.9930000000000006E-2</v>
-          </cell>
-          <cell r="F6">
-            <v>0.14530999999999999</v>
-          </cell>
-          <cell r="G6">
-            <v>0.14552999999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7">
-            <v>5.9639999999999999E-2</v>
-          </cell>
-          <cell r="F7">
-            <v>0.13275000000000001</v>
-          </cell>
-          <cell r="G7">
-            <v>0.13299</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="E8">
-            <v>6.4280000000000004E-2</v>
-          </cell>
-          <cell r="F8">
-            <v>0.11869</v>
-          </cell>
-          <cell r="G8">
-            <v>0.11885999999999999</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9">
-            <v>5.4140000000000001E-2</v>
-          </cell>
-          <cell r="F9">
-            <v>9.9510000000000001E-2</v>
-          </cell>
-          <cell r="G9">
-            <v>9.955E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="E10">
-            <v>5.4609999999999999E-2</v>
-          </cell>
-          <cell r="F10">
-            <v>8.181999999999999E-2</v>
-          </cell>
-          <cell r="G10">
-            <v>8.1939999999999999E-2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11">
-            <v>5.33E-2</v>
-          </cell>
-          <cell r="F11">
-            <v>8.2019999999999996E-2</v>
-          </cell>
-          <cell r="G11">
-            <v>8.2170000000000007E-2</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="E12">
-            <v>5.9360000000000003E-2</v>
-          </cell>
-          <cell r="F12">
-            <v>7.3209999999999997E-2</v>
-          </cell>
-          <cell r="G12">
-            <v>7.5400000000000009E-2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="E13">
-            <v>5.9159999999999997E-2</v>
-          </cell>
-          <cell r="F13">
-            <v>6.5680000000000002E-2</v>
-          </cell>
-          <cell r="G13">
-            <v>7.0730000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="E14">
-            <v>5.6919999999999998E-2</v>
-          </cell>
-          <cell r="F14">
-            <v>6.5370000000000011E-2</v>
-          </cell>
-          <cell r="G14">
-            <v>6.9339999999999999E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Acceleration"/>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1">
-        <row r="4">
-          <cell r="E4">
-            <v>8.7139999999999995E-2</v>
-          </cell>
-          <cell r="F4">
-            <v>6.9879999999999998E-2</v>
-          </cell>
-          <cell r="G4">
-            <v>9.1069999999999998E-2</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="E5">
-            <v>7.3819999999999997E-2</v>
-          </cell>
-          <cell r="F5">
-            <v>6.9889999999999994E-2</v>
-          </cell>
-          <cell r="G5">
-            <v>8.131999999999999E-2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="E6">
-            <v>9.0029999999999999E-2</v>
-          </cell>
-          <cell r="F6">
-            <v>7.1160000000000001E-2</v>
-          </cell>
-          <cell r="G6">
-            <v>9.3310000000000004E-2</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7">
-            <v>7.3300000000000004E-2</v>
-          </cell>
-          <cell r="F7">
-            <v>6.7080000000000001E-2</v>
-          </cell>
-          <cell r="G7">
-            <v>7.9489999999999991E-2</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="E8">
-            <v>7.886E-2</v>
-          </cell>
-          <cell r="F8">
-            <v>6.2859999999999999E-2</v>
-          </cell>
-          <cell r="G8">
-            <v>8.1220000000000001E-2</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9">
-            <v>6.4879999999999993E-2</v>
-          </cell>
-          <cell r="F9">
-            <v>5.7540000000000001E-2</v>
-          </cell>
-          <cell r="G9">
-            <v>6.9379999999999997E-2</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="E10">
-            <v>6.2260000000000003E-2</v>
-          </cell>
-          <cell r="F10">
-            <v>5.2139999999999999E-2</v>
-          </cell>
-          <cell r="G10">
-            <v>6.5769999999999995E-2</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11">
-            <v>5.6509999999999998E-2</v>
-          </cell>
-          <cell r="F11">
-            <v>3.9399999999999998E-2</v>
-          </cell>
-          <cell r="G11">
-            <v>5.808E-2</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="E12">
-            <v>5.2470000000000003E-2</v>
-          </cell>
-          <cell r="F12">
-            <v>3.8490000000000003E-2</v>
-          </cell>
-          <cell r="G12">
-            <v>5.3900000000000003E-2</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="E13">
-            <v>5.3999999999999999E-2</v>
-          </cell>
-          <cell r="F13">
-            <v>3.678E-2</v>
-          </cell>
-          <cell r="G13">
-            <v>5.5100000000000003E-2</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="E14">
-            <v>6.1080000000000002E-2</v>
-          </cell>
-          <cell r="F14">
-            <v>3.1719999999999998E-2</v>
-          </cell>
-          <cell r="G14">
-            <v>6.164E-2</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="E15">
-            <v>6.404E-2</v>
-          </cell>
-          <cell r="F15">
-            <v>3.1949999999999999E-2</v>
-          </cell>
-          <cell r="G15">
-            <v>6.4899999999999999E-2</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16">
-            <v>7.0550000000000002E-2</v>
-          </cell>
-          <cell r="F16">
-            <v>3.3619999999999997E-2</v>
-          </cell>
-          <cell r="G16">
-            <v>7.1510000000000004E-2</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="E17">
-            <v>7.0150000000000004E-2</v>
-          </cell>
-          <cell r="F17">
-            <v>3.0929999999999999E-2</v>
-          </cell>
-          <cell r="G17">
-            <v>7.0870000000000002E-2</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="E18">
-            <v>6.5799999999999997E-2</v>
-          </cell>
-          <cell r="F18">
-            <v>3.2000000000000001E-2</v>
-          </cell>
-          <cell r="G18">
-            <v>6.6670000000000007E-2</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="E19">
-            <v>8.1129999999999994E-2</v>
-          </cell>
-          <cell r="F19">
-            <v>3.4660000000000003E-2</v>
-          </cell>
-          <cell r="G19">
-            <v>8.201E-2</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="E20">
-            <v>8.5709999999999995E-2</v>
-          </cell>
-          <cell r="F20">
-            <v>3.9399999999999998E-2</v>
-          </cell>
-          <cell r="G20">
-            <v>8.6609999999999993E-2</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21">
-            <v>8.7459999999999996E-2</v>
-          </cell>
-          <cell r="F21">
-            <v>4.2610000000000002E-2</v>
-          </cell>
-          <cell r="G21">
-            <v>8.8439999999999991E-2</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="E22">
-            <v>9.1249999999999998E-2</v>
-          </cell>
-          <cell r="F22">
-            <v>4.4650000000000002E-2</v>
-          </cell>
-          <cell r="G22">
-            <v>9.2499999999999999E-2</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2681,10 +4074,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2752,7 +4145,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -2819,8 +4212,12 @@
       <c r="V2">
         <v>0.11650000000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W2">
+        <f>MAX(J2,N2,R2,V2)</f>
+        <v>0.12695000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2887,8 +4284,12 @@
       <c r="V3">
         <v>0.13408999999999999</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3">
+        <f t="shared" ref="W3:W20" si="0">MAX(J3,N3,R3,V3)</f>
+        <v>0.14563000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -2955,8 +4356,12 @@
       <c r="V4">
         <v>0.12271</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W4">
+        <f>MAX(J4,N4,R4,V4)</f>
+        <v>0.13300999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3023,8 +4428,12 @@
       <c r="V5">
         <v>0.1105</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>0.11905</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -3091,8 +4500,12 @@
       <c r="V6">
         <v>9.2799999999999994E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>9.9919999999999995E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -3159,8 +4572,12 @@
       <c r="V7">
         <v>7.6239999999999988E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>8.2189999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -3227,8 +4644,12 @@
       <c r="V8">
         <v>7.5989999999999988E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>8.2290000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
@@ -3295,8 +4716,12 @@
       <c r="V9">
         <v>7.0319999999999994E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W9">
+        <f t="shared" si="0"/>
+        <v>7.5400000000000009E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -3363,8 +4788,12 @@
       <c r="V10">
         <v>6.5239999999999992E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W10">
+        <f t="shared" si="0"/>
+        <v>7.0730000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -3431,19 +4860,26 @@
       <c r="V11">
         <v>6.4069999999999988E-2</v>
       </c>
+      <c r="W11">
+        <f t="shared" si="0"/>
+        <v>6.9339999999999999E-2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="W2:W20">
+    <cfRule type="top10" dxfId="0" priority="1" percent="1" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3511,7 +4947,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -3578,8 +5014,12 @@
       <c r="V2">
         <v>8.165E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W2">
+        <f>MAX(J2,N2,R2,V2)</f>
+        <v>9.1069999999999998E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -3646,8 +5086,12 @@
       <c r="V3">
         <v>7.5370000000000006E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3">
+        <f t="shared" ref="W3:W20" si="0">MAX(J3,N3,R3,V3)</f>
+        <v>8.131999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -3714,8 +5158,12 @@
       <c r="V4">
         <v>8.3949999999999997E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W4">
+        <f>MAX(J4,N4,R4,V4)</f>
+        <v>9.3310000000000004E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -3782,8 +5230,12 @@
       <c r="V5">
         <v>7.3469999999999994E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>7.9489999999999991E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -3850,8 +5302,12 @@
       <c r="V6">
         <v>7.3709999999999998E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>8.1220000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -3918,8 +5374,12 @@
       <c r="V7">
         <v>6.4030000000000004E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>6.9379999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
@@ -3986,8 +5446,12 @@
       <c r="V8">
         <v>5.9549999999999999E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>6.5769999999999995E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>59</v>
       </c>
@@ -4054,8 +5518,12 @@
       <c r="V9">
         <v>4.9840000000000002E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W9">
+        <f t="shared" si="0"/>
+        <v>5.808E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -4122,8 +5590,12 @@
       <c r="V10">
         <v>4.725E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W10">
+        <f t="shared" si="0"/>
+        <v>5.3900000000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -4190,8 +5662,12 @@
       <c r="V11">
         <v>4.7210000000000002E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W11">
+        <f t="shared" si="0"/>
+        <v>5.5329999999999997E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -4258,8 +5734,12 @@
       <c r="V12">
         <v>5.2490000000000002E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W12">
+        <f t="shared" si="0"/>
+        <v>6.2729999999999994E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -4326,8 +5806,12 @@
       <c r="V13">
         <v>5.5049999999999988E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W13">
+        <f t="shared" si="0"/>
+        <v>6.5340000000000009E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -4394,8 +5878,12 @@
       <c r="V14">
         <v>6.0699999999999997E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W14">
+        <f t="shared" si="0"/>
+        <v>7.1859999999999993E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>65</v>
       </c>
@@ -4462,8 +5950,12 @@
       <c r="V15">
         <v>6.0290000000000003E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W15">
+        <f t="shared" si="0"/>
+        <v>7.1669999999999998E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -4530,8 +6022,12 @@
       <c r="V16">
         <v>5.6680000000000001E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16">
+        <f t="shared" si="0"/>
+        <v>6.7049999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -4598,8 +6094,12 @@
       <c r="V17">
         <v>6.9819999999999993E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W17">
+        <f t="shared" si="0"/>
+        <v>8.2750000000000004E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -4666,8 +6166,12 @@
       <c r="V18">
         <v>7.3880000000000001E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W18">
+        <f t="shared" si="0"/>
+        <v>8.7419999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -4734,8 +6238,12 @@
       <c r="V19">
         <v>7.5409999999999991E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W19">
+        <f t="shared" si="0"/>
+        <v>8.9230000000000004E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -4802,19 +6310,40 @@
       <c r="V20">
         <v>7.9010000000000011E-2</v>
       </c>
+      <c r="W20">
+        <f t="shared" si="0"/>
+        <v>9.2790000000000011E-2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="W2:W20">
+    <cfRule type="top10" dxfId="1" priority="1" percent="1" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="36.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4882,7 +6411,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -4949,8 +6478,12 @@
       <c r="V2">
         <v>6.8030000000000007E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W2">
+        <f>MAX(J2,N2,R2,V2)</f>
+        <v>6.8030000000000007E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -5017,8 +6550,12 @@
       <c r="V3">
         <v>6.5519999999999995E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3">
+        <f t="shared" ref="W3:W20" si="0">MAX(J3,N3,R3,V3)</f>
+        <v>6.5519999999999995E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>89</v>
       </c>
@@ -5085,8 +6622,12 @@
       <c r="V4">
         <v>6.4909999999999995E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W4">
+        <f t="shared" si="0"/>
+        <v>6.4909999999999995E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -5153,8 +6694,12 @@
       <c r="V5">
         <v>6.5619999999999998E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W5">
+        <f t="shared" si="0"/>
+        <v>6.5619999999999998E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -5221,8 +6766,12 @@
       <c r="V6">
         <v>6.1400000000000003E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W6">
+        <f t="shared" si="0"/>
+        <v>6.1400000000000003E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -5289,8 +6838,12 @@
       <c r="V7">
         <v>4.9689999999999998E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W7">
+        <f t="shared" si="0"/>
+        <v>4.9689999999999998E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -5357,8 +6910,12 @@
       <c r="V8">
         <v>4.7659999999999987E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W8">
+        <f t="shared" si="0"/>
+        <v>4.7659999999999987E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -5425,8 +6982,12 @@
       <c r="V9">
         <v>4.5439999999999987E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W9">
+        <f t="shared" si="0"/>
+        <v>4.5439999999999987E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -5493,8 +7054,12 @@
       <c r="V10">
         <v>4.5840000000000013E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W10">
+        <f t="shared" si="0"/>
+        <v>4.5840000000000013E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -5561,8 +7126,12 @@
       <c r="V11">
         <v>5.0500000000000003E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W11">
+        <f t="shared" si="0"/>
+        <v>5.0500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>97</v>
       </c>
@@ -5629,8 +7198,12 @@
       <c r="V12">
         <v>4.4150000000000002E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W12">
+        <f t="shared" si="0"/>
+        <v>4.4150000000000002E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>98</v>
       </c>
@@ -5697,8 +7270,12 @@
       <c r="V13">
         <v>4.4429999999999997E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W13">
+        <f t="shared" si="0"/>
+        <v>4.446E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -5765,8 +7342,12 @@
       <c r="V14">
         <v>4.2869999999999998E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W14">
+        <f t="shared" si="0"/>
+        <v>4.2869999999999998E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>100</v>
       </c>
@@ -5833,8 +7414,12 @@
       <c r="V15">
         <v>4.8920000000000012E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W15">
+        <f t="shared" si="0"/>
+        <v>4.8920000000000012E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -5901,8 +7486,12 @@
       <c r="V16">
         <v>5.2749999999999998E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16">
+        <f t="shared" si="0"/>
+        <v>5.2749999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>102</v>
       </c>
@@ -5969,8 +7558,12 @@
       <c r="V17">
         <v>5.9929999999999997E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W17">
+        <f t="shared" si="0"/>
+        <v>5.9929999999999997E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>103</v>
       </c>
@@ -6037,8 +7630,12 @@
       <c r="V18">
         <v>6.1069999999999999E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W18">
+        <f t="shared" si="0"/>
+        <v>6.1069999999999999E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -6105,8 +7702,12 @@
       <c r="V19">
         <v>6.5909999999999996E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W19">
+        <f t="shared" si="0"/>
+        <v>6.5909999999999996E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>105</v>
       </c>
@@ -6173,29 +7774,36 @@
       <c r="V20">
         <v>7.4189999999999992E-2</v>
       </c>
+      <c r="W20">
+        <f t="shared" si="0"/>
+        <v>7.4189999999999992E-2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="W2:W20">
+    <cfRule type="top10" dxfId="2" priority="1" percent="1" rank="10"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01DC68E7-4326-406B-BB2B-B8AE4EE2F45F}">
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>108</v>
       </c>
@@ -6215,7 +7823,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -6247,7 +7855,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0</v>
       </c>
@@ -6261,17 +7869,17 @@
         <v>0.22881801939514301</v>
       </c>
       <c r="E5">
-        <v>6.9769999999999999E-2</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="F5">
         <v>0.1265</v>
       </c>
       <c r="G5">
-        <v>0.12695000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
       <c r="H5">
         <f t="shared" ref="H5:J14" si="0">(E5-B5)/B5</f>
-        <v>-0.51755507035085357</v>
+        <v>-0.55240561421543277</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
@@ -6279,10 +7887,10 @@
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>-0.44519229588832504</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.44645967859169167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8.7266462599716502E-2</v>
       </c>
@@ -6296,17 +7904,17 @@
         <v>0.242018594909096</v>
       </c>
       <c r="E6">
-        <v>6.9930000000000006E-2</v>
+        <v>6.5129999999999993E-2</v>
       </c>
       <c r="F6">
         <v>0.14530999999999999</v>
       </c>
       <c r="G6">
-        <v>0.14552999999999999</v>
+        <v>0.14563000000000001</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>-0.52018552200002954</v>
+        <v>-0.55312002070444632</v>
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
@@ -6314,10 +7922,10 @@
       </c>
       <c r="J6">
         <f t="shared" si="0"/>
-        <v>-0.39868256794622681</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.39826937655472411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.174532925199433</v>
       </c>
@@ -6331,17 +7939,17 @@
         <v>0.19790102555998401</v>
       </c>
       <c r="E7">
-        <v>5.9639999999999999E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="F7">
         <v>0.13275000000000001</v>
       </c>
       <c r="G7">
-        <v>0.13299</v>
+        <v>0.13300999999999999</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>-0.51598106445055814</v>
+        <v>-0.5516088834824503</v>
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
@@ -6349,10 +7957,10 @@
       </c>
       <c r="J7">
         <f t="shared" si="0"/>
-        <v>-0.32799741879209926</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.32789635817382606</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.26179938779914902</v>
       </c>
@@ -6366,17 +7974,17 @@
         <v>0.201287478382664</v>
       </c>
       <c r="E8">
-        <v>6.4280000000000004E-2</v>
+        <v>6.012E-2</v>
       </c>
       <c r="F8">
         <v>0.11869</v>
       </c>
       <c r="G8">
-        <v>0.11885999999999999</v>
+        <v>0.11905</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>-0.46069723197752499</v>
+        <v>-0.49559921572011206</v>
       </c>
       <c r="I8">
         <f t="shared" si="0"/>
@@ -6384,10 +7992,10 @@
       </c>
       <c r="J8">
         <f t="shared" si="0"/>
-        <v>-0.40950127173813872</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.40855734814424877</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.34906585039886601</v>
       </c>
@@ -6401,17 +8009,17 @@
         <v>0.150365553159441</v>
       </c>
       <c r="E9">
-        <v>5.4140000000000001E-2</v>
+        <v>5.0380000000000001E-2</v>
       </c>
       <c r="F9">
         <v>9.9510000000000001E-2</v>
       </c>
       <c r="G9">
-        <v>9.955E-2</v>
+        <v>9.9919999999999995E-2</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>-0.48799207422154595</v>
+        <v>-0.52355080715333369</v>
       </c>
       <c r="I9">
         <f t="shared" si="0"/>
@@ -6419,10 +8027,10 @@
       </c>
       <c r="J9">
         <f t="shared" si="0"/>
-        <v>-0.33794677099720061</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.33548610103506066</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.43633231299858199</v>
       </c>
@@ -6436,17 +8044,17 @@
         <v>0.129943884511105</v>
       </c>
       <c r="E10">
-        <v>5.4609999999999999E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="F10">
         <v>8.181999999999999E-2</v>
       </c>
       <c r="G10">
-        <v>8.1939999999999999E-2</v>
+        <v>8.2189999999999999E-2</v>
       </c>
       <c r="H10">
         <f t="shared" si="0"/>
-        <v>-0.51737200141170658</v>
+        <v>-0.54671323846193787</v>
       </c>
       <c r="I10">
         <f t="shared" si="0"/>
@@ -6454,10 +8062,10 @@
       </c>
       <c r="J10">
         <f t="shared" si="0"/>
-        <v>-0.36942011308737344</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.36749620569503566</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.52359877559829904</v>
       </c>
@@ -6471,17 +8079,17 @@
         <v>0.13194455836051999</v>
       </c>
       <c r="E11">
-        <v>5.33E-2</v>
+        <v>5.0349999999999999E-2</v>
       </c>
       <c r="F11">
         <v>8.2019999999999996E-2</v>
       </c>
       <c r="G11">
-        <v>8.2170000000000007E-2</v>
+        <v>8.2290000000000002E-2</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>-0.49146951146930323</v>
+        <v>-0.51961519516846943</v>
       </c>
       <c r="I11">
         <f t="shared" si="0"/>
@@ -6489,10 +8097,10 @@
       </c>
       <c r="J11">
         <f t="shared" si="0"/>
-        <v>-0.37723843240672333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.37632895950771894</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.61086523819801497</v>
       </c>
@@ -6506,17 +8114,17 @@
         <v>0.12722112864763599</v>
       </c>
       <c r="E12">
-        <v>5.9360000000000003E-2</v>
+        <v>5.5879999999999999E-2</v>
       </c>
       <c r="F12">
         <v>7.3209999999999997E-2</v>
       </c>
       <c r="G12">
-        <v>7.5400000000000009E-2</v>
+        <v>7.3810000000000001E-2</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>-0.46254553638429735</v>
+        <v>-0.49405398539680828</v>
       </c>
       <c r="I12">
         <f t="shared" si="0"/>
@@ -6524,10 +8132,10 @@
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
-        <v>-0.40733115008879395</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.4198290741121205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.69813170079773201</v>
       </c>
@@ -6541,17 +8149,17 @@
         <v>0.112717366536148</v>
       </c>
       <c r="E13">
-        <v>5.9159999999999997E-2</v>
+        <v>5.5229999999999987E-2</v>
       </c>
       <c r="F13">
         <v>6.5680000000000002E-2</v>
       </c>
       <c r="G13">
-        <v>7.0730000000000001E-2</v>
+        <v>6.8659999999999999E-2</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>-0.42424750200043104</v>
+        <v>-0.46249475212109215</v>
       </c>
       <c r="I13">
         <f t="shared" si="0"/>
@@ -6559,10 +8167,10 @@
       </c>
       <c r="J13">
         <f t="shared" si="0"/>
-        <v>-0.37250130859544894</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.39086582564913797</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.78539816339744795</v>
       </c>
@@ -6576,17 +8184,17 @@
         <v>0.115269005057364</v>
       </c>
       <c r="E14">
-        <v>5.6919999999999998E-2</v>
+        <v>5.3159999999999999E-2</v>
       </c>
       <c r="F14">
         <v>6.5370000000000011E-2</v>
       </c>
       <c r="G14">
-        <v>6.9339999999999999E-2</v>
+        <v>6.7409999999999998E-2</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>-0.41472639219684254</v>
+        <v>-0.45338817654926478</v>
       </c>
       <c r="I14">
         <f t="shared" si="0"/>
@@ -6594,10 +8202,10 @@
       </c>
       <c r="J14">
         <f t="shared" si="0"/>
-        <v>-0.39845060720795916</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-0.41519405007050081</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.87266462599716499</v>
       </c>
@@ -6610,11 +8218,8 @@
       <c r="D15">
         <v>0.112717366536148</v>
       </c>
-      <c r="R15">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.95993108859688103</v>
       </c>
@@ -7506,6 +9111,27 @@
       <c r="D58">
         <v>0.13358617856798699</v>
       </c>
+      <c r="E58">
+        <v>6.7780000000000007E-2</v>
+      </c>
+      <c r="F58">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="G58">
+        <v>6.8030000000000007E-2</v>
+      </c>
+      <c r="H58">
+        <f>(E58-B58)/B58</f>
+        <v>-0.48616153432466946</v>
+      </c>
+      <c r="I58">
+        <f t="shared" ref="I58" si="3">(F58-C58)/C58</f>
+        <v>-0.27880510170029199</v>
+      </c>
+      <c r="J58">
+        <f t="shared" ref="J58" si="4">(G58-D58)/D58</f>
+        <v>-0.49074072835029858</v>
+      </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59">
@@ -7520,6 +9146,27 @@
       <c r="D59">
         <v>0.12966659916158399</v>
       </c>
+      <c r="E59">
+        <v>6.5129999999999993E-2</v>
+      </c>
+      <c r="F59">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="G59">
+        <v>6.5519999999999995E-2</v>
+      </c>
+      <c r="H59">
+        <f t="shared" ref="H59:H76" si="5">(E59-B59)/B59</f>
+        <v>-0.49505248998345736</v>
+      </c>
+      <c r="I59">
+        <f t="shared" ref="I59:I76" si="6">(F59-C59)/C59</f>
+        <v>-0.11909266435603688</v>
+      </c>
+      <c r="J59">
+        <f t="shared" ref="J59:J76" si="7">(G59-D59)/D59</f>
+        <v>-0.49470410712050628</v>
+      </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60">
@@ -7534,6 +9181,27 @@
       <c r="D60">
         <v>0.119775740231519</v>
       </c>
+      <c r="E60">
+        <v>6.470999999999999E-2</v>
+      </c>
+      <c r="F60">
+        <v>4.4790000000000003E-2</v>
+      </c>
+      <c r="G60">
+        <v>6.4909999999999995E-2</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="5"/>
+        <v>-0.45416303937291996</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="6"/>
+        <v>-0.22838858876211929</v>
+      </c>
+      <c r="J60">
+        <f t="shared" si="7"/>
+        <v>-0.45807055857444062</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61">
@@ -7548,6 +9216,27 @@
       <c r="D61">
         <v>0.12658099419575999</v>
       </c>
+      <c r="E61">
+        <v>6.5409999999999996E-2</v>
+      </c>
+      <c r="F61">
+        <v>4.6039999999999998E-2</v>
+      </c>
+      <c r="G61">
+        <v>6.5619999999999998E-2</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="5"/>
+        <v>-0.47865871332516041</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="6"/>
+        <v>-0.20394476893793317</v>
+      </c>
+      <c r="J61">
+        <f t="shared" si="7"/>
+        <v>-0.48159674035647582</v>
+      </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62">
@@ -7562,6 +9251,27 @@
       <c r="D62">
         <v>0.11101559533019099</v>
       </c>
+      <c r="E62">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="F62">
+        <v>4.6710000000000002E-2</v>
+      </c>
+      <c r="G62">
+        <v>6.1400000000000003E-2</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="5"/>
+        <v>-0.4456132489289974</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="6"/>
+        <v>-0.16235358486745941</v>
+      </c>
+      <c r="J62">
+        <f t="shared" si="7"/>
+        <v>-0.44692455310103529</v>
+      </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63">
@@ -7576,6 +9286,27 @@
       <c r="D63">
         <v>0.10498600694860399</v>
       </c>
+      <c r="E63">
+        <v>4.7229999999999987E-2</v>
+      </c>
+      <c r="F63">
+        <v>4.0329999999999998E-2</v>
+      </c>
+      <c r="G63">
+        <v>4.9689999999999998E-2</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="5"/>
+        <v>-0.54447429411970649</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="6"/>
+        <v>-0.24418228693862268</v>
+      </c>
+      <c r="J63">
+        <f t="shared" si="7"/>
+        <v>-0.52669882926087674</v>
+      </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64">
@@ -7590,8 +9321,29 @@
       <c r="D64">
         <v>9.6144885824918702E-2</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64">
+        <v>4.7479999999999987E-2</v>
+      </c>
+      <c r="F64">
+        <v>3.3520000000000001E-2</v>
+      </c>
+      <c r="G64">
+        <v>4.7659999999999987E-2</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="5"/>
+        <v>-0.50102580689685416</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="6"/>
+        <v>-0.24775539538323929</v>
+      </c>
+      <c r="J64">
+        <f t="shared" si="7"/>
+        <v>-0.50428980604553875</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>0.61086523800000003</v>
       </c>
@@ -7604,8 +9356,29 @@
       <c r="D65">
         <v>9.7416716702063103E-2</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65">
+        <v>4.5269999999999998E-2</v>
+      </c>
+      <c r="F65">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="G65">
+        <v>4.5439999999999987E-2</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="5"/>
+        <v>-0.5306947591604102</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="6"/>
+        <v>-0.28324308928011033</v>
+      </c>
+      <c r="J65">
+        <f t="shared" si="7"/>
+        <v>-0.53355028235069168</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>0.69813170099999999</v>
       </c>
@@ -7618,8 +9391,29 @@
       <c r="D66">
         <v>8.7891175624806597E-2</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66">
+        <v>4.5770000000000012E-2</v>
+      </c>
+      <c r="F66">
+        <v>2.512E-2</v>
+      </c>
+      <c r="G66">
+        <v>4.5840000000000013E-2</v>
+      </c>
+      <c r="H66">
+        <f t="shared" si="5"/>
+        <v>-0.47171506966213778</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="6"/>
+        <v>-0.39272729085996766</v>
+      </c>
+      <c r="J66">
+        <f t="shared" si="7"/>
+        <v>-0.478445934143791</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>0.78539816299999998</v>
       </c>
@@ -7632,8 +9426,29 @@
       <c r="D67">
         <v>8.5070690443153699E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67">
+        <v>5.042E-2</v>
+      </c>
+      <c r="F67">
+        <v>2.4170000000000001E-2</v>
+      </c>
+      <c r="G67">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="5"/>
+        <v>-0.39764760704143665</v>
+      </c>
+      <c r="I67">
+        <f t="shared" si="6"/>
+        <v>-0.37851376509510309</v>
+      </c>
+      <c r="J67">
+        <f t="shared" si="7"/>
+        <v>-0.40637604165508295</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>0.87266462600000005</v>
       </c>
@@ -7646,8 +9461,29 @@
       <c r="D68">
         <v>7.87923861843388E-2</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68">
+        <v>4.4089999999999997E-2</v>
+      </c>
+      <c r="F68">
+        <v>2.213E-2</v>
+      </c>
+      <c r="G68">
+        <v>4.4150000000000002E-2</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="5"/>
+        <v>-0.42947211616121833</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="6"/>
+        <v>-0.41259799479569975</v>
+      </c>
+      <c r="J68">
+        <f t="shared" si="7"/>
+        <v>-0.43966667164123158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>0.95993108900000002</v>
       </c>
@@ -7660,8 +9496,29 @@
       <c r="D69">
         <v>8.65759036183254E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69">
+        <v>4.4420000000000001E-2</v>
+      </c>
+      <c r="F69">
+        <v>2.0740000000000001E-2</v>
+      </c>
+      <c r="G69">
+        <v>4.4429999999999997E-2</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="5"/>
+        <v>-0.47743034589292843</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="6"/>
+        <v>-0.45012793951487917</v>
+      </c>
+      <c r="J69">
+        <f t="shared" si="7"/>
+        <v>-0.48680870608209786</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>1.047197551</v>
       </c>
@@ -7674,8 +9531,29 @@
       <c r="D70">
         <v>8.5811466447113696E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70">
+        <v>4.2840000000000003E-2</v>
+      </c>
+      <c r="F70">
+        <v>2.1080000000000002E-2</v>
+      </c>
+      <c r="G70">
+        <v>4.2869999999999998E-2</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="5"/>
+        <v>-0.49148352937985912</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="6"/>
+        <v>-0.39690259726556559</v>
+      </c>
+      <c r="J70">
+        <f t="shared" si="7"/>
+        <v>-0.50041641548660487</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>1.134464014</v>
       </c>
@@ -7688,8 +9566,29 @@
       <c r="D71">
         <v>8.9834381647751704E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71">
+        <v>4.888E-2</v>
+      </c>
+      <c r="F71">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="G71">
+        <v>4.8920000000000012E-2</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="5"/>
+        <v>-0.44771354071624797</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="6"/>
+        <v>-0.39366803767069075</v>
+      </c>
+      <c r="J71">
+        <f t="shared" si="7"/>
+        <v>-0.45544234732065597</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>1.2217304760000001</v>
       </c>
@@ -7702,8 +9601,29 @@
       <c r="D72">
         <v>8.7846676258970594E-2</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72">
+        <v>5.2690000000000001E-2</v>
+      </c>
+      <c r="F72">
+        <v>2.0570000000000001E-2</v>
+      </c>
+      <c r="G72">
+        <v>5.2749999999999998E-2</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="5"/>
+        <v>-0.38839273939902885</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="6"/>
+        <v>-0.4860751868812494</v>
+      </c>
+      <c r="J72">
+        <f t="shared" si="7"/>
+        <v>-0.39952195977803595</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>1.308996939</v>
       </c>
@@ -7716,8 +9636,29 @@
       <c r="D73">
         <v>0.100015712124532</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73">
+        <v>5.9859999999999997E-2</v>
+      </c>
+      <c r="F73">
+        <v>2.1350000000000001E-2</v>
+      </c>
+      <c r="G73">
+        <v>5.9929999999999997E-2</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="5"/>
+        <v>-0.39024749661903824</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="6"/>
+        <v>-0.46914928016059371</v>
+      </c>
+      <c r="J73">
+        <f t="shared" si="7"/>
+        <v>-0.40079414796967405</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1.396263402</v>
       </c>
@@ -7730,8 +9671,29 @@
       <c r="D74">
         <v>0.120565536929489</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74">
+        <v>6.1009999999999988E-2</v>
+      </c>
+      <c r="F74">
+        <v>2.2249999999999999E-2</v>
+      </c>
+      <c r="G74">
+        <v>6.1069999999999999E-2</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="5"/>
+        <v>-0.48679471713050182</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="6"/>
+        <v>-0.4981753768774958</v>
+      </c>
+      <c r="J74">
+        <f t="shared" si="7"/>
+        <v>-0.49347050943989162</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1.4835298640000001</v>
       </c>
@@ -7744,8 +9706,29 @@
       <c r="D75">
         <v>0.112551701534839</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75">
+        <v>6.583E-2</v>
+      </c>
+      <c r="F75">
+        <v>2.4410000000000001E-2</v>
+      </c>
+      <c r="G75">
+        <v>6.5909999999999996E-2</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="5"/>
+        <v>-0.40335889630440458</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="6"/>
+        <v>-0.47076481809989601</v>
+      </c>
+      <c r="J75">
+        <f t="shared" si="7"/>
+        <v>-0.4144024559273467</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1.570796327</v>
       </c>
@@ -7757,6 +9740,27 @@
       </c>
       <c r="D76">
         <v>0.13088670980851999</v>
+      </c>
+      <c r="E76">
+        <v>7.4090000000000003E-2</v>
+      </c>
+      <c r="F76">
+        <v>2.4840000000000001E-2</v>
+      </c>
+      <c r="G76">
+        <v>7.4189999999999992E-2</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="5"/>
+        <v>-0.42464144417005112</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="6"/>
+        <v>-0.45884641853537333</v>
+      </c>
+      <c r="J76">
+        <f t="shared" si="7"/>
+        <v>-0.43317392492686346</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/Timehistory_modal/响应统计结果.xlsx
+++ b/data/output/Timehistory_modal/响应统计结果.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyFiles\GitHub\corner-point-response\data\output\Timehistory_modal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098832C7-6727-4DCC-AC7A-99EF3CD1D53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88BB6B9-4F5C-40EE-A3C7-7D989AC9BE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-1_Acceleration" sheetId="1" r:id="rId1"/>
     <sheet name="2-1_Acceleration" sheetId="2" r:id="rId2"/>
     <sheet name="3-1_Acceleration" sheetId="3" r:id="rId3"/>
     <sheet name="结果对比" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -354,7 +355,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -375,6 +376,18 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -384,7 +397,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -407,19 +420,102 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -501,34 +597,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.13789000000000001</c:v>
+                  <c:v>6.4510000000000012E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.4549999999999996E-2</c:v>
+                  <c:v>6.4649999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.4309999999999997E-2</c:v>
+                  <c:v>5.4429999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.9229999999999998E-2</c:v>
+                  <c:v>5.9389999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.9919999999999999E-2</c:v>
+                  <c:v>5.0049999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.0889999999999998E-2</c:v>
+                  <c:v>5.1060000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.0110000000000002E-2</c:v>
+                  <c:v>5.0209999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.6300000000000003E-2</c:v>
+                  <c:v>5.6390000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.6120000000000003E-2</c:v>
+                  <c:v>5.62E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.4100000000000002E-2</c:v>
+                  <c:v>5.4200000000000012E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -536,7 +632,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4046-4B13-A066-87458D40734A}"/>
+              <c16:uniqueId val="{00000000-DA9B-408F-AC66-119D73929DD6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -562,34 +658,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>9.1329999999999995E-2</c:v>
+                  <c:v>0.12007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13819999999999999</c:v>
+                  <c:v>0.13833999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.12631000000000001</c:v>
+                  <c:v>0.12645000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11303000000000001</c:v>
+                  <c:v>0.11321000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.4790000000000013E-2</c:v>
+                  <c:v>9.5060000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.7719999999999997E-2</c:v>
+                  <c:v>7.7900000000000011E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.7930000000000013E-2</c:v>
+                  <c:v>7.8060000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.966E-2</c:v>
+                  <c:v>6.9739999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.2049999999999987E-2</c:v>
+                  <c:v>6.2109999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.1940000000000002E-2</c:v>
+                  <c:v>6.1969999999999997E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -597,7 +693,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4046-4B13-A066-87458D40734A}"/>
+              <c16:uniqueId val="{00000001-DA9B-408F-AC66-119D73929DD6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -634,34 +730,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.13567000000000001</c:v>
+                  <c:v>0.12665999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14563000000000001</c:v>
+                  <c:v>0.14582000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13300999999999999</c:v>
+                  <c:v>0.13320000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11905</c:v>
+                  <c:v>0.11928999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.9919999999999995E-2</c:v>
+                  <c:v>0.10031</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2189999999999999E-2</c:v>
+                  <c:v>8.2430000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2290000000000002E-2</c:v>
+                  <c:v>8.2450000000000009E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.3810000000000001E-2</c:v>
+                  <c:v>7.392E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.8659999999999999E-2</c:v>
+                  <c:v>6.8790000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.7409999999999998E-2</c:v>
+                  <c:v>6.7519999999999997E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -669,7 +765,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4046-4B13-A066-87458D40734A}"/>
+              <c16:uniqueId val="{00000002-DA9B-408F-AC66-119D73929DD6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -976,7 +1072,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C201-4335-9A1A-220297CF30D7}"/>
+              <c16:uniqueId val="{00000000-8CEF-413F-B521-6F5B40C574D2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1064,7 +1160,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C201-4335-9A1A-220297CF30D7}"/>
+              <c16:uniqueId val="{00000001-8CEF-413F-B521-6F5B40C574D2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1163,7 +1259,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C201-4335-9A1A-220297CF30D7}"/>
+              <c16:uniqueId val="{00000002-8CEF-413F-B521-6F5B40C574D2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1470,7 +1566,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1E59-4887-9575-E6B6E98B2DFE}"/>
+              <c16:uniqueId val="{00000000-0AAA-4CD4-A075-F19224C190C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1558,7 +1654,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1E59-4887-9575-E6B6E98B2DFE}"/>
+              <c16:uniqueId val="{00000001-0AAA-4CD4-A075-F19224C190C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1657,7 +1753,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1E59-4887-9575-E6B6E98B2DFE}"/>
+              <c16:uniqueId val="{00000002-0AAA-4CD4-A075-F19224C190C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1927,34 +2023,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.13569000000000001</c:v>
+                  <c:v>6.473000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.5129999999999993E-2</c:v>
+                  <c:v>6.5329999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.525E-2</c:v>
+                  <c:v>5.5469999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.012E-2</c:v>
+                  <c:v>6.0409999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.0380000000000001E-2</c:v>
+                  <c:v>5.0700000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.1290000000000002E-2</c:v>
+                  <c:v>5.1580000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.0360000000000002E-2</c:v>
+                  <c:v>5.0549999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.5879999999999999E-2</c:v>
+                  <c:v>5.6030000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.525E-2</c:v>
+                  <c:v>5.5390000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.3179999999999998E-2</c:v>
+                  <c:v>5.3330000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1962,7 +2058,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D4FB-43DB-9C5B-F40A78B88825}"/>
+              <c16:uniqueId val="{00000000-0DDA-4E0B-8F85-B3CAD1735300}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1999,34 +2095,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>9.8459999999999992E-2</c:v>
+                  <c:v>0.12651000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14532</c:v>
+                  <c:v>0.14549999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13277</c:v>
+                  <c:v>0.13295999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11871</c:v>
+                  <c:v>0.11895</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.9510000000000001E-2</c:v>
+                  <c:v>9.9890000000000007E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.181999999999999E-2</c:v>
+                  <c:v>8.2049999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2019999999999996E-2</c:v>
+                  <c:v>8.2180000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.3209999999999997E-2</c:v>
+                  <c:v>7.331E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.5709999999999991E-2</c:v>
+                  <c:v>6.5790000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.5370000000000011E-2</c:v>
+                  <c:v>6.5420000000000006E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2034,7 +2130,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D4FB-43DB-9C5B-F40A78B88825}"/>
+              <c16:uniqueId val="{00000001-0DDA-4E0B-8F85-B3CAD1735300}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2071,34 +2167,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.13567000000000001</c:v>
+                  <c:v>0.12665999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14563000000000001</c:v>
+                  <c:v>0.14582000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13300999999999999</c:v>
+                  <c:v>0.13320000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11905</c:v>
+                  <c:v>0.11928999999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.9919999999999995E-2</c:v>
+                  <c:v>0.10031</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2189999999999999E-2</c:v>
+                  <c:v>8.2430000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2290000000000002E-2</c:v>
+                  <c:v>8.2450000000000009E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.3810000000000001E-2</c:v>
+                  <c:v>7.392E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.8659999999999999E-2</c:v>
+                  <c:v>6.8790000000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.7409999999999998E-2</c:v>
+                  <c:v>6.7519999999999997E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2106,7 +2202,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D4FB-43DB-9C5B-F40A78B88825}"/>
+              <c16:uniqueId val="{00000002-0DDA-4E0B-8F85-B3CAD1735300}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2411,7 +2507,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D892-4964-BE18-599607682F80}"/>
+              <c16:uniqueId val="{00000000-3C41-4A18-B28E-8A38F84C9950}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2483,7 +2579,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D892-4964-BE18-599607682F80}"/>
+              <c16:uniqueId val="{00000001-3C41-4A18-B28E-8A38F84C9950}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2555,7 +2651,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D892-4964-BE18-599607682F80}"/>
+              <c16:uniqueId val="{00000002-3C41-4A18-B28E-8A38F84C9950}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2887,7 +2983,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E8C9-463F-8A71-90D42C1CB24F}"/>
+              <c16:uniqueId val="{00000000-1896-43E4-8125-328D2F6F43E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2986,7 +3082,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E8C9-463F-8A71-90D42C1CB24F}"/>
+              <c16:uniqueId val="{00000001-1896-43E4-8125-328D2F6F43E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3085,7 +3181,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E8C9-463F-8A71-90D42C1CB24F}"/>
+              <c16:uniqueId val="{00000002-1896-43E4-8125-328D2F6F43E6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3417,7 +3513,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3EC6-4748-8695-ACD3A2C4AFF4}"/>
+              <c16:uniqueId val="{00000000-43EB-499A-8BB3-9AA5460EC256}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3516,7 +3612,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3EC6-4748-8695-ACD3A2C4AFF4}"/>
+              <c16:uniqueId val="{00000001-43EB-499A-8BB3-9AA5460EC256}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3615,7 +3711,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3EC6-4748-8695-ACD3A2C4AFF4}"/>
+              <c16:uniqueId val="{00000002-43EB-499A-8BB3-9AA5460EC256}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3946,7 +4042,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8378-48A0-AAE3-26F3DB47E163}"/>
+              <c16:uniqueId val="{00000000-52CA-466C-AFD8-7A0DB49171DD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4045,7 +4141,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8378-48A0-AAE3-26F3DB47E163}"/>
+              <c16:uniqueId val="{00000001-52CA-466C-AFD8-7A0DB49171DD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4144,7 +4240,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8378-48A0-AAE3-26F3DB47E163}"/>
+              <c16:uniqueId val="{00000002-52CA-466C-AFD8-7A0DB49171DD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4476,7 +4572,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-54BC-46A8-94BD-CD0A2F90ED2A}"/>
+              <c16:uniqueId val="{00000000-9BFA-43C2-85EF-057440BD44D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4575,7 +4671,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-54BC-46A8-94BD-CD0A2F90ED2A}"/>
+              <c16:uniqueId val="{00000001-9BFA-43C2-85EF-057440BD44D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4674,7 +4770,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-54BC-46A8-94BD-CD0A2F90ED2A}"/>
+              <c16:uniqueId val="{00000002-9BFA-43C2-85EF-057440BD44D7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5488,55 +5584,55 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5548,49 +5644,49 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.13789000000000001</v>
+        <v>6.4510000000000012E-2</v>
       </c>
       <c r="D2">
-        <v>9.1329999999999995E-2</v>
+        <v>0.12007</v>
       </c>
       <c r="E2">
-        <v>0.13786000000000001</v>
+        <v>0.12007</v>
       </c>
       <c r="F2">
-        <v>0.14449999999999999</v>
+        <v>6.9769999999999999E-2</v>
       </c>
       <c r="G2">
-        <v>9.8459999999999992E-2</v>
+        <v>0.12651000000000001</v>
       </c>
       <c r="H2">
-        <v>0.14510000000000001</v>
+        <v>0.12695000000000001</v>
       </c>
       <c r="I2">
-        <v>0.14449999999999999</v>
+        <v>6.9769999999999999E-2</v>
       </c>
       <c r="J2">
-        <v>8.9560000000000001E-2</v>
+        <v>0.11637</v>
       </c>
       <c r="K2">
-        <v>0.14459</v>
+        <v>0.1164</v>
       </c>
       <c r="L2">
-        <v>0.13569000000000001</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="M2">
-        <v>9.8459999999999992E-2</v>
+        <v>0.12651000000000001</v>
       </c>
       <c r="N2">
-        <v>0.13567000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
       <c r="O2">
-        <v>0.13569000000000001</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="P2">
-        <v>8.9560000000000001E-2</v>
+        <v>0.11637</v>
       </c>
       <c r="Q2">
-        <v>0.13583000000000001</v>
+        <v>0.11650000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -5601,49 +5697,49 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>6.4549999999999996E-2</v>
+        <v>6.4649999999999999E-2</v>
       </c>
       <c r="D3">
-        <v>0.13819999999999999</v>
+        <v>0.13833999999999999</v>
       </c>
       <c r="E3">
-        <v>0.13821</v>
+        <v>0.13835</v>
       </c>
       <c r="F3">
-        <v>6.9930000000000006E-2</v>
+        <v>7.0080000000000003E-2</v>
       </c>
       <c r="G3">
-        <v>0.14532</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="H3">
-        <v>0.14552999999999999</v>
+        <v>0.14571999999999999</v>
       </c>
       <c r="I3">
-        <v>6.9930000000000006E-2</v>
+        <v>7.0080000000000003E-2</v>
       </c>
       <c r="J3">
-        <v>0.13381999999999999</v>
+        <v>0.13400999999999999</v>
       </c>
       <c r="K3">
-        <v>0.13381000000000001</v>
+        <v>0.13400999999999999</v>
       </c>
       <c r="L3">
-        <v>6.5129999999999993E-2</v>
+        <v>6.5329999999999999E-2</v>
       </c>
       <c r="M3">
-        <v>0.14532</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="N3">
-        <v>0.14563000000000001</v>
+        <v>0.14582000000000001</v>
       </c>
       <c r="O3">
-        <v>6.5129999999999993E-2</v>
+        <v>6.5329999999999999E-2</v>
       </c>
       <c r="P3">
-        <v>0.13381999999999999</v>
+        <v>0.13400999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.13408999999999999</v>
+        <v>0.13428000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -5654,49 +5750,49 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>5.4309999999999997E-2</v>
+        <v>5.4429999999999999E-2</v>
       </c>
       <c r="D4">
-        <v>0.12631000000000001</v>
+        <v>0.12645000000000001</v>
       </c>
       <c r="E4">
-        <v>0.1263</v>
+        <v>0.12645000000000001</v>
       </c>
       <c r="F4">
-        <v>5.9639999999999999E-2</v>
+        <v>5.9830000000000001E-2</v>
       </c>
       <c r="G4">
-        <v>0.13277</v>
+        <v>0.13295999999999999</v>
       </c>
       <c r="H4">
-        <v>0.13299</v>
+        <v>0.13317999999999999</v>
       </c>
       <c r="I4">
-        <v>5.9639999999999999E-2</v>
+        <v>5.9830000000000001E-2</v>
       </c>
       <c r="J4">
-        <v>0.12255000000000001</v>
+        <v>0.12275</v>
       </c>
       <c r="K4">
-        <v>0.12254</v>
+        <v>0.12274</v>
       </c>
       <c r="L4">
-        <v>5.525E-2</v>
+        <v>5.5469999999999998E-2</v>
       </c>
       <c r="M4">
-        <v>0.13277</v>
+        <v>0.13295999999999999</v>
       </c>
       <c r="N4">
-        <v>0.13300999999999999</v>
+        <v>0.13320000000000001</v>
       </c>
       <c r="O4">
-        <v>5.525E-2</v>
+        <v>5.5469999999999998E-2</v>
       </c>
       <c r="P4">
-        <v>0.12255000000000001</v>
+        <v>0.12275</v>
       </c>
       <c r="Q4">
-        <v>0.12271</v>
+        <v>0.12291000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -5707,49 +5803,49 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>5.9229999999999998E-2</v>
+        <v>5.9389999999999998E-2</v>
       </c>
       <c r="D5">
-        <v>0.11303000000000001</v>
+        <v>0.11321000000000001</v>
       </c>
       <c r="E5">
-        <v>0.11305</v>
+        <v>0.11323</v>
       </c>
       <c r="F5">
-        <v>6.4280000000000004E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="G5">
-        <v>0.11871</v>
+        <v>0.11895</v>
       </c>
       <c r="H5">
-        <v>0.11885999999999999</v>
+        <v>0.11909</v>
       </c>
       <c r="I5">
-        <v>6.4280000000000004E-2</v>
+        <v>6.4500000000000002E-2</v>
       </c>
       <c r="J5">
-        <v>0.11024</v>
+        <v>0.11049</v>
       </c>
       <c r="K5">
-        <v>0.11024</v>
+        <v>0.1105</v>
       </c>
       <c r="L5">
-        <v>6.012E-2</v>
+        <v>6.0409999999999998E-2</v>
       </c>
       <c r="M5">
-        <v>0.11871</v>
+        <v>0.11895</v>
       </c>
       <c r="N5">
-        <v>0.11905</v>
+        <v>0.11928999999999999</v>
       </c>
       <c r="O5">
-        <v>6.012E-2</v>
+        <v>6.0409999999999998E-2</v>
       </c>
       <c r="P5">
-        <v>0.11024</v>
+        <v>0.11049</v>
       </c>
       <c r="Q5">
-        <v>0.1105</v>
+        <v>0.11075</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -5760,49 +5856,49 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>4.9919999999999999E-2</v>
+        <v>5.0049999999999997E-2</v>
       </c>
       <c r="D6">
-        <v>9.4790000000000013E-2</v>
+        <v>9.5060000000000006E-2</v>
       </c>
       <c r="E6">
-        <v>9.4879999999999992E-2</v>
+        <v>9.5150000000000012E-2</v>
       </c>
       <c r="F6">
-        <v>5.4140000000000001E-2</v>
+        <v>5.4369999999999988E-2</v>
       </c>
       <c r="G6">
-        <v>9.9510000000000001E-2</v>
+        <v>9.9890000000000007E-2</v>
       </c>
       <c r="H6">
-        <v>9.955E-2</v>
+        <v>9.9930000000000005E-2</v>
       </c>
       <c r="I6">
-        <v>5.4140000000000001E-2</v>
+        <v>5.4369999999999988E-2</v>
       </c>
       <c r="J6">
-        <v>9.2450000000000004E-2</v>
+        <v>9.2769999999999991E-2</v>
       </c>
       <c r="K6">
-        <v>9.2499999999999999E-2</v>
+        <v>9.282E-2</v>
       </c>
       <c r="L6">
-        <v>5.0380000000000001E-2</v>
+        <v>5.0700000000000002E-2</v>
       </c>
       <c r="M6">
-        <v>9.9510000000000001E-2</v>
+        <v>9.9890000000000007E-2</v>
       </c>
       <c r="N6">
-        <v>9.9919999999999995E-2</v>
+        <v>0.10031</v>
       </c>
       <c r="O6">
-        <v>5.0380000000000001E-2</v>
+        <v>5.0700000000000002E-2</v>
       </c>
       <c r="P6">
-        <v>9.2450000000000004E-2</v>
+        <v>9.2769999999999991E-2</v>
       </c>
       <c r="Q6">
-        <v>9.2799999999999994E-2</v>
+        <v>9.3120000000000008E-2</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -5813,49 +5909,49 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>5.0889999999999998E-2</v>
+        <v>5.1060000000000001E-2</v>
       </c>
       <c r="D7">
-        <v>7.7719999999999997E-2</v>
+        <v>7.7900000000000011E-2</v>
       </c>
       <c r="E7">
-        <v>7.7790000000000012E-2</v>
+        <v>7.7969999999999998E-2</v>
       </c>
       <c r="F7">
-        <v>5.4609999999999999E-2</v>
+        <v>5.4829999999999997E-2</v>
       </c>
       <c r="G7">
-        <v>8.181999999999999E-2</v>
+        <v>8.2049999999999998E-2</v>
       </c>
       <c r="H7">
-        <v>8.1939999999999999E-2</v>
+        <v>8.2170000000000007E-2</v>
       </c>
       <c r="I7">
-        <v>5.4609999999999999E-2</v>
+        <v>5.4829999999999997E-2</v>
       </c>
       <c r="J7">
-        <v>7.5870000000000007E-2</v>
+        <v>7.6109999999999997E-2</v>
       </c>
       <c r="K7">
-        <v>7.5950000000000004E-2</v>
+        <v>7.6200000000000004E-2</v>
       </c>
       <c r="L7">
-        <v>5.1290000000000002E-2</v>
+        <v>5.1580000000000001E-2</v>
       </c>
       <c r="M7">
-        <v>8.181999999999999E-2</v>
+        <v>8.2049999999999998E-2</v>
       </c>
       <c r="N7">
-        <v>8.2189999999999999E-2</v>
+        <v>8.2430000000000003E-2</v>
       </c>
       <c r="O7">
-        <v>5.1290000000000002E-2</v>
+        <v>5.1580000000000001E-2</v>
       </c>
       <c r="P7">
-        <v>7.5870000000000007E-2</v>
+        <v>7.6109999999999997E-2</v>
       </c>
       <c r="Q7">
-        <v>7.6239999999999988E-2</v>
+        <v>7.6469999999999996E-2</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -5866,49 +5962,49 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>5.0110000000000002E-2</v>
+        <v>5.0209999999999998E-2</v>
       </c>
       <c r="D8">
-        <v>7.7930000000000013E-2</v>
+        <v>7.8060000000000004E-2</v>
       </c>
       <c r="E8">
-        <v>7.7959999999999988E-2</v>
+        <v>7.8090000000000007E-2</v>
       </c>
       <c r="F8">
-        <v>5.3310000000000003E-2</v>
+        <v>5.348E-2</v>
       </c>
       <c r="G8">
-        <v>8.2019999999999996E-2</v>
+        <v>8.2180000000000003E-2</v>
       </c>
       <c r="H8">
-        <v>8.2170000000000007E-2</v>
+        <v>8.233E-2</v>
       </c>
       <c r="I8">
-        <v>5.3310000000000003E-2</v>
+        <v>5.348E-2</v>
       </c>
       <c r="J8">
-        <v>7.5700000000000003E-2</v>
+        <v>7.5900000000000009E-2</v>
       </c>
       <c r="K8">
-        <v>7.571E-2</v>
+        <v>7.5909999999999991E-2</v>
       </c>
       <c r="L8">
-        <v>5.0360000000000002E-2</v>
+        <v>5.0549999999999998E-2</v>
       </c>
       <c r="M8">
-        <v>8.2019999999999996E-2</v>
+        <v>8.2180000000000003E-2</v>
       </c>
       <c r="N8">
-        <v>8.2290000000000002E-2</v>
+        <v>8.2450000000000009E-2</v>
       </c>
       <c r="O8">
-        <v>5.0360000000000002E-2</v>
+        <v>5.0549999999999998E-2</v>
       </c>
       <c r="P8">
-        <v>7.5700000000000003E-2</v>
+        <v>7.5900000000000009E-2</v>
       </c>
       <c r="Q8">
-        <v>7.5989999999999988E-2</v>
+        <v>7.6189999999999994E-2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -5919,49 +6015,49 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>5.6300000000000003E-2</v>
+        <v>5.6390000000000003E-2</v>
       </c>
       <c r="D9">
-        <v>6.966E-2</v>
+        <v>6.9739999999999996E-2</v>
       </c>
       <c r="E9">
-        <v>7.1650000000000005E-2</v>
+        <v>7.1749999999999994E-2</v>
       </c>
       <c r="F9">
-        <v>5.9360000000000003E-2</v>
+        <v>5.9490000000000001E-2</v>
       </c>
       <c r="G9">
-        <v>7.3209999999999997E-2</v>
+        <v>7.331E-2</v>
       </c>
       <c r="H9">
-        <v>7.5400000000000009E-2</v>
+        <v>7.553E-2</v>
       </c>
       <c r="I9">
-        <v>5.9360000000000003E-2</v>
+        <v>5.9490000000000001E-2</v>
       </c>
       <c r="J9">
-        <v>6.7849999999999994E-2</v>
+        <v>6.8010000000000001E-2</v>
       </c>
       <c r="K9">
-        <v>7.2120000000000004E-2</v>
+        <v>7.2279999999999997E-2</v>
       </c>
       <c r="L9">
-        <v>5.5879999999999999E-2</v>
+        <v>5.6030000000000003E-2</v>
       </c>
       <c r="M9">
-        <v>7.3209999999999997E-2</v>
+        <v>7.331E-2</v>
       </c>
       <c r="N9">
-        <v>7.3810000000000001E-2</v>
+        <v>7.392E-2</v>
       </c>
       <c r="O9">
-        <v>5.5879999999999999E-2</v>
+        <v>5.6030000000000003E-2</v>
       </c>
       <c r="P9">
-        <v>6.7849999999999994E-2</v>
+        <v>6.8010000000000001E-2</v>
       </c>
       <c r="Q9">
-        <v>7.0319999999999994E-2</v>
+        <v>7.0489999999999997E-2</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5972,49 +6068,49 @@
         <v>40</v>
       </c>
       <c r="C10">
-        <v>5.6120000000000003E-2</v>
+        <v>5.62E-2</v>
       </c>
       <c r="D10">
-        <v>6.2049999999999987E-2</v>
+        <v>6.2109999999999999E-2</v>
       </c>
       <c r="E10">
-        <v>6.6909999999999997E-2</v>
+        <v>6.6989999999999994E-2</v>
       </c>
       <c r="F10">
-        <v>5.919E-2</v>
+        <v>5.9290000000000002E-2</v>
       </c>
       <c r="G10">
-        <v>6.5709999999999991E-2</v>
+        <v>6.5790000000000001E-2</v>
       </c>
       <c r="H10">
-        <v>7.0730000000000001E-2</v>
+        <v>7.0830000000000004E-2</v>
       </c>
       <c r="I10">
-        <v>5.919E-2</v>
+        <v>5.9290000000000002E-2</v>
       </c>
       <c r="J10">
-        <v>6.0010000000000001E-2</v>
+        <v>6.012E-2</v>
       </c>
       <c r="K10">
-        <v>6.7420000000000008E-2</v>
+        <v>6.7530000000000007E-2</v>
       </c>
       <c r="L10">
-        <v>5.525E-2</v>
+        <v>5.5390000000000002E-2</v>
       </c>
       <c r="M10">
-        <v>6.5709999999999991E-2</v>
+        <v>6.5790000000000001E-2</v>
       </c>
       <c r="N10">
-        <v>6.8659999999999999E-2</v>
+        <v>6.8790000000000004E-2</v>
       </c>
       <c r="O10">
-        <v>5.525E-2</v>
+        <v>5.5390000000000002E-2</v>
       </c>
       <c r="P10">
-        <v>6.0010000000000001E-2</v>
+        <v>6.012E-2</v>
       </c>
       <c r="Q10">
-        <v>6.5239999999999992E-2</v>
+        <v>6.5379999999999994E-2</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -6025,170 +6121,170 @@
         <v>45</v>
       </c>
       <c r="C11">
-        <v>5.4100000000000002E-2</v>
+        <v>5.4200000000000012E-2</v>
       </c>
       <c r="D11">
-        <v>6.1940000000000002E-2</v>
+        <v>6.1969999999999997E-2</v>
       </c>
       <c r="E11">
-        <v>6.5790000000000001E-2</v>
+        <v>6.5849999999999992E-2</v>
       </c>
       <c r="F11">
-        <v>5.6939999999999998E-2</v>
+        <v>5.7020000000000001E-2</v>
       </c>
       <c r="G11">
-        <v>6.5370000000000011E-2</v>
+        <v>6.5420000000000006E-2</v>
       </c>
       <c r="H11">
-        <v>6.9339999999999999E-2</v>
+        <v>6.9419999999999996E-2</v>
       </c>
       <c r="I11">
-        <v>5.6939999999999998E-2</v>
+        <v>5.7020000000000001E-2</v>
       </c>
       <c r="J11">
-        <v>5.9889999999999999E-2</v>
+        <v>5.9950000000000003E-2</v>
       </c>
       <c r="K11">
-        <v>6.6099999999999992E-2</v>
+        <v>6.6180000000000003E-2</v>
       </c>
       <c r="L11">
-        <v>5.3179999999999998E-2</v>
+        <v>5.3330000000000002E-2</v>
       </c>
       <c r="M11">
-        <v>6.5370000000000011E-2</v>
+        <v>6.5420000000000006E-2</v>
       </c>
       <c r="N11">
-        <v>6.7409999999999998E-2</v>
+        <v>6.7519999999999997E-2</v>
       </c>
       <c r="O11">
-        <v>5.3179999999999998E-2</v>
+        <v>5.3330000000000002E-2</v>
       </c>
       <c r="P11">
-        <v>5.9889999999999999E-2</v>
+        <v>5.9950000000000003E-2</v>
       </c>
       <c r="Q11">
-        <v>6.4069999999999988E-2</v>
+        <v>6.4189999999999997E-2</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>0.13569000000000001</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="B14">
-        <v>9.8459999999999992E-2</v>
+        <v>0.12651000000000001</v>
       </c>
       <c r="C14">
-        <v>0.13567000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>6.5129999999999993E-2</v>
+        <v>6.5329999999999999E-2</v>
       </c>
       <c r="B15">
-        <v>0.14532</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="C15">
-        <v>0.14563000000000001</v>
+        <v>0.14582000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>5.525E-2</v>
+        <v>5.5469999999999998E-2</v>
       </c>
       <c r="B16">
-        <v>0.13277</v>
+        <v>0.13295999999999999</v>
       </c>
       <c r="C16">
-        <v>0.13300999999999999</v>
+        <v>0.13320000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>6.012E-2</v>
+        <v>6.0409999999999998E-2</v>
       </c>
       <c r="B17">
-        <v>0.11871</v>
+        <v>0.11895</v>
       </c>
       <c r="C17">
-        <v>0.11905</v>
+        <v>0.11928999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>5.0380000000000001E-2</v>
+        <v>5.0700000000000002E-2</v>
       </c>
       <c r="B18">
-        <v>9.9510000000000001E-2</v>
+        <v>9.9890000000000007E-2</v>
       </c>
       <c r="C18">
-        <v>9.9919999999999995E-2</v>
+        <v>0.10031</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>5.1290000000000002E-2</v>
+        <v>5.1580000000000001E-2</v>
       </c>
       <c r="B19">
-        <v>8.181999999999999E-2</v>
+        <v>8.2049999999999998E-2</v>
       </c>
       <c r="C19">
-        <v>8.2189999999999999E-2</v>
+        <v>8.2430000000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>5.0360000000000002E-2</v>
+        <v>5.0549999999999998E-2</v>
       </c>
       <c r="B20">
-        <v>8.2019999999999996E-2</v>
+        <v>8.2180000000000003E-2</v>
       </c>
       <c r="C20">
-        <v>8.2290000000000002E-2</v>
+        <v>8.2450000000000009E-2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>5.5879999999999999E-2</v>
+        <v>5.6030000000000003E-2</v>
       </c>
       <c r="B21">
-        <v>7.3209999999999997E-2</v>
+        <v>7.331E-2</v>
       </c>
       <c r="C21">
-        <v>7.3810000000000001E-2</v>
+        <v>7.392E-2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>5.525E-2</v>
+        <v>5.5390000000000002E-2</v>
       </c>
       <c r="B22">
-        <v>6.5709999999999991E-2</v>
+        <v>6.5790000000000001E-2</v>
       </c>
       <c r="C22">
-        <v>6.8659999999999999E-2</v>
+        <v>6.8790000000000004E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>5.3179999999999998E-2</v>
+        <v>5.3330000000000002E-2</v>
       </c>
       <c r="B23">
-        <v>6.5370000000000011E-2</v>
+        <v>6.5420000000000006E-2</v>
       </c>
       <c r="C23">
-        <v>6.7409999999999998E-2</v>
+        <v>6.7519999999999997E-2</v>
       </c>
     </row>
   </sheetData>
@@ -8801,21 +8897,21 @@
       <c r="A3" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="2" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -8864,27 +8960,27 @@
       </c>
       <c r="E5">
         <f>'1-1_Acceleration'!A14</f>
-        <v>0.13569000000000001</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="F5">
         <f>'1-1_Acceleration'!B14</f>
-        <v>9.8459999999999992E-2</v>
+        <v>0.12651000000000001</v>
       </c>
       <c r="G5">
         <f>'1-1_Acceleration'!C14</f>
-        <v>0.13567000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
       <c r="H5">
         <f t="shared" ref="H5:H14" si="0">(E5-B5)/B5</f>
-        <v>-6.1732083931594094E-2</v>
+        <v>-0.55240561421543277</v>
       </c>
       <c r="I5">
         <f t="shared" ref="I5:I14" si="1">(F5-C5)/C5</f>
-        <v>-0.5608960768764909</v>
+        <v>-0.43580096166610655</v>
       </c>
       <c r="J5">
         <f t="shared" ref="J5:J14" si="2">(G5-D5)/D5</f>
-        <v>-0.40708340908364754</v>
+        <v>-0.44645967859169167</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -8902,27 +8998,27 @@
       </c>
       <c r="E6">
         <f>'1-1_Acceleration'!A15</f>
-        <v>6.5129999999999993E-2</v>
+        <v>6.5329999999999999E-2</v>
       </c>
       <c r="F6">
         <f>'1-1_Acceleration'!B15</f>
-        <v>0.14532</v>
+        <v>0.14549999999999999</v>
       </c>
       <c r="G6">
         <f>'1-1_Acceleration'!C15</f>
-        <v>0.14563000000000001</v>
+        <v>0.14582000000000001</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>-0.55312002070444632</v>
+        <v>-0.55174774992509557</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>-0.39174982893112537</v>
+        <v>-0.39099642244342653</v>
       </c>
       <c r="J6">
         <f t="shared" si="2"/>
-        <v>-0.39826937655472411</v>
+        <v>-0.39748431291086911</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -8940,27 +9036,27 @@
       </c>
       <c r="E7">
         <f>'1-1_Acceleration'!A16</f>
-        <v>5.525E-2</v>
+        <v>5.5469999999999998E-2</v>
       </c>
       <c r="F7">
         <f>'1-1_Acceleration'!B16</f>
-        <v>0.13277</v>
+        <v>0.13295999999999999</v>
       </c>
       <c r="G7">
         <f>'1-1_Acceleration'!C16</f>
-        <v>0.13300999999999999</v>
+        <v>0.13320000000000001</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>-0.5516088834824503</v>
+        <v>-0.54982343469269712</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>-0.32104468259334068</v>
+        <v>-0.32007306618671821</v>
       </c>
       <c r="J7">
         <f t="shared" si="2"/>
-        <v>-0.32789635817382606</v>
+        <v>-0.32693628230023014</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -8978,27 +9074,27 @@
       </c>
       <c r="E8">
         <f>'1-1_Acceleration'!A17</f>
-        <v>6.012E-2</v>
+        <v>6.0409999999999998E-2</v>
       </c>
       <c r="F8">
         <f>'1-1_Acceleration'!B17</f>
-        <v>0.11871</v>
+        <v>0.11895</v>
       </c>
       <c r="G8">
         <f>'1-1_Acceleration'!C17</f>
-        <v>0.11905</v>
+        <v>0.11928999999999999</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>-0.49559921572011206</v>
+        <v>-0.49316614473805676</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>-0.40635021358722734</v>
+        <v>-0.40515001184568017</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
-        <v>-0.40855734814424877</v>
+        <v>-0.40736502360459836</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -9016,27 +9112,27 @@
       </c>
       <c r="E9">
         <f>'1-1_Acceleration'!A18</f>
-        <v>5.0380000000000001E-2</v>
+        <v>5.0700000000000002E-2</v>
       </c>
       <c r="F9">
         <f>'1-1_Acceleration'!B18</f>
-        <v>9.9510000000000001E-2</v>
+        <v>9.9890000000000007E-2</v>
       </c>
       <c r="G9">
         <f>'1-1_Acceleration'!C18</f>
-        <v>9.9919999999999995E-2</v>
+        <v>0.10031</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>-0.52355080715333369</v>
+        <v>-0.52052453201020277</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>-0.32411583874699396</v>
+        <v>-0.32153483200117799</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
-        <v>-0.33548610103506066</v>
+        <v>-0.33289242188577794</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -9054,27 +9150,27 @@
       </c>
       <c r="E10">
         <f>'1-1_Acceleration'!A19</f>
-        <v>5.1290000000000002E-2</v>
+        <v>5.1580000000000001E-2</v>
       </c>
       <c r="F10">
         <f>'1-1_Acceleration'!B19</f>
-        <v>8.181999999999999E-2</v>
+        <v>8.2049999999999998E-2</v>
       </c>
       <c r="G10">
         <f>'1-1_Acceleration'!C19</f>
-        <v>8.2189999999999999E-2</v>
+        <v>8.2430000000000003E-2</v>
       </c>
       <c r="H10">
         <f t="shared" si="0"/>
-        <v>-0.54671323846193787</v>
+        <v>-0.54415029908104418</v>
       </c>
       <c r="I10">
         <f t="shared" si="1"/>
-        <v>-0.29788889742406832</v>
+        <v>-0.29591522896168171</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>-0.36749620569503566</v>
+        <v>-0.36564925459839137</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -9092,27 +9188,27 @@
       </c>
       <c r="E11">
         <f>'1-1_Acceleration'!A20</f>
-        <v>5.0360000000000002E-2</v>
+        <v>5.0549999999999998E-2</v>
       </c>
       <c r="F11">
         <f>'1-1_Acceleration'!B20</f>
-        <v>8.2019999999999996E-2</v>
+        <v>8.2180000000000003E-2</v>
       </c>
       <c r="G11">
         <f>'1-1_Acceleration'!C20</f>
-        <v>8.2290000000000002E-2</v>
+        <v>8.2450000000000009E-2</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>-0.51951978607118399</v>
+        <v>-0.51770701322276325</v>
       </c>
       <c r="I11">
         <f t="shared" si="1"/>
-        <v>-0.3559203243975701</v>
+        <v>-0.3546638900145368</v>
       </c>
       <c r="J11">
         <f t="shared" si="2"/>
-        <v>-0.37632895950771894</v>
+        <v>-0.37511632897571301</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -9130,27 +9226,27 @@
       </c>
       <c r="E12">
         <f>'1-1_Acceleration'!A21</f>
-        <v>5.5879999999999999E-2</v>
+        <v>5.6030000000000003E-2</v>
       </c>
       <c r="F12">
         <f>'1-1_Acceleration'!B21</f>
-        <v>7.3209999999999997E-2</v>
+        <v>7.331E-2</v>
       </c>
       <c r="G12">
         <f>'1-1_Acceleration'!C21</f>
-        <v>7.3810000000000001E-2</v>
+        <v>7.392E-2</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>-0.49405398539680828</v>
+        <v>-0.49269586259454484</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>-0.36014033234976117</v>
+        <v>-0.35926632652043422</v>
       </c>
       <c r="J12">
         <f t="shared" si="2"/>
-        <v>-0.4198290741121205</v>
+        <v>-0.41896443785893439</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -9168,27 +9264,27 @@
       </c>
       <c r="E13">
         <f>'1-1_Acceleration'!A22</f>
-        <v>5.525E-2</v>
+        <v>5.5390000000000002E-2</v>
       </c>
       <c r="F13">
         <f>'1-1_Acceleration'!B22</f>
-        <v>6.5709999999999991E-2</v>
+        <v>6.5790000000000001E-2</v>
       </c>
       <c r="G13">
         <f>'1-1_Acceleration'!C22</f>
-        <v>6.8659999999999999E-2</v>
+        <v>6.8790000000000004E-2</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>-0.46230010962683932</v>
+        <v>-0.46093761216707019</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
-        <v>-0.31839213700615338</v>
+        <v>-0.31756229940092562</v>
       </c>
       <c r="J13">
         <f t="shared" si="2"/>
-        <v>-0.39086582564913797</v>
+        <v>-0.38971249849117678</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -9206,27 +9302,27 @@
       </c>
       <c r="E14">
         <f>'1-1_Acceleration'!A23</f>
-        <v>5.3179999999999998E-2</v>
+        <v>5.3330000000000002E-2</v>
       </c>
       <c r="F14">
         <f>'1-1_Acceleration'!B23</f>
-        <v>6.5370000000000011E-2</v>
+        <v>6.5420000000000006E-2</v>
       </c>
       <c r="G14">
         <f>'1-1_Acceleration'!C23</f>
-        <v>6.7409999999999998E-2</v>
+        <v>6.7519999999999997E-2</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>-0.45318252876015613</v>
+        <v>-0.4516401703418414</v>
       </c>
       <c r="I14">
         <f t="shared" si="1"/>
-        <v>-0.38512082330941139</v>
+        <v>-0.38465051645864612</v>
       </c>
       <c r="J14">
         <f t="shared" si="2"/>
-        <v>-0.41519405007050081</v>
+        <v>-0.41423976058092593</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -10911,4 +11007,126 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2BE2EBB-C63A-42A7-952E-6BF06D186903}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="10.21875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="5"/>
+    <col min="4" max="4" width="10.21875" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="8">
+        <v>200</v>
+      </c>
+      <c r="B1" s="6">
+        <v>5409.0518000000002</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6">
+        <v>6.0679999999999996</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>196.15</v>
+      </c>
+      <c r="B2" s="7">
+        <v>5409.0518000000002</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7">
+        <v>5.3490000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>192.3</v>
+      </c>
+      <c r="B3" s="7">
+        <v>7617676.6408393905</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7">
+        <v>4.8150000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>188.7</v>
+      </c>
+      <c r="B4" s="7">
+        <v>5632.2224999999999</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7">
+        <v>1.9630000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>185.1</v>
+      </c>
+      <c r="B5" s="7">
+        <v>5632.2224999999999</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7">
+        <v>1.5589999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>23.1</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>19.5</v>
+      </c>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/output/Timehistory_modal/响应统计结果.xlsx
+++ b/data/output/Timehistory_modal/响应统计结果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyFiles\GitHub\corner-point-response\data\output\Timehistory_modal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95E3FB23-E6E2-436D-B54D-7CC79D6DF9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E6E7DAA-84C6-43DD-9ADC-9528CD81454F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-1_Acceleration" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,50 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="3">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="3">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+    <bk>
+      <rc t="1" v="1"/>
+    </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="128">
   <si>
     <t>folder</t>
   </si>
@@ -354,6 +396,15 @@
     <t>3-1模型</t>
   </si>
   <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
     <t>质量</t>
   </si>
   <si>
@@ -372,23 +423,77 @@
     <t>偏差</t>
   </si>
   <si>
-    <t>1-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>….</t>
   </si>
   <si>
-    <t>2-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>Building</t>
   </si>
   <si>
-    <t>3-1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>1D principal axes response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2D vectorial response </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (%)</t>
+  </si>
+  <si>
+    <t>(º)</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>Corner</t>
+  </si>
+  <si>
+    <t>Acce</t>
+  </si>
+  <si>
+    <r>
+      <t>(m/s</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10.5"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFEE0000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>5/85</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>B31</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="180" formatCode="0.000_ "/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,22 +509,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -437,6 +530,25 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFEE0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10.5"/>
+      <color rgb="FFEE0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -467,27 +579,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -511,21 +608,6 @@
       <top/>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,14 +651,74 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -585,24 +727,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -615,51 +782,53 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FFFF7C80"/>
-    </mruColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -735,34 +904,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.12019000000000001</c:v>
+                  <c:v>6.4510000000000012E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13833999999999999</c:v>
+                  <c:v>6.4549999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.12645000000000001</c:v>
+                  <c:v>5.4309999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11321000000000001</c:v>
+                  <c:v>5.9229999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.5060000000000006E-2</c:v>
+                  <c:v>4.9919999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.7900000000000011E-2</c:v>
+                  <c:v>5.0889999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7.8060000000000004E-2</c:v>
+                  <c:v>5.0110000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.9739999999999996E-2</c:v>
+                  <c:v>5.6300000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.2109999999999999E-2</c:v>
+                  <c:v>5.6120000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.1969999999999997E-2</c:v>
+                  <c:v>5.4100000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -770,7 +939,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B79F-4EF3-B2D6-73F37D4B66A1}"/>
+              <c16:uniqueId val="{00000000-D1AD-4487-931A-E0226CE245AA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -796,34 +965,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.4579999999999999E-2</c:v>
+                  <c:v>0.12007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.4649999999999999E-2</c:v>
+                  <c:v>0.13819999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.4429999999999999E-2</c:v>
+                  <c:v>0.12631000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.9389999999999998E-2</c:v>
+                  <c:v>0.11303000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.0049999999999997E-2</c:v>
+                  <c:v>9.4790000000000013E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.1060000000000001E-2</c:v>
+                  <c:v>7.7719999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.0209999999999998E-2</c:v>
+                  <c:v>7.7930000000000013E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.6390000000000003E-2</c:v>
+                  <c:v>6.966E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.62E-2</c:v>
+                  <c:v>6.2049999999999987E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.4200000000000012E-2</c:v>
+                  <c:v>6.1940000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -831,7 +1000,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B79F-4EF3-B2D6-73F37D4B66A1}"/>
+              <c16:uniqueId val="{00000001-D1AD-4487-931A-E0226CE245AA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -868,34 +1037,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.12684000000000001</c:v>
+                  <c:v>0.12665999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14582000000000001</c:v>
+                  <c:v>0.14563000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13320000000000001</c:v>
+                  <c:v>0.13300999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11928999999999999</c:v>
+                  <c:v>0.11905</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.10031</c:v>
+                  <c:v>9.9919999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2430000000000003E-2</c:v>
+                  <c:v>8.2189999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2450000000000009E-2</c:v>
+                  <c:v>8.2290000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.392E-2</c:v>
+                  <c:v>7.3810000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.8790000000000004E-2</c:v>
+                  <c:v>6.8659999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.7519999999999997E-2</c:v>
+                  <c:v>6.7409999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -903,7 +1072,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-B79F-4EF3-B2D6-73F37D4B66A1}"/>
+              <c16:uniqueId val="{00000002-D1AD-4487-931A-E0226CE245AA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1235,7 +1404,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F7D0-49DF-BAA9-25183FAF9116}"/>
+              <c16:uniqueId val="{00000000-9586-4991-919F-19A7B8B888F8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1334,7 +1503,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F7D0-49DF-BAA9-25183FAF9116}"/>
+              <c16:uniqueId val="{00000001-9586-4991-919F-19A7B8B888F8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1433,7 +1602,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F7D0-49DF-BAA9-25183FAF9116}"/>
+              <c16:uniqueId val="{00000002-9586-4991-919F-19A7B8B888F8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1764,7 +1933,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5456-4036-85D6-9F7B4AF4E9C6}"/>
+              <c16:uniqueId val="{00000000-2FEB-45E7-8688-B8271091D2B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1863,7 +2032,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-5456-4036-85D6-9F7B4AF4E9C6}"/>
+              <c16:uniqueId val="{00000001-2FEB-45E7-8688-B8271091D2B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1962,7 +2131,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5456-4036-85D6-9F7B4AF4E9C6}"/>
+              <c16:uniqueId val="{00000002-2FEB-45E7-8688-B8271091D2B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2294,7 +2463,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E060-472E-9DDE-EC54F05FEDF9}"/>
+              <c16:uniqueId val="{00000000-8763-4E5E-BB9C-A8B4E92C6C08}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2393,7 +2562,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E060-472E-9DDE-EC54F05FEDF9}"/>
+              <c16:uniqueId val="{00000001-8763-4E5E-BB9C-A8B4E92C6C08}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2492,7 +2661,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E060-472E-9DDE-EC54F05FEDF9}"/>
+              <c16:uniqueId val="{00000002-8763-4E5E-BB9C-A8B4E92C6C08}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2737,34 +2906,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>-0.4908546199936929</c:v>
+                  <c:v>-5.2029054160745297E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.5566451789877932</c:v>
+                  <c:v>-5.1019707477854968E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.59136636636636641</c:v>
+                  <c:v>-5.0372152469739001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.50213764774918268</c:v>
+                  <c:v>-5.0566988660226776E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.50104675505931617</c:v>
+                  <c:v>-5.134107285828645E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.38056532815722433</c:v>
+                  <c:v>-5.4386178367197981E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.391024863553669</c:v>
+                  <c:v>-5.2983351561550478E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.23714826839826836</c:v>
+                  <c:v>-5.6225443706814808E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.18302078790521883</c:v>
+                  <c:v>-9.6271482668220387E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.19727488151658745</c:v>
+                  <c:v>-8.1145230677940897E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2772,7 +2941,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CE73-49B9-9E42-097BF66D78A3}"/>
+              <c16:uniqueId val="{00000000-88E3-4F45-A373-B92E71AC977F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3017,61 +3186,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>5.9330000000000001E-2</c:v>
+                  <c:v>8.0399999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.0400000000000002E-2</c:v>
+                  <c:v>6.8069999999999992E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.0840000000000012E-2</c:v>
+                  <c:v>8.3290000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.8270000000000002E-2</c:v>
+                  <c:v>6.7720000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.4710000000000002E-2</c:v>
+                  <c:v>7.2819999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4.9709999999999997E-2</c:v>
+                  <c:v>5.9909999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.4650000000000002E-2</c:v>
+                  <c:v>5.7419999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.3939999999999998E-2</c:v>
+                  <c:v>5.2159999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.3250000000000002E-2</c:v>
+                  <c:v>4.8460000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.177E-2</c:v>
+                  <c:v>4.9889999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.7689999999999999E-2</c:v>
+                  <c:v>5.6550000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.699E-2</c:v>
+                  <c:v>5.917E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.8320000000000001E-2</c:v>
+                  <c:v>6.522E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.6579999999999999E-2</c:v>
+                  <c:v>6.4890000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.7050000000000001E-2</c:v>
+                  <c:v>6.0859999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.9239999999999999E-2</c:v>
+                  <c:v>7.51E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3.3660000000000002E-2</c:v>
+                  <c:v>7.9430000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.6679999999999997E-2</c:v>
+                  <c:v>8.1009999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.7580000000000002E-2</c:v>
+                  <c:v>8.4610000000000005E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3079,7 +3248,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-43DB-4CAE-8252-57A2408B4775}"/>
+              <c16:uniqueId val="{00000000-4AAF-4972-B18A-1F7267D939E2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3105,61 +3274,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>8.0399999999999999E-2</c:v>
+                  <c:v>5.9330000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.8069999999999992E-2</c:v>
+                  <c:v>6.0400000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.3290000000000003E-2</c:v>
+                  <c:v>6.0840000000000012E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.7720000000000002E-2</c:v>
+                  <c:v>5.8270000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2819999999999996E-2</c:v>
+                  <c:v>5.4710000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.9909999999999998E-2</c:v>
+                  <c:v>4.9709999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.7419999999999999E-2</c:v>
+                  <c:v>4.4650000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.2159999999999998E-2</c:v>
+                  <c:v>3.3939999999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.8460000000000003E-2</c:v>
+                  <c:v>3.3250000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.9889999999999997E-2</c:v>
+                  <c:v>3.177E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.6550000000000003E-2</c:v>
+                  <c:v>2.7689999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5.917E-2</c:v>
+                  <c:v>2.699E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6.522E-2</c:v>
+                  <c:v>2.8320000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.4890000000000003E-2</c:v>
+                  <c:v>2.6579999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>6.0859999999999997E-2</c:v>
+                  <c:v>2.7050000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.51E-2</c:v>
+                  <c:v>2.9239999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.9430000000000001E-2</c:v>
+                  <c:v>3.3660000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8.1009999999999999E-2</c:v>
+                  <c:v>3.6679999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.4610000000000005E-2</c:v>
+                  <c:v>3.7580000000000002E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3167,7 +3336,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-43DB-4CAE-8252-57A2408B4775}"/>
+              <c16:uniqueId val="{00000001-4AAF-4972-B18A-1F7267D939E2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3266,7 +3435,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-43DB-4CAE-8252-57A2408B4775}"/>
+              <c16:uniqueId val="{00000002-4AAF-4972-B18A-1F7267D939E2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3511,61 +3680,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>-0.34852311408806408</c:v>
+                  <c:v>-0.11716262215877896</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.25725528775209039</c:v>
+                  <c:v>-0.16293654697491392</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.3479798521058835</c:v>
+                  <c:v>-0.10738398885435646</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.26695181783872174</c:v>
+                  <c:v>-0.14806893948924379</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.32639743905442009</c:v>
+                  <c:v>-0.10342280226545192</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.28351109829922166</c:v>
+                  <c:v>-0.13649466705102334</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-0.32111905123916673</c:v>
+                  <c:v>-0.12695757944351524</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-0.41563360881542705</c:v>
+                  <c:v>-0.10192837465564741</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-0.38311688311688313</c:v>
+                  <c:v>-0.10092764378478664</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.42341197822141563</c:v>
+                  <c:v>-9.4555353901996472E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.55077871512005194</c:v>
+                  <c:v>-8.2576249188838366E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.58412942989214178</c:v>
+                  <c:v>-8.8289676425269636E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.60397147252132577</c:v>
+                  <c:v>-8.7959725912459846E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.62494708621419504</c:v>
+                  <c:v>-8.4379850430365444E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.5942702864856757</c:v>
+                  <c:v>-8.7145642717864236E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-0.64345811486404092</c:v>
+                  <c:v>-8.4258017314961589E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-0.61136127467959811</c:v>
+                  <c:v>-8.2900357926336363E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-0.58525554047942108</c:v>
+                  <c:v>-8.4011759384893636E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.5937297297297297</c:v>
+                  <c:v>-8.5297297297297237E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3573,7 +3742,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0FC7-4809-8FBE-158E2121375D}"/>
+              <c16:uniqueId val="{00000000-1E3B-4E16-B5D4-7EC1B0D41516}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3880,7 +4049,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3159-4E91-93E1-873717DDE571}"/>
+              <c16:uniqueId val="{00000000-D42D-4009-A908-52B553274F12}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3968,7 +4137,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-3159-4E91-93E1-873717DDE571}"/>
+              <c16:uniqueId val="{00000001-D42D-4009-A908-52B553274F12}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4067,7 +4236,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-3159-4E91-93E1-873717DDE571}"/>
+              <c16:uniqueId val="{00000002-D42D-4009-A908-52B553274F12}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4374,7 +4543,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-940C-4AA4-B62F-15DD836CB7D1}"/>
+              <c16:uniqueId val="{00000000-AA01-451C-9F92-B2323DB85676}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4644,34 +4813,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.12667999999999999</c:v>
+                  <c:v>6.473000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14549999999999999</c:v>
+                  <c:v>6.5129999999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13295999999999999</c:v>
+                  <c:v>5.525E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11895</c:v>
+                  <c:v>6.012E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.9890000000000007E-2</c:v>
+                  <c:v>5.0380000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2049999999999998E-2</c:v>
+                  <c:v>5.1290000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2180000000000003E-2</c:v>
+                  <c:v>5.0360000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.331E-2</c:v>
+                  <c:v>5.5879999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.5790000000000001E-2</c:v>
+                  <c:v>5.525E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.5420000000000006E-2</c:v>
+                  <c:v>5.3179999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4679,7 +4848,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-82C2-4E56-A84E-ADDCA3CC675F}"/>
+              <c16:uniqueId val="{00000000-5C60-42C5-B9FB-95409A9CF92B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4716,34 +4885,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>6.4920000000000005E-2</c:v>
+                  <c:v>0.12651000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.5329999999999999E-2</c:v>
+                  <c:v>0.14532</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.5469999999999998E-2</c:v>
+                  <c:v>0.13277</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.0409999999999998E-2</c:v>
+                  <c:v>0.11871</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.0700000000000002E-2</c:v>
+                  <c:v>9.9510000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.1580000000000001E-2</c:v>
+                  <c:v>8.181999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.0549999999999998E-2</c:v>
+                  <c:v>8.2019999999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.6030000000000003E-2</c:v>
+                  <c:v>7.3209999999999997E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.5390000000000002E-2</c:v>
+                  <c:v>6.5709999999999991E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5.3330000000000002E-2</c:v>
+                  <c:v>6.5370000000000011E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4751,7 +4920,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-82C2-4E56-A84E-ADDCA3CC675F}"/>
+              <c16:uniqueId val="{00000001-5C60-42C5-B9FB-95409A9CF92B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4788,34 +4957,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>0.12684000000000001</c:v>
+                  <c:v>0.12665999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.14582000000000001</c:v>
+                  <c:v>0.14563000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.13320000000000001</c:v>
+                  <c:v>0.13300999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11928999999999999</c:v>
+                  <c:v>0.11905</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.10031</c:v>
+                  <c:v>9.9919999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.2430000000000003E-2</c:v>
+                  <c:v>8.2189999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.2450000000000009E-2</c:v>
+                  <c:v>8.2290000000000002E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.392E-2</c:v>
+                  <c:v>7.3810000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.8790000000000004E-2</c:v>
+                  <c:v>6.8659999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.7519999999999997E-2</c:v>
+                  <c:v>6.7409999999999998E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4823,7 +4992,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-82C2-4E56-A84E-ADDCA3CC675F}"/>
+              <c16:uniqueId val="{00000002-5C60-42C5-B9FB-95409A9CF92B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5128,7 +5297,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1F87-433F-B4FB-A1C0A78F5124}"/>
+              <c16:uniqueId val="{00000000-EED5-49BE-AAC5-ED199C2610FC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5200,7 +5369,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1F87-433F-B4FB-A1C0A78F5124}"/>
+              <c16:uniqueId val="{00000001-EED5-49BE-AAC5-ED199C2610FC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5272,7 +5441,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1F87-433F-B4FB-A1C0A78F5124}"/>
+              <c16:uniqueId val="{00000002-EED5-49BE-AAC5-ED199C2610FC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5604,7 +5773,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-34F2-4FD0-AE49-D8D305A00248}"/>
+              <c16:uniqueId val="{00000000-F836-4B80-BB8A-C4219DD100CD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5703,7 +5872,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-34F2-4FD0-AE49-D8D305A00248}"/>
+              <c16:uniqueId val="{00000001-F836-4B80-BB8A-C4219DD100CD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5802,7 +5971,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-34F2-4FD0-AE49-D8D305A00248}"/>
+              <c16:uniqueId val="{00000002-F836-4B80-BB8A-C4219DD100CD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6432,7 +6601,365 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE41E05A-A54B-22BD-20B7-85ED72E63B3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4876800" y="14638020"/>
+          <a:ext cx="746760" cy="281940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{033362E2-6060-EB52-F422-686CB3FC1472}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1828800" y="14836140"/>
+          <a:ext cx="106680" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="图片 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D4992DA-CE03-D05D-545C-64292635CA06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="3048000" y="14836140"/>
+          <a:ext cx="106680" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="图片 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5503E0B5-7A99-2C9C-475F-0A67EE2083D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4267200" y="14836140"/>
+          <a:ext cx="106680" cy="182880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>1</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+  <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6724,55 +7251,55 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="17" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6784,49 +7311,49 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.12019000000000001</v>
+        <v>6.4510000000000012E-2</v>
       </c>
       <c r="D2">
-        <v>6.4579999999999999E-2</v>
+        <v>0.12007</v>
       </c>
       <c r="E2">
-        <v>0.12019000000000001</v>
+        <v>0.12007</v>
       </c>
       <c r="F2">
-        <v>6.9900000000000004E-2</v>
+        <v>6.9769999999999999E-2</v>
       </c>
       <c r="G2">
-        <v>0.12667999999999999</v>
+        <v>0.12651000000000001</v>
       </c>
       <c r="H2">
-        <v>0.12712999999999999</v>
+        <v>0.12695000000000001</v>
       </c>
       <c r="I2">
-        <v>6.9900000000000004E-2</v>
+        <v>6.9769999999999999E-2</v>
       </c>
       <c r="J2">
-        <v>0.11654</v>
+        <v>0.11637</v>
       </c>
       <c r="K2">
-        <v>0.11656999999999999</v>
+        <v>0.1164</v>
       </c>
       <c r="L2">
-        <v>6.4920000000000005E-2</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="M2">
-        <v>0.12667999999999999</v>
+        <v>0.12651000000000001</v>
       </c>
       <c r="N2">
-        <v>0.12684000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
       <c r="O2">
-        <v>6.4920000000000005E-2</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="P2">
-        <v>0.11654</v>
+        <v>0.11637</v>
       </c>
       <c r="Q2">
-        <v>0.11667</v>
+        <v>0.11650000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -6837,49 +7364,49 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>0.13833999999999999</v>
+        <v>6.4549999999999996E-2</v>
       </c>
       <c r="D3">
-        <v>6.4649999999999999E-2</v>
+        <v>0.13819999999999999</v>
       </c>
       <c r="E3">
-        <v>0.13835</v>
+        <v>0.13821</v>
       </c>
       <c r="F3">
-        <v>7.0080000000000003E-2</v>
+        <v>6.9930000000000006E-2</v>
       </c>
       <c r="G3">
-        <v>0.14549999999999999</v>
+        <v>0.14532</v>
       </c>
       <c r="H3">
-        <v>0.14571999999999999</v>
+        <v>0.14552999999999999</v>
       </c>
       <c r="I3">
-        <v>7.0080000000000003E-2</v>
+        <v>6.9930000000000006E-2</v>
       </c>
       <c r="J3">
-        <v>0.13400999999999999</v>
+        <v>0.13381999999999999</v>
       </c>
       <c r="K3">
-        <v>0.13400999999999999</v>
+        <v>0.13381000000000001</v>
       </c>
       <c r="L3">
-        <v>6.5329999999999999E-2</v>
+        <v>6.5129999999999993E-2</v>
       </c>
       <c r="M3">
-        <v>0.14549999999999999</v>
+        <v>0.14532</v>
       </c>
       <c r="N3">
-        <v>0.14582000000000001</v>
+        <v>0.14563000000000001</v>
       </c>
       <c r="O3">
-        <v>6.5329999999999999E-2</v>
+        <v>6.5129999999999993E-2</v>
       </c>
       <c r="P3">
-        <v>0.13400999999999999</v>
+        <v>0.13381999999999999</v>
       </c>
       <c r="Q3">
-        <v>0.13428000000000001</v>
+        <v>0.13408999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
@@ -6890,49 +7417,49 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>0.12645000000000001</v>
+        <v>5.4309999999999997E-2</v>
       </c>
       <c r="D4">
-        <v>5.4429999999999999E-2</v>
+        <v>0.12631000000000001</v>
       </c>
       <c r="E4">
-        <v>0.12645000000000001</v>
+        <v>0.1263</v>
       </c>
       <c r="F4">
-        <v>5.9830000000000001E-2</v>
+        <v>5.9639999999999999E-2</v>
       </c>
       <c r="G4">
-        <v>0.13295999999999999</v>
+        <v>0.13277</v>
       </c>
       <c r="H4">
-        <v>0.13317999999999999</v>
+        <v>0.13299</v>
       </c>
       <c r="I4">
-        <v>5.9830000000000001E-2</v>
+        <v>5.9639999999999999E-2</v>
       </c>
       <c r="J4">
-        <v>0.12275</v>
+        <v>0.12255000000000001</v>
       </c>
       <c r="K4">
-        <v>0.12274</v>
+        <v>0.12254</v>
       </c>
       <c r="L4">
-        <v>5.5469999999999998E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="M4">
-        <v>0.13295999999999999</v>
+        <v>0.13277</v>
       </c>
       <c r="N4">
-        <v>0.13320000000000001</v>
+        <v>0.13300999999999999</v>
       </c>
       <c r="O4">
-        <v>5.5469999999999998E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="P4">
-        <v>0.12275</v>
+        <v>0.12255000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.12291000000000001</v>
+        <v>0.12271</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -6943,49 +7470,49 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>0.11321000000000001</v>
+        <v>5.9229999999999998E-2</v>
       </c>
       <c r="D5">
-        <v>5.9389999999999998E-2</v>
+        <v>0.11303000000000001</v>
       </c>
       <c r="E5">
-        <v>0.11323</v>
+        <v>0.11305</v>
       </c>
       <c r="F5">
-        <v>6.4500000000000002E-2</v>
+        <v>6.4280000000000004E-2</v>
       </c>
       <c r="G5">
-        <v>0.11895</v>
+        <v>0.11871</v>
       </c>
       <c r="H5">
-        <v>0.11909</v>
+        <v>0.11885999999999999</v>
       </c>
       <c r="I5">
-        <v>6.4500000000000002E-2</v>
+        <v>6.4280000000000004E-2</v>
       </c>
       <c r="J5">
-        <v>0.11049</v>
+        <v>0.11024</v>
       </c>
       <c r="K5">
+        <v>0.11024</v>
+      </c>
+      <c r="L5">
+        <v>6.012E-2</v>
+      </c>
+      <c r="M5">
+        <v>0.11871</v>
+      </c>
+      <c r="N5">
+        <v>0.11905</v>
+      </c>
+      <c r="O5">
+        <v>6.012E-2</v>
+      </c>
+      <c r="P5">
+        <v>0.11024</v>
+      </c>
+      <c r="Q5">
         <v>0.1105</v>
-      </c>
-      <c r="L5">
-        <v>6.0409999999999998E-2</v>
-      </c>
-      <c r="M5">
-        <v>0.11895</v>
-      </c>
-      <c r="N5">
-        <v>0.11928999999999999</v>
-      </c>
-      <c r="O5">
-        <v>6.0409999999999998E-2</v>
-      </c>
-      <c r="P5">
-        <v>0.11049</v>
-      </c>
-      <c r="Q5">
-        <v>0.11075</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -6996,49 +7523,49 @@
         <v>20</v>
       </c>
       <c r="C6">
-        <v>9.5060000000000006E-2</v>
+        <v>4.9919999999999999E-2</v>
       </c>
       <c r="D6">
-        <v>5.0049999999999997E-2</v>
+        <v>9.4790000000000013E-2</v>
       </c>
       <c r="E6">
-        <v>9.5150000000000012E-2</v>
+        <v>9.4879999999999992E-2</v>
       </c>
       <c r="F6">
-        <v>5.4369999999999988E-2</v>
+        <v>5.4140000000000001E-2</v>
       </c>
       <c r="G6">
-        <v>9.9890000000000007E-2</v>
+        <v>9.9510000000000001E-2</v>
       </c>
       <c r="H6">
-        <v>9.9930000000000005E-2</v>
+        <v>9.955E-2</v>
       </c>
       <c r="I6">
-        <v>5.4369999999999988E-2</v>
+        <v>5.4140000000000001E-2</v>
       </c>
       <c r="J6">
-        <v>9.2769999999999991E-2</v>
+        <v>9.2450000000000004E-2</v>
       </c>
       <c r="K6">
-        <v>9.282E-2</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="L6">
-        <v>5.0700000000000002E-2</v>
+        <v>5.0380000000000001E-2</v>
       </c>
       <c r="M6">
-        <v>9.9890000000000007E-2</v>
+        <v>9.9510000000000001E-2</v>
       </c>
       <c r="N6">
-        <v>0.10031</v>
+        <v>9.9919999999999995E-2</v>
       </c>
       <c r="O6">
-        <v>5.0700000000000002E-2</v>
+        <v>5.0380000000000001E-2</v>
       </c>
       <c r="P6">
-        <v>9.2769999999999991E-2</v>
+        <v>9.2450000000000004E-2</v>
       </c>
       <c r="Q6">
-        <v>9.3120000000000008E-2</v>
+        <v>9.2799999999999994E-2</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -7049,49 +7576,49 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>7.7900000000000011E-2</v>
+        <v>5.0889999999999998E-2</v>
       </c>
       <c r="D7">
-        <v>5.1060000000000001E-2</v>
+        <v>7.7719999999999997E-2</v>
       </c>
       <c r="E7">
-        <v>7.7969999999999998E-2</v>
+        <v>7.7790000000000012E-2</v>
       </c>
       <c r="F7">
-        <v>5.4829999999999997E-2</v>
+        <v>5.4609999999999999E-2</v>
       </c>
       <c r="G7">
-        <v>8.2049999999999998E-2</v>
+        <v>8.181999999999999E-2</v>
       </c>
       <c r="H7">
-        <v>8.2170000000000007E-2</v>
+        <v>8.1939999999999999E-2</v>
       </c>
       <c r="I7">
-        <v>5.4829999999999997E-2</v>
+        <v>5.4609999999999999E-2</v>
       </c>
       <c r="J7">
-        <v>7.6109999999999997E-2</v>
+        <v>7.5870000000000007E-2</v>
       </c>
       <c r="K7">
-        <v>7.6200000000000004E-2</v>
+        <v>7.5950000000000004E-2</v>
       </c>
       <c r="L7">
-        <v>5.1580000000000001E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="M7">
-        <v>8.2049999999999998E-2</v>
+        <v>8.181999999999999E-2</v>
       </c>
       <c r="N7">
-        <v>8.2430000000000003E-2</v>
+        <v>8.2189999999999999E-2</v>
       </c>
       <c r="O7">
-        <v>5.1580000000000001E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="P7">
-        <v>7.6109999999999997E-2</v>
+        <v>7.5870000000000007E-2</v>
       </c>
       <c r="Q7">
-        <v>7.6469999999999996E-2</v>
+        <v>7.6239999999999988E-2</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -7102,49 +7629,49 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>7.8060000000000004E-2</v>
+        <v>5.0110000000000002E-2</v>
       </c>
       <c r="D8">
-        <v>5.0209999999999998E-2</v>
+        <v>7.7930000000000013E-2</v>
       </c>
       <c r="E8">
-        <v>7.8090000000000007E-2</v>
+        <v>7.7959999999999988E-2</v>
       </c>
       <c r="F8">
-        <v>5.348E-2</v>
+        <v>5.3310000000000003E-2</v>
       </c>
       <c r="G8">
-        <v>8.2180000000000003E-2</v>
+        <v>8.2019999999999996E-2</v>
       </c>
       <c r="H8">
-        <v>8.233E-2</v>
+        <v>8.2170000000000007E-2</v>
       </c>
       <c r="I8">
-        <v>5.348E-2</v>
+        <v>5.3310000000000003E-2</v>
       </c>
       <c r="J8">
-        <v>7.5900000000000009E-2</v>
+        <v>7.5700000000000003E-2</v>
       </c>
       <c r="K8">
-        <v>7.5909999999999991E-2</v>
+        <v>7.571E-2</v>
       </c>
       <c r="L8">
-        <v>5.0549999999999998E-2</v>
+        <v>5.0360000000000002E-2</v>
       </c>
       <c r="M8">
-        <v>8.2180000000000003E-2</v>
+        <v>8.2019999999999996E-2</v>
       </c>
       <c r="N8">
-        <v>8.2450000000000009E-2</v>
+        <v>8.2290000000000002E-2</v>
       </c>
       <c r="O8">
-        <v>5.0549999999999998E-2</v>
+        <v>5.0360000000000002E-2</v>
       </c>
       <c r="P8">
-        <v>7.5900000000000009E-2</v>
+        <v>7.5700000000000003E-2</v>
       </c>
       <c r="Q8">
-        <v>7.6189999999999994E-2</v>
+        <v>7.5989999999999988E-2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -7155,49 +7682,49 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>6.9739999999999996E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="D9">
-        <v>5.6390000000000003E-2</v>
+        <v>6.966E-2</v>
       </c>
       <c r="E9">
-        <v>7.1749999999999994E-2</v>
+        <v>7.1650000000000005E-2</v>
       </c>
       <c r="F9">
-        <v>5.9490000000000001E-2</v>
+        <v>5.9360000000000003E-2</v>
       </c>
       <c r="G9">
-        <v>7.331E-2</v>
+        <v>7.3209999999999997E-2</v>
       </c>
       <c r="H9">
-        <v>7.553E-2</v>
+        <v>7.5400000000000009E-2</v>
       </c>
       <c r="I9">
-        <v>5.9490000000000001E-2</v>
+        <v>5.9360000000000003E-2</v>
       </c>
       <c r="J9">
-        <v>6.8010000000000001E-2</v>
+        <v>6.7849999999999994E-2</v>
       </c>
       <c r="K9">
-        <v>7.2279999999999997E-2</v>
+        <v>7.2120000000000004E-2</v>
       </c>
       <c r="L9">
-        <v>5.6030000000000003E-2</v>
+        <v>5.5879999999999999E-2</v>
       </c>
       <c r="M9">
-        <v>7.331E-2</v>
+        <v>7.3209999999999997E-2</v>
       </c>
       <c r="N9">
-        <v>7.392E-2</v>
+        <v>7.3810000000000001E-2</v>
       </c>
       <c r="O9">
-        <v>5.6030000000000003E-2</v>
+        <v>5.5879999999999999E-2</v>
       </c>
       <c r="P9">
-        <v>6.8010000000000001E-2</v>
+        <v>6.7849999999999994E-2</v>
       </c>
       <c r="Q9">
-        <v>7.0489999999999997E-2</v>
+        <v>7.0319999999999994E-2</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -7208,49 +7735,49 @@
         <v>40</v>
       </c>
       <c r="C10">
-        <v>6.2109999999999999E-2</v>
+        <v>5.6120000000000003E-2</v>
       </c>
       <c r="D10">
-        <v>5.62E-2</v>
+        <v>6.2049999999999987E-2</v>
       </c>
       <c r="E10">
-        <v>6.6989999999999994E-2</v>
+        <v>6.6909999999999997E-2</v>
       </c>
       <c r="F10">
-        <v>5.9290000000000002E-2</v>
+        <v>5.919E-2</v>
       </c>
       <c r="G10">
-        <v>6.5790000000000001E-2</v>
+        <v>6.5709999999999991E-2</v>
       </c>
       <c r="H10">
-        <v>7.0830000000000004E-2</v>
+        <v>7.0730000000000001E-2</v>
       </c>
       <c r="I10">
-        <v>5.9290000000000002E-2</v>
+        <v>5.919E-2</v>
       </c>
       <c r="J10">
-        <v>6.012E-2</v>
+        <v>6.0010000000000001E-2</v>
       </c>
       <c r="K10">
-        <v>6.7530000000000007E-2</v>
+        <v>6.7420000000000008E-2</v>
       </c>
       <c r="L10">
-        <v>5.5390000000000002E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="M10">
-        <v>6.5790000000000001E-2</v>
+        <v>6.5709999999999991E-2</v>
       </c>
       <c r="N10">
-        <v>6.8790000000000004E-2</v>
+        <v>6.8659999999999999E-2</v>
       </c>
       <c r="O10">
-        <v>5.5390000000000002E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="P10">
-        <v>6.012E-2</v>
+        <v>6.0010000000000001E-2</v>
       </c>
       <c r="Q10">
-        <v>6.5379999999999994E-2</v>
+        <v>6.5239999999999992E-2</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -7261,180 +7788,180 @@
         <v>45</v>
       </c>
       <c r="C11">
-        <v>6.1969999999999997E-2</v>
+        <v>5.4100000000000002E-2</v>
       </c>
       <c r="D11">
-        <v>5.4200000000000012E-2</v>
+        <v>6.1940000000000002E-2</v>
       </c>
       <c r="E11">
-        <v>6.5849999999999992E-2</v>
+        <v>6.5790000000000001E-2</v>
       </c>
       <c r="F11">
-        <v>5.7020000000000001E-2</v>
+        <v>5.6939999999999998E-2</v>
       </c>
       <c r="G11">
-        <v>6.5420000000000006E-2</v>
+        <v>6.5370000000000011E-2</v>
       </c>
       <c r="H11">
-        <v>6.9419999999999996E-2</v>
+        <v>6.9339999999999999E-2</v>
       </c>
       <c r="I11">
-        <v>5.7020000000000001E-2</v>
+        <v>5.6939999999999998E-2</v>
       </c>
       <c r="J11">
-        <v>5.9950000000000003E-2</v>
+        <v>5.9889999999999999E-2</v>
       </c>
       <c r="K11">
-        <v>6.6180000000000003E-2</v>
+        <v>6.6099999999999992E-2</v>
       </c>
       <c r="L11">
-        <v>5.3330000000000002E-2</v>
+        <v>5.3179999999999998E-2</v>
       </c>
       <c r="M11">
-        <v>6.5420000000000006E-2</v>
+        <v>6.5370000000000011E-2</v>
       </c>
       <c r="N11">
-        <v>6.7519999999999997E-2</v>
+        <v>6.7409999999999998E-2</v>
       </c>
       <c r="O11">
-        <v>5.3330000000000002E-2</v>
+        <v>5.3179999999999998E-2</v>
       </c>
       <c r="P11">
-        <v>5.9950000000000003E-2</v>
+        <v>5.9889999999999999E-2</v>
       </c>
       <c r="Q11">
-        <v>6.4189999999999997E-2</v>
+        <v>6.4069999999999988E-2</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="17" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>0.12667999999999999</v>
+        <v>6.473000000000001E-2</v>
       </c>
       <c r="B14">
-        <v>6.4920000000000005E-2</v>
+        <v>0.12651000000000001</v>
       </c>
       <c r="C14">
-        <v>0.12684000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>0.14549999999999999</v>
+        <v>6.5129999999999993E-2</v>
       </c>
       <c r="B15">
-        <v>6.5329999999999999E-2</v>
+        <v>0.14532</v>
       </c>
       <c r="C15">
-        <v>0.14582000000000001</v>
+        <v>0.14563000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>0.13295999999999999</v>
+        <v>5.525E-2</v>
       </c>
       <c r="B16">
-        <v>5.5469999999999998E-2</v>
+        <v>0.13277</v>
       </c>
       <c r="C16">
-        <v>0.13320000000000001</v>
+        <v>0.13300999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>0.11895</v>
+        <v>6.012E-2</v>
       </c>
       <c r="B17">
-        <v>6.0409999999999998E-2</v>
+        <v>0.11871</v>
       </c>
       <c r="C17">
-        <v>0.11928999999999999</v>
+        <v>0.11905</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9.9890000000000007E-2</v>
+        <v>5.0380000000000001E-2</v>
       </c>
       <c r="B18">
-        <v>5.0700000000000002E-2</v>
+        <v>9.9510000000000001E-2</v>
       </c>
       <c r="C18">
-        <v>0.10031</v>
+        <v>9.9919999999999995E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>8.2049999999999998E-2</v>
+        <v>5.1290000000000002E-2</v>
       </c>
       <c r="B19">
-        <v>5.1580000000000001E-2</v>
+        <v>8.181999999999999E-2</v>
       </c>
       <c r="C19">
-        <v>8.2430000000000003E-2</v>
+        <v>8.2189999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>8.2180000000000003E-2</v>
+        <v>5.0360000000000002E-2</v>
       </c>
       <c r="B20">
-        <v>5.0549999999999998E-2</v>
+        <v>8.2019999999999996E-2</v>
       </c>
       <c r="C20">
-        <v>8.2450000000000009E-2</v>
+        <v>8.2290000000000002E-2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>7.331E-2</v>
+        <v>5.5879999999999999E-2</v>
       </c>
       <c r="B21">
-        <v>5.6030000000000003E-2</v>
+        <v>7.3209999999999997E-2</v>
       </c>
       <c r="C21">
-        <v>7.392E-2</v>
+        <v>7.3810000000000001E-2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>6.5790000000000001E-2</v>
+        <v>5.525E-2</v>
       </c>
       <c r="B22">
-        <v>5.5390000000000002E-2</v>
+        <v>6.5709999999999991E-2</v>
       </c>
       <c r="C22">
-        <v>6.8790000000000004E-2</v>
+        <v>6.8659999999999999E-2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>6.5420000000000006E-2</v>
+        <v>5.3179999999999998E-2</v>
       </c>
       <c r="B23">
-        <v>5.3330000000000002E-2</v>
+        <v>6.5370000000000011E-2</v>
       </c>
       <c r="C23">
-        <v>6.7519999999999997E-2</v>
+        <v>6.7409999999999998E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B24">
         <f>(C15-D3)/D3</f>
-        <v>1.2555297757153907</v>
+        <v>5.3762662807525473E-2</v>
       </c>
       <c r="C24">
         <f>(C15-B15)/B15</f>
-        <v>1.2320526557477423</v>
+        <v>2.1332232314891599E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -7445,101 +7972,101 @@
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C30">
         <f t="shared" ref="C30:C39" si="0">(C2-C14)/C14</f>
-        <v>-5.2428256070640195E-2</v>
+        <v>-0.49068372019579964</v>
       </c>
       <c r="D30">
         <f t="shared" ref="D30:D39" si="1">(D2-C14)/C14</f>
-        <v>-0.4908546199936929</v>
+        <v>-5.2029054160745297E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C31">
         <f t="shared" si="0"/>
-        <v>-5.1296118502263163E-2</v>
+        <v>-0.55675341619171881</v>
       </c>
       <c r="D31">
         <f t="shared" si="1"/>
-        <v>-0.5566451789877932</v>
+        <v>-5.1019707477854968E-2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C32">
         <f t="shared" si="0"/>
-        <v>-5.0675675675675713E-2</v>
+        <v>-0.5916848357266371</v>
       </c>
       <c r="D32">
         <f t="shared" si="1"/>
-        <v>-0.59136636636636641</v>
+        <v>-5.0372152469739001E-2</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C33">
         <f t="shared" si="0"/>
-        <v>-5.0968228686394404E-2</v>
+        <v>-0.50247795044099119</v>
       </c>
       <c r="D33">
         <f t="shared" si="1"/>
-        <v>-0.50213764774918268</v>
+        <v>-5.0566988660226776E-2</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C34">
         <f t="shared" si="0"/>
-        <v>-5.2337752965805909E-2</v>
+        <v>-0.50040032025620496</v>
       </c>
       <c r="D34">
         <f t="shared" si="1"/>
-        <v>-0.50104675505931617</v>
+        <v>-5.134107285828645E-2</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C35">
         <f t="shared" si="0"/>
-        <v>-5.4955720004852507E-2</v>
+        <v>-0.38082491787322059</v>
       </c>
       <c r="D35">
         <f t="shared" si="1"/>
-        <v>-0.38056532815722433</v>
+        <v>-5.4386178367197981E-2</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C36">
         <f t="shared" si="0"/>
-        <v>-5.3244390539721097E-2</v>
+        <v>-0.39105602138777495</v>
       </c>
       <c r="D36">
         <f t="shared" si="1"/>
-        <v>-0.391024863553669</v>
+        <v>-5.2983351561550478E-2</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C37">
         <f t="shared" si="0"/>
-        <v>-5.654761904761909E-2</v>
+        <v>-0.23723072754369323</v>
       </c>
       <c r="D37">
         <f t="shared" si="1"/>
-        <v>-0.23714826839826836</v>
+        <v>-5.6225443706814808E-2</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C38">
         <f t="shared" si="0"/>
-        <v>-9.7107137665358403E-2</v>
+        <v>-0.18263909117390031</v>
       </c>
       <c r="D38">
         <f t="shared" si="1"/>
-        <v>-0.18302078790521883</v>
+        <v>-9.6271482668220387E-2</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C39">
         <f t="shared" si="0"/>
-        <v>-8.2197867298578198E-2</v>
+        <v>-0.19744844978489831</v>
       </c>
       <c r="D39">
         <f t="shared" si="1"/>
-        <v>-0.19727488151658745</v>
+        <v>-8.1145230677940897E-2</v>
       </c>
     </row>
   </sheetData>
@@ -7551,59 +8078,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:V64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="17" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7615,10 +8142,10 @@
         <v>0</v>
       </c>
       <c r="C2">
+        <v>8.0399999999999999E-2</v>
+      </c>
+      <c r="D2">
         <v>5.9330000000000001E-2</v>
-      </c>
-      <c r="D2">
-        <v>8.0399999999999999E-2</v>
       </c>
       <c r="E2">
         <v>8.0379999999999993E-2</v>
@@ -7668,10 +8195,10 @@
         <v>5</v>
       </c>
       <c r="C3">
+        <v>6.8069999999999992E-2</v>
+      </c>
+      <c r="D3">
         <v>6.0400000000000002E-2</v>
-      </c>
-      <c r="D3">
-        <v>6.8069999999999992E-2</v>
       </c>
       <c r="E3">
         <v>7.2800000000000004E-2</v>
@@ -7721,10 +8248,10 @@
         <v>10</v>
       </c>
       <c r="C4">
+        <v>8.3290000000000003E-2</v>
+      </c>
+      <c r="D4">
         <v>6.0840000000000012E-2</v>
-      </c>
-      <c r="D4">
-        <v>8.3290000000000003E-2</v>
       </c>
       <c r="E4">
         <v>8.3290000000000003E-2</v>
@@ -7774,10 +8301,10 @@
         <v>15</v>
       </c>
       <c r="C5">
+        <v>6.7720000000000002E-2</v>
+      </c>
+      <c r="D5">
         <v>5.8270000000000002E-2</v>
-      </c>
-      <c r="D5">
-        <v>6.7720000000000002E-2</v>
       </c>
       <c r="E5">
         <v>7.1470000000000006E-2</v>
@@ -7827,10 +8354,10 @@
         <v>20</v>
       </c>
       <c r="C6">
+        <v>7.2819999999999996E-2</v>
+      </c>
+      <c r="D6">
         <v>5.4710000000000002E-2</v>
-      </c>
-      <c r="D6">
-        <v>7.2819999999999996E-2</v>
       </c>
       <c r="E6">
         <v>7.2950000000000001E-2</v>
@@ -7880,10 +8407,10 @@
         <v>25</v>
       </c>
       <c r="C7">
+        <v>5.9909999999999998E-2</v>
+      </c>
+      <c r="D7">
         <v>4.9709999999999997E-2</v>
-      </c>
-      <c r="D7">
-        <v>5.9909999999999998E-2</v>
       </c>
       <c r="E7">
         <v>6.2270000000000013E-2</v>
@@ -7933,10 +8460,10 @@
         <v>30</v>
       </c>
       <c r="C8">
+        <v>5.7419999999999999E-2</v>
+      </c>
+      <c r="D8">
         <v>4.4650000000000002E-2</v>
-      </c>
-      <c r="D8">
-        <v>5.7419999999999999E-2</v>
       </c>
       <c r="E8">
         <v>5.8189999999999999E-2</v>
@@ -7986,10 +8513,10 @@
         <v>35</v>
       </c>
       <c r="C9">
+        <v>5.2159999999999998E-2</v>
+      </c>
+      <c r="D9">
         <v>3.3939999999999998E-2</v>
-      </c>
-      <c r="D9">
-        <v>5.2159999999999998E-2</v>
       </c>
       <c r="E9">
         <v>5.2170000000000001E-2</v>
@@ -8039,10 +8566,10 @@
         <v>40</v>
       </c>
       <c r="C10">
+        <v>4.8460000000000003E-2</v>
+      </c>
+      <c r="D10">
         <v>3.3250000000000002E-2</v>
-      </c>
-      <c r="D10">
-        <v>4.8460000000000003E-2</v>
       </c>
       <c r="E10">
         <v>4.8480000000000002E-2</v>
@@ -8092,10 +8619,10 @@
         <v>45</v>
       </c>
       <c r="C11">
+        <v>4.9889999999999997E-2</v>
+      </c>
+      <c r="D11">
         <v>3.177E-2</v>
-      </c>
-      <c r="D11">
-        <v>4.9889999999999997E-2</v>
       </c>
       <c r="E11">
         <v>4.9939999999999998E-2</v>
@@ -8145,10 +8672,10 @@
         <v>50</v>
       </c>
       <c r="C12">
+        <v>5.6550000000000003E-2</v>
+      </c>
+      <c r="D12">
         <v>2.7689999999999999E-2</v>
-      </c>
-      <c r="D12">
-        <v>5.6550000000000003E-2</v>
       </c>
       <c r="E12">
         <v>5.6680000000000001E-2</v>
@@ -8198,10 +8725,10 @@
         <v>55</v>
       </c>
       <c r="C13">
+        <v>5.917E-2</v>
+      </c>
+      <c r="D13">
         <v>2.699E-2</v>
-      </c>
-      <c r="D13">
-        <v>5.917E-2</v>
       </c>
       <c r="E13">
         <v>5.9200000000000003E-2</v>
@@ -8251,10 +8778,10 @@
         <v>60</v>
       </c>
       <c r="C14">
+        <v>6.522E-2</v>
+      </c>
+      <c r="D14">
         <v>2.8320000000000001E-2</v>
-      </c>
-      <c r="D14">
-        <v>6.522E-2</v>
       </c>
       <c r="E14">
         <v>6.5239999999999992E-2</v>
@@ -8304,10 +8831,10 @@
         <v>65</v>
       </c>
       <c r="C15">
+        <v>6.4890000000000003E-2</v>
+      </c>
+      <c r="D15">
         <v>2.6579999999999999E-2</v>
-      </c>
-      <c r="D15">
-        <v>6.4890000000000003E-2</v>
       </c>
       <c r="E15">
         <v>6.4939999999999998E-2</v>
@@ -8357,10 +8884,10 @@
         <v>70</v>
       </c>
       <c r="C16">
+        <v>6.0859999999999997E-2</v>
+      </c>
+      <c r="D16">
         <v>2.7050000000000001E-2</v>
-      </c>
-      <c r="D16">
-        <v>6.0859999999999997E-2</v>
       </c>
       <c r="E16">
         <v>6.089E-2</v>
@@ -8402,7 +8929,7 @@
         <v>5.6680000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -8410,10 +8937,10 @@
         <v>75</v>
       </c>
       <c r="C17">
+        <v>7.51E-2</v>
+      </c>
+      <c r="D17">
         <v>2.9239999999999999E-2</v>
-      </c>
-      <c r="D17">
-        <v>7.51E-2</v>
       </c>
       <c r="E17">
         <v>7.5150000000000008E-2</v>
@@ -8455,7 +8982,7 @@
         <v>6.9819999999999993E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -8463,10 +8990,10 @@
         <v>80</v>
       </c>
       <c r="C18">
+        <v>7.9430000000000001E-2</v>
+      </c>
+      <c r="D18">
         <v>3.3660000000000002E-2</v>
-      </c>
-      <c r="D18">
-        <v>7.9430000000000001E-2</v>
       </c>
       <c r="E18">
         <v>7.9489999999999991E-2</v>
@@ -8508,7 +9035,7 @@
         <v>7.3880000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -8516,10 +9043,10 @@
         <v>85</v>
       </c>
       <c r="C19">
+        <v>8.1009999999999999E-2</v>
+      </c>
+      <c r="D19">
         <v>3.6679999999999997E-2</v>
-      </c>
-      <c r="D19">
-        <v>8.1009999999999999E-2</v>
       </c>
       <c r="E19">
         <v>8.1079999999999999E-2</v>
@@ -8561,7 +9088,7 @@
         <v>7.5409999999999991E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -8569,10 +9096,10 @@
         <v>90</v>
       </c>
       <c r="C20">
+        <v>8.4610000000000005E-2</v>
+      </c>
+      <c r="D20">
         <v>3.7580000000000002E-2</v>
-      </c>
-      <c r="D20">
-        <v>8.4610000000000005E-2</v>
       </c>
       <c r="E20">
         <v>8.4620000000000001E-2</v>
@@ -8614,23 +9141,23 @@
         <v>7.9010000000000011E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>6.9879999999999998E-2</v>
       </c>
@@ -8641,7 +9168,7 @@
         <v>9.1069999999999998E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6.9889999999999994E-2</v>
       </c>
@@ -8652,7 +9179,7 @@
         <v>8.131999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>7.1169999999999997E-2</v>
       </c>
@@ -8662,8 +9189,14 @@
       <c r="C25">
         <v>9.3310000000000004E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U25">
+        <v>6.9879999999999998E-2</v>
+      </c>
+      <c r="V25">
+        <v>8.7139999999999995E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>6.7080000000000001E-2</v>
       </c>
@@ -8673,8 +9206,14 @@
       <c r="C26">
         <v>7.9489999999999991E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U26">
+        <v>6.9889999999999994E-2</v>
+      </c>
+      <c r="V26">
+        <v>7.3819999999999997E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>6.2869999999999995E-2</v>
       </c>
@@ -8684,8 +9223,14 @@
       <c r="C27">
         <v>8.1220000000000001E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U27">
+        <v>7.1169999999999997E-2</v>
+      </c>
+      <c r="V27">
+        <v>9.0029999999999999E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5.7540000000000001E-2</v>
       </c>
@@ -8695,8 +9240,14 @@
       <c r="C28">
         <v>6.9379999999999997E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U28">
+        <v>6.7080000000000001E-2</v>
+      </c>
+      <c r="V28">
+        <v>7.3319999999999996E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>5.2139999999999999E-2</v>
       </c>
@@ -8706,8 +9257,14 @@
       <c r="C29">
         <v>6.5769999999999995E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U29">
+        <v>6.2869999999999995E-2</v>
+      </c>
+      <c r="V29">
+        <v>7.887000000000001E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3.9409999999999987E-2</v>
       </c>
@@ -8717,8 +9274,14 @@
       <c r="C30">
         <v>5.808E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U30">
+        <v>5.7540000000000001E-2</v>
+      </c>
+      <c r="V30">
+        <v>6.4899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>3.8490000000000003E-2</v>
       </c>
@@ -8728,8 +9291,14 @@
       <c r="C31">
         <v>5.3900000000000003E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="U31">
+        <v>5.2139999999999999E-2</v>
+      </c>
+      <c r="V31">
+        <v>6.2270000000000013E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>3.678E-2</v>
       </c>
@@ -8739,8 +9308,14 @@
       <c r="C32">
         <v>5.5100000000000003E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U32">
+        <v>3.9409999999999987E-2</v>
+      </c>
+      <c r="V32">
+        <v>5.6509999999999998E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>3.1719999999999998E-2</v>
       </c>
@@ -8750,8 +9325,14 @@
       <c r="C33">
         <v>6.164E-2</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U33">
+        <v>3.8490000000000003E-2</v>
+      </c>
+      <c r="V33">
+        <v>5.2470000000000003E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>3.1949999999999999E-2</v>
       </c>
@@ -8761,8 +9342,14 @@
       <c r="C34">
         <v>6.4899999999999999E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U34">
+        <v>3.678E-2</v>
+      </c>
+      <c r="V34">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>3.3619999999999997E-2</v>
       </c>
@@ -8772,8 +9359,14 @@
       <c r="C35">
         <v>7.1510000000000004E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U35">
+        <v>3.1719999999999998E-2</v>
+      </c>
+      <c r="V35">
+        <v>6.1100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3.0939999999999999E-2</v>
       </c>
@@ -8783,8 +9376,14 @@
       <c r="C36">
         <v>7.0870000000000002E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U36">
+        <v>3.1949999999999999E-2</v>
+      </c>
+      <c r="V36">
+        <v>6.404E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>3.2000000000000001E-2</v>
       </c>
@@ -8794,8 +9393,14 @@
       <c r="C37">
         <v>6.6670000000000007E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U37">
+        <v>3.3619999999999997E-2</v>
+      </c>
+      <c r="V37">
+        <v>7.0550000000000002E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>3.4660000000000003E-2</v>
       </c>
@@ -8805,8 +9410,14 @@
       <c r="C38">
         <v>8.201E-2</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U38">
+        <v>3.0939999999999999E-2</v>
+      </c>
+      <c r="V38">
+        <v>7.0150000000000004E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>3.9399999999999998E-2</v>
       </c>
@@ -8816,8 +9427,14 @@
       <c r="C39">
         <v>8.6609999999999993E-2</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U39">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="V39">
+        <v>6.5799999999999997E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>4.2610000000000002E-2</v>
       </c>
@@ -8827,8 +9444,14 @@
       <c r="C40">
         <v>8.8439999999999991E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U40">
+        <v>3.4660000000000003E-2</v>
+      </c>
+      <c r="V40">
+        <v>8.1140000000000004E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>4.4650000000000002E-2</v>
       </c>
@@ -8838,211 +9461,231 @@
       <c r="C41">
         <v>9.2499999999999999E-2</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4">
+      <c r="U41">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="V41">
+        <v>8.5720000000000005E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2">
         <f>(C41-C20)/C20</f>
-        <v>1.4614156466205426</v>
-      </c>
-      <c r="C42" s="4">
+        <v>9.3251388724736956E-2</v>
+      </c>
+      <c r="C42" s="2">
         <f>(C41-A41)/A41</f>
         <v>1.0716685330347142</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="U42">
+        <v>4.2610000000000002E-2</v>
+      </c>
+      <c r="V42">
+        <v>8.7459999999999996E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U43">
+        <v>4.4650000000000002E-2</v>
+      </c>
+      <c r="V43">
+        <v>9.126999999999999E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C46">
         <f t="shared" ref="C46:C64" si="0">(C2-C23)/C23</f>
-        <v>-0.34852311408806408</v>
+        <v>-0.11716262215877896</v>
       </c>
       <c r="D46">
         <f t="shared" ref="D46:D64" si="1">(D2-C23)/C23</f>
-        <v>-0.11716262215877896</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.34852311408806408</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C47">
         <f t="shared" si="0"/>
-        <v>-0.25725528775209039</v>
+        <v>-0.16293654697491392</v>
       </c>
       <c r="D47">
         <f t="shared" si="1"/>
-        <v>-0.16293654697491392</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.25725528775209039</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C48">
         <f t="shared" si="0"/>
-        <v>-0.3479798521058835</v>
+        <v>-0.10738398885435646</v>
       </c>
       <c r="D48">
         <f t="shared" si="1"/>
-        <v>-0.10738398885435646</v>
+        <v>-0.3479798521058835</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C49">
         <f t="shared" si="0"/>
-        <v>-0.26695181783872174</v>
+        <v>-0.14806893948924379</v>
       </c>
       <c r="D49">
         <f t="shared" si="1"/>
-        <v>-0.14806893948924379</v>
+        <v>-0.26695181783872174</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C50">
         <f t="shared" si="0"/>
-        <v>-0.32639743905442009</v>
+        <v>-0.10342280226545192</v>
       </c>
       <c r="D50">
         <f t="shared" si="1"/>
-        <v>-0.10342280226545192</v>
+        <v>-0.32639743905442009</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C51">
         <f t="shared" si="0"/>
-        <v>-0.28351109829922166</v>
+        <v>-0.13649466705102334</v>
       </c>
       <c r="D51">
         <f t="shared" si="1"/>
-        <v>-0.13649466705102334</v>
+        <v>-0.28351109829922166</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C52">
         <f t="shared" si="0"/>
-        <v>-0.32111905123916673</v>
+        <v>-0.12695757944351524</v>
       </c>
       <c r="D52">
         <f t="shared" si="1"/>
-        <v>-0.12695757944351524</v>
+        <v>-0.32111905123916673</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C53">
         <f t="shared" si="0"/>
-        <v>-0.41563360881542705</v>
+        <v>-0.10192837465564741</v>
       </c>
       <c r="D53">
         <f t="shared" si="1"/>
-        <v>-0.10192837465564741</v>
+        <v>-0.41563360881542705</v>
       </c>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C54">
         <f t="shared" si="0"/>
-        <v>-0.38311688311688313</v>
+        <v>-0.10092764378478664</v>
       </c>
       <c r="D54">
         <f t="shared" si="1"/>
-        <v>-0.10092764378478664</v>
+        <v>-0.38311688311688313</v>
       </c>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C55">
         <f t="shared" si="0"/>
-        <v>-0.42341197822141563</v>
+        <v>-9.4555353901996472E-2</v>
       </c>
       <c r="D55">
         <f t="shared" si="1"/>
-        <v>-9.4555353901996472E-2</v>
+        <v>-0.42341197822141563</v>
       </c>
     </row>
     <row r="56" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C56">
         <f t="shared" si="0"/>
-        <v>-0.55077871512005194</v>
+        <v>-8.2576249188838366E-2</v>
       </c>
       <c r="D56">
         <f t="shared" si="1"/>
-        <v>-8.2576249188838366E-2</v>
+        <v>-0.55077871512005194</v>
       </c>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C57">
         <f t="shared" si="0"/>
-        <v>-0.58412942989214178</v>
+        <v>-8.8289676425269636E-2</v>
       </c>
       <c r="D57">
         <f t="shared" si="1"/>
-        <v>-8.8289676425269636E-2</v>
+        <v>-0.58412942989214178</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C58">
         <f t="shared" si="0"/>
-        <v>-0.60397147252132577</v>
+        <v>-8.7959725912459846E-2</v>
       </c>
       <c r="D58">
         <f t="shared" si="1"/>
-        <v>-8.7959725912459846E-2</v>
+        <v>-0.60397147252132577</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C59">
         <f t="shared" si="0"/>
-        <v>-0.62494708621419504</v>
+        <v>-8.4379850430365444E-2</v>
       </c>
       <c r="D59">
         <f t="shared" si="1"/>
-        <v>-8.4379850430365444E-2</v>
+        <v>-0.62494708621419504</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C60">
         <f t="shared" si="0"/>
-        <v>-0.5942702864856757</v>
+        <v>-8.7145642717864236E-2</v>
       </c>
       <c r="D60">
         <f t="shared" si="1"/>
-        <v>-8.7145642717864236E-2</v>
+        <v>-0.5942702864856757</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C61">
         <f t="shared" si="0"/>
-        <v>-0.64345811486404092</v>
+        <v>-8.4258017314961589E-2</v>
       </c>
       <c r="D61">
         <f t="shared" si="1"/>
-        <v>-8.4258017314961589E-2</v>
+        <v>-0.64345811486404092</v>
       </c>
     </row>
     <row r="62" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C62">
         <f t="shared" si="0"/>
-        <v>-0.61136127467959811</v>
+        <v>-8.2900357926336363E-2</v>
       </c>
       <c r="D62">
         <f t="shared" si="1"/>
-        <v>-8.2900357926336363E-2</v>
+        <v>-0.61136127467959811</v>
       </c>
     </row>
     <row r="63" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C63">
         <f t="shared" si="0"/>
-        <v>-0.58525554047942108</v>
+        <v>-8.4011759384893636E-2</v>
       </c>
       <c r="D63">
         <f t="shared" si="1"/>
-        <v>-8.4011759384893636E-2</v>
+        <v>-0.58525554047942108</v>
       </c>
     </row>
     <row r="64" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C64">
         <f t="shared" si="0"/>
-        <v>-0.5937297297297297</v>
+        <v>-8.5297297297297237E-2</v>
       </c>
       <c r="D64">
         <f t="shared" si="1"/>
-        <v>-8.5297297297297237E-2</v>
+        <v>-0.5937297297297297</v>
       </c>
     </row>
   </sheetData>
@@ -9058,55 +9701,55 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="17" t="s">
         <v>73</v>
       </c>
     </row>
@@ -10118,13 +10761,13 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="17" t="s">
         <v>73</v>
       </c>
     </row>
@@ -10551,63 +11194,64 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:AD86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="8.88671875" style="7"/>
-    <col min="5" max="7" width="8.88671875" style="8"/>
+    <col min="2" max="4" width="8.88671875" style="5" customWidth="1"/>
+    <col min="5" max="7" width="8.88671875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="13" t="s">
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="9" t="s">
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H4" t="s">
@@ -10620,551 +11264,589 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>0</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>0.14461754225656301</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>0.22422937900353401</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>0.22881801939514301</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="6">
         <f>'1-1_Acceleration'!A14</f>
-        <v>0.12667999999999999</v>
-      </c>
-      <c r="F5" s="8">
+        <v>6.473000000000001E-2</v>
+      </c>
+      <c r="F5" s="6">
         <f>'1-1_Acceleration'!B14</f>
-        <v>6.4920000000000005E-2</v>
-      </c>
-      <c r="G5" s="8">
+        <v>0.12651000000000001</v>
+      </c>
+      <c r="G5" s="6">
         <f>'1-1_Acceleration'!C14</f>
-        <v>0.12684000000000001</v>
+        <v>0.12665999999999999</v>
       </c>
       <c r="H5">
         <f t="shared" ref="H5:H14" si="0">(E5-B5)/B5</f>
-        <v>-0.12403434587997905</v>
+        <v>-0.55240561421543277</v>
       </c>
       <c r="I5">
         <f t="shared" ref="I5:I14" si="1">(F5-C5)/C5</f>
-        <v>-0.71047504886067214</v>
+        <v>-0.43580096166610655</v>
       </c>
       <c r="J5">
         <f t="shared" ref="J5:J14" si="2">(G5-D5)/D5</f>
-        <v>-0.4456730272585675</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.44645967859169167</v>
+      </c>
+      <c r="AC5" s="5"/>
+      <c r="AD5" s="5"/>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>8.7266462599716502E-2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>0.14574383059780099</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>0.23891485265779699</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>0.242018594909096</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <f>'1-1_Acceleration'!A15</f>
-        <v>0.14549999999999999</v>
-      </c>
-      <c r="F6" s="8">
+        <v>6.5129999999999993E-2</v>
+      </c>
+      <c r="F6" s="6">
         <f>'1-1_Acceleration'!B15</f>
-        <v>6.5329999999999999E-2</v>
-      </c>
-      <c r="G6" s="8">
+        <v>0.14532</v>
+      </c>
+      <c r="G6" s="6">
         <f>'1-1_Acceleration'!C15</f>
-        <v>0.14582000000000001</v>
+        <v>0.14563000000000001</v>
       </c>
       <c r="H6">
         <f t="shared" si="0"/>
-        <v>-1.6730080223696449E-3</v>
+        <v>-0.55312002070444632</v>
       </c>
       <c r="I6">
         <f t="shared" si="1"/>
-        <v>-0.72655530088129938</v>
+        <v>-0.39174982893112537</v>
       </c>
       <c r="J6">
         <f t="shared" si="2"/>
-        <v>-0.39748431291086911</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.39826937655472411</v>
+      </c>
+      <c r="AC6" s="5"/>
+      <c r="AD6" s="5"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.174532925199433</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>0.123218319821101</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>0.195550423711429</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>0.19790102555998401</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <f>'1-1_Acceleration'!A16</f>
-        <v>0.13295999999999999</v>
-      </c>
-      <c r="F7" s="8">
+        <v>5.525E-2</v>
+      </c>
+      <c r="F7" s="6">
         <f>'1-1_Acceleration'!B16</f>
-        <v>5.5469999999999998E-2</v>
-      </c>
-      <c r="G7" s="8">
+        <v>0.13277</v>
+      </c>
+      <c r="G7" s="6">
         <f>'1-1_Acceleration'!C16</f>
-        <v>0.13320000000000001</v>
+        <v>0.13300999999999999</v>
       </c>
       <c r="H7">
         <f t="shared" si="0"/>
-        <v>7.9060323116260697E-2</v>
+        <v>-0.5516088834824503</v>
       </c>
       <c r="I7">
         <f t="shared" si="1"/>
-        <v>-0.71633914697185064</v>
+        <v>-0.32104468259334068</v>
       </c>
       <c r="J7">
         <f t="shared" si="2"/>
-        <v>-0.32693628230023014</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.32789635817382606</v>
+      </c>
+      <c r="AC7" s="5"/>
+      <c r="AD7" s="5"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.26179938779914902</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>0.119190932832967</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>0.19996638206058301</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>0.201287478382664</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <f>'1-1_Acceleration'!A17</f>
-        <v>0.11895</v>
-      </c>
-      <c r="F8" s="8">
+        <v>6.012E-2</v>
+      </c>
+      <c r="F8" s="6">
         <f>'1-1_Acceleration'!B17</f>
-        <v>6.0409999999999998E-2</v>
-      </c>
-      <c r="G8" s="8">
+        <v>0.11871</v>
+      </c>
+      <c r="G8" s="6">
         <f>'1-1_Acceleration'!C17</f>
-        <v>0.11928999999999999</v>
+        <v>0.11905</v>
       </c>
       <c r="H8">
         <f t="shared" si="0"/>
-        <v>-2.0214023604013661E-3</v>
+        <v>-0.49559921572011206</v>
       </c>
       <c r="I8">
         <f t="shared" si="1"/>
-        <v>-0.69789921997139592</v>
+        <v>-0.40635021358722734</v>
       </c>
       <c r="J8">
         <f t="shared" si="2"/>
-        <v>-0.40736502360459836</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.40855734814424877</v>
+      </c>
+      <c r="AC8" s="5"/>
+      <c r="AD8" s="5"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.34906585039886601</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="5">
         <v>0.105740550632465</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="5">
         <v>0.14722937110335699</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>0.150365553159441</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <f>'1-1_Acceleration'!A18</f>
-        <v>9.9890000000000007E-2</v>
-      </c>
-      <c r="F9" s="8">
+        <v>5.0380000000000001E-2</v>
+      </c>
+      <c r="F9" s="6">
         <f>'1-1_Acceleration'!B18</f>
-        <v>5.0700000000000002E-2</v>
-      </c>
-      <c r="G9" s="8">
+        <v>9.9510000000000001E-2</v>
+      </c>
+      <c r="G9" s="6">
         <f>'1-1_Acceleration'!C18</f>
-        <v>0.10031</v>
+        <v>9.9919999999999995E-2</v>
       </c>
       <c r="H9">
         <f t="shared" si="0"/>
-        <v>-5.532929985205437E-2</v>
+        <v>-0.52355080715333369</v>
       </c>
       <c r="I9">
         <f t="shared" si="1"/>
-        <v>-0.6556393631240337</v>
+        <v>-0.32411583874699396</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
-        <v>-0.33289242188577794</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.33548610103506066</v>
+      </c>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.43633231299858199</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="5">
         <v>0.113151330133636</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="5">
         <v>0.11653426316692</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>0.129943884511105</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <f>'1-1_Acceleration'!A19</f>
-        <v>8.2049999999999998E-2</v>
-      </c>
-      <c r="F10" s="8">
+        <v>5.1290000000000002E-2</v>
+      </c>
+      <c r="F10" s="6">
         <f>'1-1_Acceleration'!B19</f>
-        <v>5.1580000000000001E-2</v>
-      </c>
-      <c r="G10" s="8">
+        <v>8.181999999999999E-2</v>
+      </c>
+      <c r="G10" s="6">
         <f>'1-1_Acceleration'!C19</f>
-        <v>8.2430000000000003E-2</v>
+        <v>8.2189999999999999E-2</v>
       </c>
       <c r="H10">
         <f t="shared" si="0"/>
-        <v>-0.27486490964714383</v>
+        <v>-0.54671323846193787</v>
       </c>
       <c r="I10">
         <f t="shared" si="1"/>
-        <v>-0.55738339439175555</v>
+        <v>-0.29788889742406832</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>-0.36564925459839137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.36749620569503566</v>
+      </c>
+      <c r="AC10" s="5"/>
+      <c r="AD10" s="5"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.52359877559829904</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="5">
         <v>0.10481180814546701</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="5">
         <v>0.12734449340182</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>0.13194455836051999</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="6">
         <f>'1-1_Acceleration'!A20</f>
-        <v>8.2180000000000003E-2</v>
-      </c>
-      <c r="F11" s="8">
+        <v>5.0360000000000002E-2</v>
+      </c>
+      <c r="F11" s="6">
         <f>'1-1_Acceleration'!B20</f>
-        <v>5.0549999999999998E-2</v>
-      </c>
-      <c r="G11" s="8">
+        <v>8.2019999999999996E-2</v>
+      </c>
+      <c r="G11" s="6">
         <f>'1-1_Acceleration'!C20</f>
-        <v>8.2450000000000009E-2</v>
+        <v>8.2290000000000002E-2</v>
       </c>
       <c r="H11">
         <f t="shared" si="0"/>
-        <v>-0.2159280385093309</v>
+        <v>-0.51951978607118399</v>
       </c>
       <c r="I11">
         <f t="shared" si="1"/>
-        <v>-0.60304526211042631</v>
+        <v>-0.3559203243975701</v>
       </c>
       <c r="J11">
         <f t="shared" si="2"/>
-        <v>-0.37511632897571301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.37632895950771894</v>
+      </c>
+      <c r="AC11" s="5"/>
+      <c r="AD11" s="5"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.61086523819801497</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>0.11044656620889901</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="5">
         <v>0.114415712852866</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>0.12722112864763599</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <f>'1-1_Acceleration'!A21</f>
-        <v>7.331E-2</v>
-      </c>
-      <c r="F12" s="8">
+        <v>5.5879999999999999E-2</v>
+      </c>
+      <c r="F12" s="6">
         <f>'1-1_Acceleration'!B21</f>
-        <v>5.6030000000000003E-2</v>
-      </c>
-      <c r="G12" s="8">
+        <v>7.3209999999999997E-2</v>
+      </c>
+      <c r="G12" s="6">
         <f>'1-1_Acceleration'!C21</f>
-        <v>7.392E-2</v>
+        <v>7.3810000000000001E-2</v>
       </c>
       <c r="H12">
         <f t="shared" si="0"/>
-        <v>-0.33624011577380125</v>
+        <v>-0.49405398539680828</v>
       </c>
       <c r="I12">
         <f t="shared" si="1"/>
-        <v>-0.51029453382812617</v>
+        <v>-0.36014033234976117</v>
       </c>
       <c r="J12">
         <f t="shared" si="2"/>
-        <v>-0.41896443785893439</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.4198290741121205</v>
+      </c>
+      <c r="AC12" s="5"/>
+      <c r="AD12" s="5"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.69813170079773201</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>0.102752485148652</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="5">
         <v>9.6404404302761398E-2</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>0.112717366536148</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="6">
         <f>'1-1_Acceleration'!A22</f>
-        <v>6.5790000000000001E-2</v>
-      </c>
-      <c r="F13" s="8">
+        <v>5.525E-2</v>
+      </c>
+      <c r="F13" s="6">
         <f>'1-1_Acceleration'!B22</f>
-        <v>5.5390000000000002E-2</v>
-      </c>
-      <c r="G13" s="8">
+        <v>6.5709999999999991E-2</v>
+      </c>
+      <c r="G13" s="6">
         <f>'1-1_Acceleration'!C22</f>
-        <v>6.8790000000000004E-2</v>
+        <v>6.8659999999999999E-2</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>-0.35972351515565171</v>
+        <v>-0.46230010962683932</v>
       </c>
       <c r="I13">
         <f t="shared" si="1"/>
-        <v>-0.42544118808051784</v>
+        <v>-0.31839213700615338</v>
       </c>
       <c r="J13">
         <f t="shared" si="2"/>
-        <v>-0.38971249849117678</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.39086582564913797</v>
+      </c>
+      <c r="AC13" s="5"/>
+      <c r="AD13" s="5"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.78539816339744795</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="5">
         <v>9.72536592135958E-2</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="5">
         <v>0.10631356936144</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>0.115269005057364</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <f>'1-1_Acceleration'!A23</f>
-        <v>6.5420000000000006E-2</v>
-      </c>
-      <c r="F14" s="8">
+        <v>5.3179999999999998E-2</v>
+      </c>
+      <c r="F14" s="6">
         <f>'1-1_Acceleration'!B23</f>
-        <v>5.3330000000000002E-2</v>
-      </c>
-      <c r="G14" s="8">
+        <v>6.5370000000000011E-2</v>
+      </c>
+      <c r="G14" s="6">
         <f>'1-1_Acceleration'!C23</f>
-        <v>6.7519999999999997E-2</v>
+        <v>6.7409999999999998E-2</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>-0.32732608182567524</v>
+        <v>-0.45318252876015613</v>
       </c>
       <c r="I14">
         <f t="shared" si="1"/>
-        <v>-0.49837071297370222</v>
+        <v>-0.38512082330941139</v>
       </c>
       <c r="J14">
         <f t="shared" si="2"/>
-        <v>-0.41423976058092593</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.41519405007050081</v>
+      </c>
+      <c r="AC14" s="5"/>
+      <c r="AD14" s="5"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.87266462599716499</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>9.6404404302761398E-2</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="5">
         <v>0.102752485148652</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="5">
         <v>0.112717366536148</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>0.95993108859688103</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>0.114415712852866</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="5">
         <v>0.11044656620889901</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="5">
         <v>0.12722112864763599</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC16" s="5"/>
+      <c r="AD16" s="5"/>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1.0471975511966001</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="5">
         <v>0.12734449340182</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="5">
         <v>0.10481180814546701</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="5">
         <v>0.13194455836051999</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC17" s="5"/>
+      <c r="AD17" s="5"/>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1.13446401379631</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="5">
         <v>0.11653426316692</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="5">
         <v>0.113151330133636</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="5">
         <v>0.129943884511105</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1.2217304763960299</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="5">
         <v>0.14722937110335699</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="5">
         <v>0.105740550632465</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="5">
         <v>0.150365553159441</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC19" s="5"/>
+      <c r="AD19" s="5"/>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1.3089969389957501</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="5">
         <v>0.19996638206058301</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="5">
         <v>0.119190932832967</v>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="5">
         <v>0.201287478382664</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC20" s="5"/>
+      <c r="AD20" s="5"/>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1.39626340159546</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="5">
         <v>0.195550423711429</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="5">
         <v>0.123218319821101</v>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="5">
         <v>0.19790102555998401</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC21" s="5"/>
+      <c r="AD21" s="5"/>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1.48352986419518</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="5">
         <v>0.23891485265779699</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="5">
         <v>0.14574383059780099</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="5">
         <v>0.242018594909096</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC22" s="5"/>
+      <c r="AD22" s="5"/>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1.5707963267949001</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="5">
         <v>0.22422937900353401</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="5">
         <v>0.14461754225656301</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="5">
         <v>0.22881801939514301</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="AC23" s="5"/>
+      <c r="AD23" s="5"/>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="6" t="s">
         <v>97</v>
       </c>
       <c r="H28" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>99</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H29" t="s">
@@ -11177,28 +11859,28 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>0</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="5">
         <v>0.13223209299999999</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="5">
         <v>9.5521892999999997E-2</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="5">
         <v>0.13761963699999999</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="6">
         <f>'2-1_Acceleration'!A23</f>
         <v>6.9879999999999998E-2</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="6">
         <f>'2-1_Acceleration'!B23</f>
         <v>8.7139999999999995E-2</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="6">
         <f>'2-1_Acceleration'!C23</f>
         <v>9.1069999999999998E-2</v>
       </c>
@@ -11215,28 +11897,28 @@
         <v>-0.33824850882290869</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>8.7266463000000002E-2</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="5">
         <v>0.121683868</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="5">
         <v>9.7854450999999995E-2</v>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="5">
         <v>0.12609626900000001</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="6">
         <f>'2-1_Acceleration'!A24</f>
         <v>6.9889999999999994E-2</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="6">
         <f>'2-1_Acceleration'!B24</f>
         <v>7.3819999999999997E-2</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="6">
         <f>'2-1_Acceleration'!C24</f>
         <v>8.131999999999999E-2</v>
       </c>
@@ -11253,28 +11935,28 @@
         <v>-0.35509590692171883</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>0.17453292500000001</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="5">
         <v>0.12946930800000001</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="5">
         <v>9.8119680000000001E-2</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="5">
         <v>0.13483157900000001</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="6">
         <f>'2-1_Acceleration'!A25</f>
         <v>7.1169999999999997E-2</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="6">
         <f>'2-1_Acceleration'!B25</f>
         <v>9.0029999999999999E-2</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="6">
         <f>'2-1_Acceleration'!C25</f>
         <v>9.3310000000000004E-2</v>
       </c>
@@ -11295,24 +11977,24 @@
       <c r="A33">
         <v>0.26179938800000002</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="5">
         <v>0.119927643</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="5">
         <v>9.0768804999999994E-2</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="5">
         <v>0.125383893</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="6">
         <f>'2-1_Acceleration'!A26</f>
         <v>6.7080000000000001E-2</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="6">
         <f>'2-1_Acceleration'!B26</f>
         <v>7.3319999999999996E-2</v>
       </c>
-      <c r="G33" s="8">
+      <c r="G33" s="6">
         <f>'2-1_Acceleration'!C26</f>
         <v>7.9489999999999991E-2</v>
       </c>
@@ -11333,24 +12015,24 @@
       <c r="A34">
         <v>0.34906585000000001</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="5">
         <v>0.124606461</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="5">
         <v>9.2318127999999999E-2</v>
       </c>
-      <c r="D34" s="7">
+      <c r="D34" s="5">
         <v>0.12927704000000001</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="6">
         <f>'2-1_Acceleration'!A27</f>
         <v>6.2869999999999995E-2</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="6">
         <f>'2-1_Acceleration'!B27</f>
         <v>7.887000000000001E-2</v>
       </c>
-      <c r="G34" s="8">
+      <c r="G34" s="6">
         <f>'2-1_Acceleration'!C27</f>
         <v>8.1220000000000001E-2</v>
       </c>
@@ -11371,24 +12053,24 @@
       <c r="A35">
         <v>0.43633231300000003</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="5">
         <v>0.10421169700000001</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="5">
         <v>7.1819293000000006E-2</v>
       </c>
-      <c r="D35" s="7">
+      <c r="D35" s="5">
         <v>0.107871893</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="6">
         <f>'2-1_Acceleration'!A28</f>
         <v>5.7540000000000001E-2</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="6">
         <f>'2-1_Acceleration'!B28</f>
         <v>6.4899999999999999E-2</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35" s="6">
         <f>'2-1_Acceleration'!C28</f>
         <v>6.9379999999999997E-2</v>
       </c>
@@ -11409,24 +12091,24 @@
       <c r="A36">
         <v>0.52359877600000004</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="5">
         <v>9.6632271000000006E-2</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="5">
         <v>6.6401017000000007E-2</v>
       </c>
-      <c r="D36" s="7">
+      <c r="D36" s="5">
         <v>9.9507069000000004E-2</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="6">
         <f>'2-1_Acceleration'!A29</f>
         <v>5.2139999999999999E-2</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="6">
         <f>'2-1_Acceleration'!B29</f>
         <v>6.2270000000000013E-2</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36" s="6">
         <f>'2-1_Acceleration'!C29</f>
         <v>6.5769999999999995E-2</v>
       </c>
@@ -11447,24 +12129,24 @@
       <c r="A37">
         <v>0.61086523800000003</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="5">
         <v>9.6736048000000005E-2</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="5">
         <v>5.8162268000000003E-2</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="5">
         <v>9.8793607000000006E-2</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="6">
         <f>'2-1_Acceleration'!A30</f>
         <v>3.9409999999999987E-2</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="6">
         <f>'2-1_Acceleration'!B30</f>
         <v>5.6509999999999998E-2</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37" s="6">
         <f>'2-1_Acceleration'!C30</f>
         <v>5.808E-2</v>
       </c>
@@ -11485,24 +12167,24 @@
       <c r="A38">
         <v>0.69813170099999999</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="5">
         <v>8.3372399999999999E-2</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="5">
         <v>5.6316040999999997E-2</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="5">
         <v>8.6108604000000005E-2</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="6">
         <f>'2-1_Acceleration'!A31</f>
         <v>3.8490000000000003E-2</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="6">
         <f>'2-1_Acceleration'!B31</f>
         <v>5.2470000000000003E-2</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38" s="6">
         <f>'2-1_Acceleration'!C31</f>
         <v>5.3900000000000003E-2</v>
       </c>
@@ -11523,24 +12205,24 @@
       <c r="A39">
         <v>0.78539816299999998</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="5">
         <v>8.2268566000000001E-2</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="5">
         <v>4.9343469000000001E-2</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="5">
         <v>8.4053220999999997E-2</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="6">
         <f>'2-1_Acceleration'!A32</f>
         <v>3.678E-2</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="6">
         <f>'2-1_Acceleration'!B32</f>
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39" s="6">
         <f>'2-1_Acceleration'!C32</f>
         <v>5.5100000000000003E-2</v>
       </c>
@@ -11561,24 +12243,24 @@
       <c r="A40">
         <v>0.87266462600000005</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="5">
         <v>8.3951696000000006E-2</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="5">
         <v>5.5538905999999999E-2</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="5">
         <v>8.6621157000000004E-2</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="6">
         <f>'2-1_Acceleration'!A33</f>
         <v>3.1719999999999998E-2</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="6">
         <f>'2-1_Acceleration'!B33</f>
         <v>6.1100000000000002E-2</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40" s="6">
         <f>'2-1_Acceleration'!C33</f>
         <v>6.164E-2</v>
       </c>
@@ -11599,24 +12281,24 @@
       <c r="A41">
         <v>0.95993108900000002</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="5">
         <v>8.8765075999999998E-2</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="5">
         <v>4.7363952000000001E-2</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="5">
         <v>9.0717792000000005E-2</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="6">
         <f>'2-1_Acceleration'!A34</f>
         <v>3.1949999999999999E-2</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="6">
         <f>'2-1_Acceleration'!B34</f>
         <v>6.404E-2</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41" s="6">
         <f>'2-1_Acceleration'!C34</f>
         <v>6.4899999999999999E-2</v>
       </c>
@@ -11637,24 +12319,24 @@
       <c r="A42">
         <v>1.047197551</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="5">
         <v>8.8701158000000002E-2</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="5">
         <v>5.1556794000000003E-2</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="5">
         <v>9.1220534000000006E-2</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="6">
         <f>'2-1_Acceleration'!A35</f>
         <v>3.3619999999999997E-2</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="6">
         <f>'2-1_Acceleration'!B35</f>
         <v>7.0550000000000002E-2</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42" s="6">
         <f>'2-1_Acceleration'!C35</f>
         <v>7.1510000000000004E-2</v>
       </c>
@@ -11675,24 +12357,24 @@
       <c r="A43">
         <v>1.134464014</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="5">
         <v>0.108524897</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="5">
         <v>5.3694586000000002E-2</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="5">
         <v>0.111301978</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="6">
         <f>'2-1_Acceleration'!A36</f>
         <v>3.0939999999999999E-2</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="6">
         <f>'2-1_Acceleration'!B36</f>
         <v>7.0150000000000004E-2</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43" s="6">
         <f>'2-1_Acceleration'!C36</f>
         <v>7.0870000000000002E-2</v>
       </c>
@@ -11713,24 +12395,24 @@
       <c r="A44">
         <v>1.2217304760000001</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="5">
         <v>0.102688188</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="5">
         <v>5.3583073000000002E-2</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="5">
         <v>0.107157216</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="6">
         <f>'2-1_Acceleration'!A37</f>
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="6">
         <f>'2-1_Acceleration'!B37</f>
         <v>6.5799999999999997E-2</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44" s="6">
         <f>'2-1_Acceleration'!C37</f>
         <v>6.6670000000000007E-2</v>
       </c>
@@ -11751,24 +12433,24 @@
       <c r="A45">
         <v>1.308996939</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="5">
         <v>0.117323212</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="5">
         <v>5.9746398999999999E-2</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="5">
         <v>0.122005851</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="6">
         <f>'2-1_Acceleration'!A38</f>
         <v>3.4660000000000003E-2</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="6">
         <f>'2-1_Acceleration'!B38</f>
         <v>8.1140000000000004E-2</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45" s="6">
         <f>'2-1_Acceleration'!C38</f>
         <v>8.201E-2</v>
       </c>
@@ -11789,24 +12471,24 @@
       <c r="A46">
         <v>1.396263402</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="5">
         <v>0.12884901300000001</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="5">
         <v>6.9169681999999996E-2</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="5">
         <v>0.135388114</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="6">
         <f>'2-1_Acceleration'!A39</f>
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="6">
         <f>'2-1_Acceleration'!B39</f>
         <v>8.5720000000000005E-2</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46" s="6">
         <f>'2-1_Acceleration'!C39</f>
         <v>8.6609999999999993E-2</v>
       </c>
@@ -11827,24 +12509,24 @@
       <c r="A47">
         <v>1.4835298640000001</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="5">
         <v>0.17299767199999999</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="5">
         <v>7.9331409000000006E-2</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="5">
         <v>0.182908398</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="6">
         <f>'2-1_Acceleration'!A40</f>
         <v>4.2610000000000002E-2</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="6">
         <f>'2-1_Acceleration'!B40</f>
         <v>8.7459999999999996E-2</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47" s="6">
         <f>'2-1_Acceleration'!C40</f>
         <v>8.8439999999999991E-2</v>
       </c>
@@ -11865,24 +12547,24 @@
       <c r="A48">
         <v>1.570796327</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="5">
         <v>0.16496813900000001</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="5">
         <v>8.6099365999999997E-2</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="5">
         <v>0.175746287</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="6">
         <f>'2-1_Acceleration'!A41</f>
         <v>4.4650000000000002E-2</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="6">
         <f>'2-1_Acceleration'!B41</f>
         <v>9.126999999999999E-2</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48" s="6">
         <f>'2-1_Acceleration'!C41</f>
         <v>9.2499999999999999E-2</v>
       </c>
@@ -11908,10 +12590,10 @@
       <c r="A56" t="s">
         <v>95</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="6" t="s">
         <v>97</v>
       </c>
       <c r="H56" t="s">
@@ -11922,22 +12604,22 @@
       <c r="A57" t="s">
         <v>99</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D57" s="7" t="s">
+      <c r="D57" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="F57" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H57" t="s">
@@ -11954,24 +12636,24 @@
       <c r="A58">
         <v>0</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="5">
         <v>0.131909159254782</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C58" s="5">
         <v>5.8929978706446999E-2</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="5">
         <v>0.13358617856798699</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="6">
         <f>'3-1_Acceleration'!A23</f>
         <v>4.8039999999999999E-2</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="6">
         <f>'3-1_Acceleration'!B23</f>
         <v>8.0260000000000012E-2</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58" s="6">
         <f>'3-1_Acceleration'!C23</f>
         <v>8.0590000000000009E-2</v>
       </c>
@@ -11992,24 +12674,24 @@
       <c r="A59">
         <v>8.7266463000000002E-2</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="5">
         <v>0.12898370366826101</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="5">
         <v>5.1537770390811401E-2</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="5">
         <v>0.12966659916158399</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="6">
         <f>'3-1_Acceleration'!A24</f>
         <v>4.6510000000000003E-2</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="6">
         <f>'3-1_Acceleration'!B24</f>
         <v>7.9150000000000012E-2</v>
       </c>
-      <c r="G59" s="8">
+      <c r="G59" s="6">
         <f>'3-1_Acceleration'!C24</f>
         <v>7.9439999999999997E-2</v>
       </c>
@@ -12030,24 +12712,24 @@
       <c r="A60">
         <v>0.17453292500000001</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="5">
         <v>0.118551883928231</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="5">
         <v>5.8047353042828001E-2</v>
       </c>
-      <c r="D60" s="7">
+      <c r="D60" s="5">
         <v>0.119775740231519</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="6">
         <f>'3-1_Acceleration'!A25</f>
         <v>4.6549999999999987E-2</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="6">
         <f>'3-1_Acceleration'!B25</f>
         <v>7.3849999999999999E-2</v>
       </c>
-      <c r="G60" s="8">
+      <c r="G60" s="6">
         <f>'3-1_Acceleration'!C25</f>
         <v>7.443000000000001E-2</v>
       </c>
@@ -12068,24 +12750,24 @@
       <c r="A61">
         <v>0.26179938800000002</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="5">
         <v>0.12546483785543</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="5">
         <v>5.7835183041979599E-2</v>
       </c>
-      <c r="D61" s="7">
+      <c r="D61" s="5">
         <v>0.12658099419575999</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="6">
         <f>'3-1_Acceleration'!A26</f>
         <v>4.5539999999999997E-2</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="6">
         <f>'3-1_Acceleration'!B26</f>
         <v>7.7959999999999988E-2</v>
       </c>
-      <c r="G61" s="8">
+      <c r="G61" s="6">
         <f>'3-1_Acceleration'!C26</f>
         <v>7.8400000000000011E-2</v>
       </c>
@@ -12106,24 +12788,24 @@
       <c r="A62">
         <v>0.34906585000000001</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="5">
         <v>0.109851110046099</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="5">
         <v>5.5763385548076499E-2</v>
       </c>
-      <c r="D62" s="7">
+      <c r="D62" s="5">
         <v>0.11101559533019099</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="6">
         <f>'3-1_Acceleration'!A27</f>
         <v>4.4420000000000001E-2</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="6">
         <f>'3-1_Acceleration'!B27</f>
         <v>7.6219999999999996E-2</v>
       </c>
-      <c r="G62" s="8">
+      <c r="G62" s="6">
         <f>'3-1_Acceleration'!C27</f>
         <v>7.664E-2</v>
       </c>
@@ -12144,24 +12826,24 @@
       <c r="A63">
         <v>0.43633231300000003</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="5">
         <v>0.103682403408451</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="5">
         <v>5.3359426887002501E-2</v>
       </c>
-      <c r="D63" s="7">
+      <c r="D63" s="5">
         <v>0.10498600694860399</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="6">
         <f>'3-1_Acceleration'!A28</f>
         <v>4.1149999999999999E-2</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="6">
         <f>'3-1_Acceleration'!B28</f>
         <v>6.4019999999999994E-2</v>
       </c>
-      <c r="G63" s="8">
+      <c r="G63" s="6">
         <f>'3-1_Acceleration'!C28</f>
         <v>6.4299999999999996E-2</v>
       </c>
@@ -12182,24 +12864,24 @@
       <c r="A64">
         <v>0.52359877600000004</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="5">
         <v>9.5155221765517495E-2</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="5">
         <v>4.4559973968942103E-2</v>
       </c>
-      <c r="D64" s="7">
+      <c r="D64" s="5">
         <v>9.6144885824918702E-2</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="6">
         <f>'3-1_Acceleration'!A29</f>
         <v>3.7350000000000001E-2</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="6">
         <f>'3-1_Acceleration'!B29</f>
         <v>6.0339999999999998E-2</v>
       </c>
-      <c r="G64" s="8">
+      <c r="G64" s="6">
         <f>'3-1_Acceleration'!C29</f>
         <v>6.062E-2</v>
       </c>
@@ -12220,24 +12902,24 @@
       <c r="A65">
         <v>0.61086523800000003</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="5">
         <v>9.6461739738963298E-2</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="5">
         <v>4.1297125367470301E-2</v>
       </c>
-      <c r="D65" s="7">
+      <c r="D65" s="5">
         <v>9.7416716702063103E-2</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="6">
         <f>'3-1_Acceleration'!A30</f>
         <v>3.3320000000000002E-2</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="6">
         <f>'3-1_Acceleration'!B30</f>
         <v>4.931E-2</v>
       </c>
-      <c r="G65" s="8">
+      <c r="G65" s="6">
         <f>'3-1_Acceleration'!C30</f>
         <v>4.9529999999999998E-2</v>
       </c>
@@ -12258,24 +12940,24 @@
       <c r="A66">
         <v>0.69813170099999999</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="5">
         <v>8.6638852201837396E-2</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="5">
         <v>4.1365270696212902E-2</v>
       </c>
-      <c r="D66" s="7">
+      <c r="D66" s="5">
         <v>8.7891175624806597E-2</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="6">
         <f>'3-1_Acceleration'!A31</f>
         <v>3.0329999999999999E-2</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="6">
         <f>'3-1_Acceleration'!B31</f>
         <v>5.5010000000000003E-2</v>
       </c>
-      <c r="G66" s="8">
+      <c r="G66" s="6">
         <f>'3-1_Acceleration'!C31</f>
         <v>5.525E-2</v>
       </c>
@@ -12296,24 +12978,24 @@
       <c r="A67">
         <v>0.78539816299999998</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="5">
         <v>8.3705154307353202E-2</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="5">
         <v>3.8890644140651999E-2</v>
       </c>
-      <c r="D67" s="7">
+      <c r="D67" s="5">
         <v>8.5070690443153699E-2</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="6">
         <f>'3-1_Acceleration'!A32</f>
         <v>2.8639999999999999E-2</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="6">
         <f>'3-1_Acceleration'!B32</f>
         <v>4.6330000000000003E-2</v>
       </c>
-      <c r="G67" s="8">
+      <c r="G67" s="6">
         <f>'3-1_Acceleration'!C32</f>
         <v>4.675E-2</v>
       </c>
@@ -12334,24 +13016,24 @@
       <c r="A68">
         <v>0.87266462600000005</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="5">
         <v>7.7279307898750899E-2</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="5">
         <v>3.7674369178060801E-2</v>
       </c>
-      <c r="D68" s="7">
+      <c r="D68" s="5">
         <v>7.87923861843388E-2</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="6">
         <f>'3-1_Acceleration'!A33</f>
         <v>2.4250000000000001E-2</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="6">
         <f>'3-1_Acceleration'!B33</f>
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="6">
         <f>'3-1_Acceleration'!C33</f>
         <v>4.8149999999999998E-2</v>
       </c>
@@ -12372,24 +13054,24 @@
       <c r="A69">
         <v>0.95993108900000002</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="5">
         <v>8.5003022373929496E-2</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="5">
         <v>3.7717864736939499E-2</v>
       </c>
-      <c r="D69" s="7">
+      <c r="D69" s="5">
         <v>8.65759036183254E-2</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="6">
         <f>'3-1_Acceleration'!A34</f>
         <v>2.359E-2</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="6">
         <f>'3-1_Acceleration'!B34</f>
         <v>4.8500000000000001E-2</v>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="6">
         <f>'3-1_Acceleration'!C34</f>
         <v>4.8800000000000003E-2</v>
       </c>
@@ -12410,24 +13092,24 @@
       <c r="A70">
         <v>1.047197551</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="5">
         <v>8.4245058862609107E-2</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="5">
         <v>3.4952894680732503E-2</v>
       </c>
-      <c r="D70" s="7">
+      <c r="D70" s="5">
         <v>8.5811466447113696E-2</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="6">
         <f>'3-1_Acceleration'!A35</f>
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="6">
         <f>'3-1_Acceleration'!B35</f>
         <v>5.4479999999999987E-2</v>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="6">
         <f>'3-1_Acceleration'!C35</f>
         <v>5.4739999999999997E-2</v>
       </c>
@@ -12448,24 +13130,24 @@
       <c r="A71">
         <v>1.134464014</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="5">
         <v>8.8504795253157895E-2</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="5">
         <v>3.5459123608468097E-2</v>
       </c>
-      <c r="D71" s="7">
+      <c r="D71" s="5">
         <v>8.9834381647751704E-2</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="6">
         <f>'3-1_Acceleration'!A36</f>
         <v>2.4709999999999999E-2</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="6">
         <f>'3-1_Acceleration'!B36</f>
         <v>5.203E-2</v>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="6">
         <f>'3-1_Acceleration'!C36</f>
         <v>5.2260000000000001E-2</v>
       </c>
@@ -12486,24 +13168,24 @@
       <c r="A72">
         <v>1.2217304760000001</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="5">
         <v>8.61500564074833E-2</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="5">
         <v>4.0025310074388198E-2</v>
       </c>
-      <c r="D72" s="7">
+      <c r="D72" s="5">
         <v>8.7846676258970594E-2</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="6">
         <f>'3-1_Acceleration'!A37</f>
         <v>2.1440000000000001E-2</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="6">
         <f>'3-1_Acceleration'!B37</f>
         <v>5.2499999999999998E-2</v>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="6">
         <f>'3-1_Acceleration'!C37</f>
         <v>5.2760000000000001E-2</v>
       </c>
@@ -12524,24 +13206,24 @@
       <c r="A73">
         <v>1.308996939</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="5">
         <v>9.81709786644379E-2</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="5">
         <v>4.0218462935227503E-2</v>
       </c>
-      <c r="D73" s="7">
+      <c r="D73" s="5">
         <v>0.100015712124532</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="6">
         <f>'3-1_Acceleration'!A38</f>
         <v>2.8510000000000001E-2</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="6">
         <f>'3-1_Acceleration'!B38</f>
         <v>6.1899999999999997E-2</v>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="6">
         <f>'3-1_Acceleration'!C38</f>
         <v>6.2170000000000003E-2</v>
       </c>
@@ -12562,24 +13244,24 @@
       <c r="A74">
         <v>1.396263402</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="5">
         <v>0.118880303918294</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="5">
         <v>4.4338198993811397E-2</v>
       </c>
-      <c r="D74" s="7">
+      <c r="D74" s="5">
         <v>0.120565536929489</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="6">
         <f>'3-1_Acceleration'!A39</f>
         <v>2.7699999999999999E-2</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="6">
         <f>'3-1_Acceleration'!B39</f>
         <v>8.020999999999999E-2</v>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="6">
         <f>'3-1_Acceleration'!C39</f>
         <v>8.0599999999999991E-2</v>
       </c>
@@ -12600,24 +13282,24 @@
       <c r="A75">
         <v>1.4835298640000001</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="5">
         <v>0.110334335989004</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="5">
         <v>4.6123161941655499E-2</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="5">
         <v>0.112551701534839</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="6">
         <f>'3-1_Acceleration'!A40</f>
         <v>2.802E-2</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="6">
         <f>'3-1_Acceleration'!B40</f>
         <v>7.5379999999999989E-2</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="6">
         <f>'3-1_Acceleration'!C40</f>
         <v>7.578E-2</v>
       </c>
@@ -12638,24 +13320,24 @@
       <c r="A76">
         <v>1.570796327</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="5">
         <v>0.12877187494522599</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="5">
         <v>4.5901941428107697E-2</v>
       </c>
-      <c r="D76" s="7">
+      <c r="D76" s="5">
         <v>0.13088670980851999</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="6">
         <f>'3-1_Acceleration'!A41</f>
         <v>2.9929999999999998E-2</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="6">
         <f>'3-1_Acceleration'!B41</f>
         <v>9.1569999999999999E-2</v>
       </c>
-      <c r="G76" s="8">
+      <c r="G76" s="6">
         <f>'3-1_Acceleration'!C41</f>
         <v>9.1980000000000006E-2</v>
       </c>
@@ -12672,11 +13354,174 @@
         <v>-0.29725485395299756</v>
       </c>
     </row>
+    <row r="80" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="81" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="34" t="s">
+        <v>115</v>
+      </c>
+      <c r="B81" s="34"/>
+      <c r="C81" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="D81" s="34"/>
+      <c r="E81" s="34"/>
+      <c r="F81" s="34"/>
+      <c r="G81" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="H81" s="36"/>
+      <c r="I81" s="34" t="s">
+        <v>118</v>
+      </c>
+      <c r="J81" s="34"/>
+      <c r="K81" s="34"/>
+    </row>
+    <row r="82" spans="1:11" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="35"/>
+      <c r="B82" s="35"/>
+      <c r="C82" s="29" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D82" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E82" s="30" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F82" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G82" s="29" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H82" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="I82" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="J82" s="35"/>
+      <c r="K82" s="31" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="B83" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="C83" s="27">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E83" s="27">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="F83" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="G83" s="27">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="H83" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="I83" s="37">
+        <f>(G83-C83)/C83*100</f>
+        <v>5.7971014492753472</v>
+      </c>
+      <c r="J83" s="38">
+        <f>(G83-E83)/E83*100</f>
+        <v>0.68965517241379382</v>
+      </c>
+      <c r="K83" s="38"/>
+    </row>
+    <row r="84" spans="1:11" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B84" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C84" s="27">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="D84" s="27">
+        <v>10</v>
+      </c>
+      <c r="E84" s="27">
+        <v>0.09</v>
+      </c>
+      <c r="F84" s="27">
+        <v>15</v>
+      </c>
+      <c r="G84" s="27">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="H84" s="27">
+        <v>90</v>
+      </c>
+      <c r="I84" s="37">
+        <f t="shared" ref="I84:I85" si="9">(G84-C84)/C84*100</f>
+        <v>10.714285714285706</v>
+      </c>
+      <c r="J84" s="38">
+        <f>(G84-E84)/E84*100</f>
+        <v>3.3333333333333366</v>
+      </c>
+      <c r="K84" s="38"/>
+    </row>
+    <row r="85" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="32"/>
+      <c r="B85" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C85" s="33">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="D85" s="33">
+        <v>90</v>
+      </c>
+      <c r="E85" s="33">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="F85" s="33">
+        <v>90</v>
+      </c>
+      <c r="G85" s="33">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="H85" s="33">
+        <v>90</v>
+      </c>
+      <c r="I85" s="37">
+        <f t="shared" si="9"/>
+        <v>27.777777777777786</v>
+      </c>
+      <c r="J85" s="38">
+        <f>(G85-E85)/E85*100</f>
+        <v>0</v>
+      </c>
+      <c r="K85" s="38"/>
+    </row>
+    <row r="86" spans="1:11" ht="15" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="11">
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="J85:K85"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A81:B82"/>
+    <mergeCell ref="C81:F81"/>
+    <mergeCell ref="G81:H81"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I82:J82"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12689,1170 +13534,1207 @@
   <dimension ref="A1:Y57"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="8.88671875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="8.88671875" style="2"/>
-    <col min="19" max="19" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.88671875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="8.88671875" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:25" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="26"/>
+      <c r="G2" s="8"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="25"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="O2" s="26"/>
+      <c r="P2" s="8"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="U2" s="25"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="8"/>
+    </row>
+    <row r="3" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="C3" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="S1" s="26" t="s">
+      <c r="D3" s="11" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" s="25"/>
-      <c r="G2" s="16"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="O2" s="25"/>
-      <c r="P2" s="16"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="U2" s="23"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="24" t="s">
-        <v>106</v>
-      </c>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="16"/>
-    </row>
-    <row r="3" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="19" t="s">
+      <c r="K3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="O3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="P3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="S3" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="P3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="S3" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="T3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="U3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="V3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="W3" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="X3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="Y3" s="19" t="s">
-        <v>110</v>
+      <c r="T3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="U3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="V3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="W3" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="X3" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y3" s="11" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="A4" s="3">
         <v>200</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="4">
         <v>5410</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>5550</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="4">
         <f>(C4-B4)/B4</f>
         <v>2.5878003696857672E-2</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="4">
         <v>6.07</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="12">
         <v>6.81</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="4">
         <f>(F4-E4)/E4</f>
         <v>0.12191103789126842</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="3">
         <v>200</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="4">
+        <v>3690</v>
+      </c>
+      <c r="L4" s="4">
+        <v>3790</v>
+      </c>
+      <c r="M4" s="4">
+        <f>(L4-K4)/K4</f>
+        <v>2.7100271002710029E-2</v>
+      </c>
+      <c r="N4" s="4">
+        <v>5.97</v>
+      </c>
+      <c r="O4" s="12">
+        <v>6.6334359999999997</v>
+      </c>
+      <c r="P4" s="4">
+        <f>(O4-N4)/N4</f>
+        <v>0.11112830820770518</v>
+      </c>
+      <c r="S4" s="3">
+        <v>200</v>
+      </c>
+      <c r="T4" s="4">
         <v>5410</v>
       </c>
-      <c r="L4" s="6">
+      <c r="U4" s="4">
         <v>5550</v>
       </c>
-      <c r="M4" s="6">
-        <f>(L4-K4)/K4</f>
-        <v>2.5878003696857672E-2</v>
-      </c>
-      <c r="N4" s="6">
-        <v>6.07</v>
-      </c>
-      <c r="O4" s="20">
-        <v>6.81</v>
-      </c>
-      <c r="P4" s="6">
-        <f>(O4-N4)/N4</f>
-        <v>0.12191103789126842</v>
-      </c>
-      <c r="S4" s="5">
-        <v>200</v>
-      </c>
-      <c r="T4" s="6">
-        <v>5410</v>
-      </c>
-      <c r="U4" s="6">
-        <v>5550</v>
-      </c>
-      <c r="V4" s="6">
+      <c r="V4" s="4">
         <f>(U4-T4)/T4</f>
         <v>2.5878003696857672E-2</v>
       </c>
-      <c r="W4" s="6">
+      <c r="W4" s="4">
         <v>6.07</v>
       </c>
-      <c r="X4" s="20">
+      <c r="X4" s="12">
         <v>6.7639079999999998</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Y4" s="4">
         <f>(X4-W4)/W4</f>
         <v>0.11431762767710041</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="3">
         <v>196.15</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="4">
         <v>5410</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>5550</v>
       </c>
-      <c r="D5" s="6">
-        <f t="shared" ref="D5:D8" si="0">(C5-B5)/B5</f>
+      <c r="D5" s="4">
+        <f>(C5-B5)/B5</f>
         <v>2.5878003696857672E-2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>5.35</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="12">
         <v>5.67</v>
       </c>
-      <c r="G5" s="6">
-        <f t="shared" ref="G5:G8" si="1">(F5-E5)/E5</f>
+      <c r="G5" s="4">
+        <f>(F5-E5)/E5</f>
         <v>5.9813084112149591E-2</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="3">
         <v>196</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
+        <v>3690</v>
+      </c>
+      <c r="L5" s="4">
+        <v>3790</v>
+      </c>
+      <c r="M5" s="4">
+        <f>(L5-K5)/K5</f>
+        <v>2.7100271002710029E-2</v>
+      </c>
+      <c r="N5" s="4">
+        <v>5.4</v>
+      </c>
+      <c r="O5" s="12">
+        <v>5.7319680000000002</v>
+      </c>
+      <c r="P5" s="4">
+        <f>(O5-N5)/N5</f>
+        <v>6.1475555555555519E-2</v>
+      </c>
+      <c r="S5" s="3">
+        <v>196</v>
+      </c>
+      <c r="T5" s="4">
         <v>5410</v>
       </c>
-      <c r="L5" s="6">
+      <c r="U5" s="4">
         <v>5550</v>
       </c>
-      <c r="M5" s="6">
-        <f t="shared" ref="M5:M8" si="2">(L5-K5)/K5</f>
+      <c r="V5" s="4">
+        <f>(U5-T5)/T5</f>
         <v>2.5878003696857672E-2</v>
       </c>
-      <c r="N5" s="6">
+      <c r="W5" s="4">
         <v>5.35</v>
       </c>
-      <c r="O5" s="20">
-        <v>5.67</v>
-      </c>
-      <c r="P5" s="6">
-        <f t="shared" ref="P5:P8" si="3">(O5-N5)/N5</f>
-        <v>5.9813084112149591E-2</v>
-      </c>
-      <c r="S5" s="5">
-        <v>196</v>
-      </c>
-      <c r="T5" s="6">
-        <v>5410</v>
-      </c>
-      <c r="U5" s="6">
+      <c r="X5" s="12">
+        <v>5.626493</v>
+      </c>
+      <c r="Y5" s="4">
+        <f>(X5-W5)/W5</f>
+        <v>5.1680934579439314E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>192.3</v>
+      </c>
+      <c r="B6" s="4">
+        <v>7620000</v>
+      </c>
+      <c r="C6" s="4">
+        <v>7850000</v>
+      </c>
+      <c r="D6" s="4">
+        <f>(C6-B6)/B6</f>
+        <v>3.0183727034120734E-2</v>
+      </c>
+      <c r="E6" s="4">
+        <v>4.82</v>
+      </c>
+      <c r="F6" s="12">
+        <v>5.16</v>
+      </c>
+      <c r="G6" s="4">
+        <f>(F6-E6)/E6</f>
+        <v>7.0539419087136901E-2</v>
+      </c>
+      <c r="J6" s="3">
+        <v>192</v>
+      </c>
+      <c r="K6" s="4">
+        <v>2630000</v>
+      </c>
+      <c r="L6" s="4">
+        <v>2710000</v>
+      </c>
+      <c r="M6" s="4">
+        <f>(L6-K6)/K6</f>
+        <v>3.0418250950570342E-2</v>
+      </c>
+      <c r="N6" s="4">
+        <v>4.92</v>
+      </c>
+      <c r="O6" s="12">
+        <v>5.3447889999999996</v>
+      </c>
+      <c r="P6" s="4">
+        <f>(O6-N6)/N6</f>
+        <v>8.6339227642276348E-2</v>
+      </c>
+      <c r="S6" s="3">
+        <v>192</v>
+      </c>
+      <c r="T6" s="4">
+        <v>7620000</v>
+      </c>
+      <c r="U6" s="4">
+        <v>7850000</v>
+      </c>
+      <c r="V6" s="4">
+        <f>(U6-T6)/T6</f>
+        <v>3.0183727034120734E-2</v>
+      </c>
+      <c r="W6" s="4">
+        <v>4.82</v>
+      </c>
+      <c r="X6" s="12">
+        <v>5.1222390000000004</v>
+      </c>
+      <c r="Y6" s="4">
+        <f>(X6-W6)/W6</f>
+        <v>6.2705186721991726E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>188.7</v>
+      </c>
+      <c r="B7" s="4">
+        <v>5630</v>
+      </c>
+      <c r="C7" s="4">
         <v>5550</v>
       </c>
-      <c r="V5" s="6">
-        <f t="shared" ref="V5:V8" si="4">(U5-T5)/T5</f>
-        <v>2.5878003696857672E-2</v>
-      </c>
-      <c r="W5" s="6">
-        <v>5.35</v>
-      </c>
-      <c r="X5" s="20">
-        <v>5.626493</v>
-      </c>
-      <c r="Y5" s="6">
-        <f t="shared" ref="Y5:Y8" si="5">(X5-W5)/W5</f>
-        <v>5.1680934579439314E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
-        <v>192.3</v>
-      </c>
-      <c r="B6" s="6">
-        <v>7620000</v>
-      </c>
-      <c r="C6" s="6">
-        <v>7850000</v>
-      </c>
-      <c r="D6" s="6">
-        <f t="shared" si="0"/>
-        <v>3.0183727034120734E-2</v>
-      </c>
-      <c r="E6" s="6">
-        <v>4.82</v>
-      </c>
-      <c r="F6" s="20">
-        <v>5.16</v>
-      </c>
-      <c r="G6" s="6">
-        <f t="shared" si="1"/>
-        <v>7.0539419087136901E-2</v>
-      </c>
-      <c r="J6" s="5">
-        <v>192</v>
-      </c>
-      <c r="K6" s="6">
-        <v>7620000</v>
-      </c>
-      <c r="L6" s="6">
-        <v>7850000</v>
-      </c>
-      <c r="M6" s="6">
-        <f t="shared" si="2"/>
-        <v>3.0183727034120734E-2</v>
-      </c>
-      <c r="N6" s="6">
-        <v>4.82</v>
-      </c>
-      <c r="O6" s="20">
-        <v>5.16</v>
-      </c>
-      <c r="P6" s="6">
-        <f t="shared" si="3"/>
-        <v>7.0539419087136901E-2</v>
-      </c>
-      <c r="S6" s="5">
-        <v>192</v>
-      </c>
-      <c r="T6" s="6">
-        <v>7620000</v>
-      </c>
-      <c r="U6" s="6">
-        <v>7850000</v>
-      </c>
-      <c r="V6" s="6">
-        <f t="shared" si="4"/>
-        <v>3.0183727034120734E-2</v>
-      </c>
-      <c r="W6" s="6">
-        <v>4.82</v>
-      </c>
-      <c r="X6" s="20">
-        <v>5.1222390000000004</v>
-      </c>
-      <c r="Y6" s="6">
-        <f t="shared" si="5"/>
-        <v>6.2705186721991726E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
-        <v>188.7</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="D7" s="4">
+        <f>(C7-B7)/B7</f>
+        <v>-1.4209591474245116E-2</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1.96</v>
+      </c>
+      <c r="F7" s="12">
+        <v>2.17</v>
+      </c>
+      <c r="G7" s="4">
+        <f>(F7-E7)/E7</f>
+        <v>0.10714285714285712</v>
+      </c>
+      <c r="J7" s="3">
+        <v>189</v>
+      </c>
+      <c r="K7" s="4">
+        <v>3850</v>
+      </c>
+      <c r="L7" s="4">
+        <v>3790</v>
+      </c>
+      <c r="M7" s="4">
+        <f>(L7-K7)/K7</f>
+        <v>-1.5584415584415584E-2</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1.94</v>
+      </c>
+      <c r="O7" s="12">
+        <v>2.1333700000000002</v>
+      </c>
+      <c r="P7" s="4">
+        <f>(O7-N7)/N7</f>
+        <v>9.9675257731958899E-2</v>
+      </c>
+      <c r="S7" s="3">
+        <v>189</v>
+      </c>
+      <c r="T7" s="4">
         <v>5630</v>
       </c>
-      <c r="C7" s="6">
+      <c r="U7" s="4">
         <v>5550</v>
       </c>
-      <c r="D7" s="6">
-        <f t="shared" si="0"/>
+      <c r="V7" s="4">
+        <f>(U7-T7)/T7</f>
         <v>-1.4209591474245116E-2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="W7" s="4">
         <v>1.96</v>
       </c>
-      <c r="F7" s="20">
-        <v>2.17</v>
-      </c>
-      <c r="G7" s="6">
-        <f t="shared" si="1"/>
-        <v>0.10714285714285712</v>
-      </c>
-      <c r="J7" s="5">
-        <v>189</v>
-      </c>
-      <c r="K7" s="6">
+      <c r="X7" s="12">
+        <v>2.157667</v>
+      </c>
+      <c r="Y7" s="4">
+        <f>(X7-W7)/W7</f>
+        <v>0.10085051020408166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>185.1</v>
+      </c>
+      <c r="B8" s="4">
         <v>5630</v>
       </c>
-      <c r="L7" s="6">
+      <c r="C8" s="4">
         <v>5550</v>
       </c>
-      <c r="M7" s="6">
-        <f t="shared" si="2"/>
+      <c r="D8" s="4">
+        <f>(C8-B8)/B8</f>
         <v>-1.4209591474245116E-2</v>
       </c>
-      <c r="N7" s="6">
-        <v>1.96</v>
-      </c>
-      <c r="O7" s="20">
-        <v>2.17</v>
-      </c>
-      <c r="P7" s="6">
-        <f t="shared" si="3"/>
-        <v>0.10714285714285712</v>
-      </c>
-      <c r="S7" s="5">
-        <v>189</v>
-      </c>
-      <c r="T7" s="6">
+      <c r="E8" s="4">
+        <v>1.56</v>
+      </c>
+      <c r="F8" s="12">
+        <v>1.66</v>
+      </c>
+      <c r="G8" s="4">
+        <f>(F8-E8)/E8</f>
+        <v>6.4102564102564014E-2</v>
+      </c>
+      <c r="J8" s="3">
+        <v>185</v>
+      </c>
+      <c r="K8" s="4">
+        <v>3850</v>
+      </c>
+      <c r="L8" s="4">
+        <v>3790</v>
+      </c>
+      <c r="M8" s="4">
+        <f>(L8-K8)/K8</f>
+        <v>-1.5584415584415584E-2</v>
+      </c>
+      <c r="N8" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="O8" s="12">
+        <v>1.714777</v>
+      </c>
+      <c r="P8" s="4">
+        <f>(O8-N8)/N8</f>
+        <v>7.1735624999999942E-2</v>
+      </c>
+      <c r="S8" s="3">
+        <v>185</v>
+      </c>
+      <c r="T8" s="4">
         <v>5630</v>
       </c>
-      <c r="U7" s="6">
+      <c r="U8" s="4">
         <v>5550</v>
       </c>
-      <c r="V7" s="6">
-        <f t="shared" si="4"/>
+      <c r="V8" s="4">
+        <f>(U8-T8)/T8</f>
         <v>-1.4209591474245116E-2</v>
       </c>
-      <c r="W7" s="6">
-        <v>1.96</v>
-      </c>
-      <c r="X7" s="20">
-        <v>2.157667</v>
-      </c>
-      <c r="Y7" s="6">
-        <f t="shared" si="5"/>
-        <v>0.10085051020408166</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
-        <v>185.1</v>
-      </c>
-      <c r="B8" s="6">
-        <v>5630</v>
-      </c>
-      <c r="C8" s="6">
-        <v>5550</v>
-      </c>
-      <c r="D8" s="6">
-        <f t="shared" si="0"/>
-        <v>-1.4209591474245116E-2</v>
-      </c>
-      <c r="E8" s="6">
+      <c r="W8" s="4">
         <v>1.56</v>
       </c>
-      <c r="F8" s="20">
-        <v>1.66</v>
-      </c>
-      <c r="G8" s="6">
-        <f t="shared" si="1"/>
-        <v>6.4102564102564014E-2</v>
-      </c>
-      <c r="J8" s="5">
-        <v>185</v>
-      </c>
-      <c r="K8" s="6">
-        <v>5630</v>
-      </c>
-      <c r="L8" s="6">
-        <v>5550</v>
-      </c>
-      <c r="M8" s="6">
-        <f t="shared" si="2"/>
-        <v>-1.4209591474245116E-2</v>
-      </c>
-      <c r="N8" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="O8" s="20">
-        <v>1.66</v>
-      </c>
-      <c r="P8" s="6">
-        <f t="shared" si="3"/>
-        <v>6.4102564102564014E-2</v>
-      </c>
-      <c r="S8" s="5">
-        <v>185</v>
-      </c>
-      <c r="T8" s="6">
-        <v>5630</v>
-      </c>
-      <c r="U8" s="6">
-        <v>5550</v>
-      </c>
-      <c r="V8" s="6">
-        <f t="shared" si="4"/>
-        <v>-1.4209591474245116E-2</v>
-      </c>
-      <c r="W8" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="X8" s="20">
+      <c r="X8" s="12">
         <v>1.638884</v>
       </c>
-      <c r="Y8" s="6">
-        <f t="shared" si="5"/>
+      <c r="Y8" s="4">
+        <f>(X8-W8)/W8</f>
         <v>5.0566666666666635E-2</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="3">
         <v>181.5</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="18"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="18">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="J9" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10">
+        <v>1.678949</v>
+      </c>
+      <c r="P9" s="10"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10">
         <v>1.5492619999999999</v>
       </c>
-      <c r="Y9" s="18"/>
+      <c r="Y9" s="10"/>
     </row>
     <row r="10" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="3">
         <v>177.9</v>
       </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="J10" s="5">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="J10" s="3">
         <v>23.1</v>
       </c>
-      <c r="K10" s="18"/>
-      <c r="L10" s="18"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="S10" s="5">
+      <c r="K10" s="16">
+        <v>5260</v>
+      </c>
+      <c r="L10" s="10"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10">
+        <v>1.143043</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="S10" s="3">
         <v>23.1</v>
       </c>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="18">
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="14"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10">
         <v>1.1317919999999999</v>
       </c>
-      <c r="Y10" s="18"/>
+      <c r="Y10" s="10"/>
     </row>
     <row r="11" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="A11" s="3">
         <v>174.3</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="J11" s="5">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="J11" s="3">
         <v>19.5</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="S11" s="5">
+      <c r="K11" s="16">
+        <v>3680000</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10">
+        <v>0.88116899999999998</v>
+      </c>
+      <c r="P11" s="10"/>
+      <c r="S11" s="3">
         <v>19.5</v>
       </c>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="18">
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="14"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10">
         <v>0.77513299999999996</v>
       </c>
-      <c r="Y11" s="18"/>
+      <c r="Y11" s="10"/>
     </row>
     <row r="12" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="A12" s="3">
         <v>170.7</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="J12" s="5">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="J12" s="3">
         <v>15</v>
       </c>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="S12" s="5">
+      <c r="K12" s="16">
+        <v>5720</v>
+      </c>
+      <c r="L12" s="10"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10">
+        <v>0.828851</v>
+      </c>
+      <c r="P12" s="10"/>
+      <c r="S12" s="3">
         <v>15</v>
       </c>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="18"/>
-      <c r="X12" s="18">
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="14"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10">
         <v>0.73757700000000004</v>
       </c>
-      <c r="Y12" s="18"/>
-    </row>
-    <row r="13" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="Y12" s="10"/>
+    </row>
+    <row r="13" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
         <v>167.1</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="J13" s="5">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="J13" s="3">
         <v>10.5</v>
       </c>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="S13" s="5">
+      <c r="K13" s="16">
+        <v>5720</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10">
+        <v>0.72556299999999996</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="S13" s="3">
         <v>10.5</v>
       </c>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="18">
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="14"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10">
         <v>0.71250800000000003</v>
       </c>
-      <c r="Y13" s="18"/>
-    </row>
-    <row r="14" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+      <c r="Y13" s="10"/>
+    </row>
+    <row r="14" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
         <v>163.5</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="J14" s="5">
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="J14" s="3">
         <v>6</v>
       </c>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="S14" s="5">
+      <c r="K14" s="16">
+        <v>3960000</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="14"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10">
+        <v>0.55391000000000001</v>
+      </c>
+      <c r="P14" s="10"/>
+      <c r="S14" s="3">
         <v>6</v>
       </c>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="18"/>
-      <c r="X14" s="18">
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="14"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10">
         <v>0.495201</v>
       </c>
-      <c r="Y14" s="18"/>
-    </row>
-    <row r="15" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="Y14" s="10"/>
+    </row>
+    <row r="15" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
         <v>159.9</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="X15" s="2">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="O15" s="1">
+        <v>0.507108</v>
+      </c>
+      <c r="X15" s="1">
         <v>0.47172199999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+    <row r="16" spans="1:25" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
         <v>156.30000000000001</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="X16" s="2">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="O16" s="1">
+        <v>0.50588299999999997</v>
+      </c>
+      <c r="X16" s="1">
         <v>0.45078200000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+    <row r="17" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
         <v>152.69999999999999</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="X17" s="2">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="O17" s="1">
+        <v>0.38777600000000001</v>
+      </c>
+      <c r="X17" s="1">
         <v>0.36887300000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+    <row r="18" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
         <v>149.1</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="X18" s="2">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="O18" s="1">
+        <v>0.37728699999999998</v>
+      </c>
+      <c r="X18" s="1">
         <v>0.32694499999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+    <row r="19" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
         <v>145.5</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
         <v>141.9</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
         <v>138.30000000000001</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
         <v>134.69999999999999</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
         <v>131.1</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
         <v>127.5</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
         <v>123.9</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-    </row>
-    <row r="26" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
         <v>120.3</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
         <v>116.7</v>
       </c>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-    </row>
-    <row r="28" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
         <v>113.1</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-    </row>
-    <row r="29" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
         <v>109.5</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="30" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
         <v>105.9</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-    </row>
-    <row r="31" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
         <v>102.3</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="32" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="5">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="1:24" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
         <v>98.7</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-    </row>
-    <row r="33" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
         <v>95.1</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="34" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
         <v>91.5</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="5">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
         <v>87.9</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-    </row>
-    <row r="36" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="5">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
         <v>84.3</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
         <v>80.7</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-    </row>
-    <row r="38" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+    </row>
+    <row r="38" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
         <v>77.099999999999994</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-    </row>
-    <row r="39" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="5">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
         <v>73.5</v>
       </c>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="40" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+    </row>
+    <row r="40" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
         <v>69.900000000000006</v>
       </c>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="5">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
         <v>66.3</v>
       </c>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-    </row>
-    <row r="42" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+    </row>
+    <row r="42" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
         <v>62.7</v>
       </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="5">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
         <v>59.1</v>
       </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-    </row>
-    <row r="44" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+    </row>
+    <row r="44" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
         <v>55.5</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-    </row>
-    <row r="45" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+    </row>
+    <row r="45" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
         <v>51.9</v>
       </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-    </row>
-    <row r="46" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="5">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+    </row>
+    <row r="46" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
         <v>48.3</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="47" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="5">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+    </row>
+    <row r="47" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
         <v>44.7</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+    </row>
+    <row r="48" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
         <v>41.1</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-    </row>
-    <row r="49" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="5">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+    </row>
+    <row r="49" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
         <v>37.5</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+    </row>
+    <row r="50" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
         <v>33.9</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-    </row>
-    <row r="51" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="5">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+    </row>
+    <row r="51" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
         <v>30.3</v>
       </c>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-    </row>
-    <row r="52" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="5">
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+    </row>
+    <row r="52" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
         <v>26.7</v>
       </c>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-    </row>
-    <row r="53" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="5">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+    </row>
+    <row r="53" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
         <v>23.1</v>
       </c>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-    </row>
-    <row r="54" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+    </row>
+    <row r="54" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
         <v>19.5</v>
       </c>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="5">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+    </row>
+    <row r="55" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
         <v>15</v>
       </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="5">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+    </row>
+    <row r="56" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
         <v>10.5</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" ht="16.2" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+    </row>
+    <row r="57" spans="1:7" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
         <v>6</v>
       </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B2:D2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="W2:X2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="K2:M2"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="W2:X2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
